--- a/商品校验调试记录.xlsx
+++ b/商品校验调试记录.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6027,6 +6027,2224 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>CPB防晒霜50g</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>CPB/肌肤之钥 御龄防晒霜防晒乳50ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 09:50:51</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配：搜索词规格['50g']，商品规格['50ml', '5']</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>CPB防晒霜50g</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>原装正品CPB肌肤之钥御龄防晒霜50ml高倍防晒隔离乳面部防护SPF50【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 09:51:03</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配：搜索词规格['50g']，商品规格['SPF50', '50ml', '5']</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>CPB滋润洁面125ml</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>【CPB】肌肤之钥净采洗面奶(滋润型)125ml/支</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:02:20</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>CPB长管隔离38ml 清爽</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>【肌肤之钥】CPB长管隔离霜37ml保湿滋润款控油提亮肤色</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:03:29</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>CPB长管隔离新款37ml滋润</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>【CPB】肌肤之钥光透妆前乳长管隔离37ml/支</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:04:34</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>CPB长管隔离新款37ml滋润</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>【肌肤之钥】CPB长管隔离霜37ml保湿滋润款控油提亮肤色</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:04:53</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>CPB长管隔离新款37ml滋润</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>【肌肤之钥】CPB长管隔离 黑隔离 37ml 妆前乳 提亮肤色</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:05:09</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>CPB长管隔离新款37ml滋润</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】 CPB长管隔离37ml *2光凝润采妆前霜 防晒保湿</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:05:23</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>MAC/魅可 尤雾弹口红唇膏#923 暖粉豆沙 哑光雾面显白【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:34:33</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=18.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可尤雾弹子弹头唇膏口红925 316 314 923正品显色显白【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:34:47</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=31.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可子弹头唇膏哑光滋润316/923显色尤雾弹显白口红正装</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:34:58</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=31.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>【520礼物】MAC/魅可全新轻尤雾弹子弹头口红唇膏316 314 923 930</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:35:11</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=31.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可口红哑光602/707/923/916泫雅色柔雾子弹头素颜口红送礼盒【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:35:23</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=31.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>MAC/魅可子弹头口红哑光小辣椒显白橘红色#316#923#925#666【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:35:33</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>MAC热吻棒67</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>【520情人节】MAC/魅可热吻棒唇膏口红显色哑光滋润不掉色67/69</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:36:36</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>MAC紫白饼</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>MAC/魅可 新品紫白饼粉饼7g 绝绝紫双色去黄提亮柔焦控油【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:37:48</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>MAC紫白饼</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可新品紫白饼粉饼双色去黄提亮柔焦控油轻薄【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:38:06</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>MiuMiu粉漾女士淡香氛50ml</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>MIUMIU缪缪同名女士香水EDP50ml</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:39:08</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>MiuMiu粉漾女士淡香氛50ml</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>缪缪(MiuMiu) 同名女士香水 莹铃滢蓝粉漾幻境游转【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:39:24</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>MiuMiu粉漾女士淡香氛50ml</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>正品Miu Miu缪缪同名游转幻境粉黛Twist黑盖五代女士浓香水简装【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:39:36</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>MiuMiu粉漾女士淡香氛50ml</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>【MIU MIU】缪缪女士玫瑰之水粉漾EDT淡香水100ml花香调</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:39:48</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>MIUMIU缪缪同名女士香水EDP50ml</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:40:51</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=40.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>【MIU MIU】 缪缪同名女士香水100ml红盖EDP</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:41:06</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=40.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>正品Miu Miu缪缪 经典同名 女士淡香精浓香水EDP一代 简装 意大利【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:41:21</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=40.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>缪缪(MiuMiu) 同名女士香水 莹铃滢蓝粉漾幻境游转【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>缪缪</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:41:34</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=40.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶-L2</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】超方瓶流光美肌粉底液#L2持妆水润30ml</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:42:38</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>NARS超方瓶粉底液L4</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】流光美肌粉底液 L4超方瓶DEAUVILLE 黄1.5白 健康小麦色 30ml</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:43:46</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液 L3#</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯/娜斯超方瓶粉底液L0/L1/L2持妆遮瑕30ml</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:44:55</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液 L3#</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr"/>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:45:14</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液 L3#</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr"/>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:45:22</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液 L3#</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】NARS/娜斯超方瓶流光美肌粉底液#L3持妆遮瑕不暗沉【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:45:31</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液#L1</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯/娜斯超方瓶粉底液L0/L1/L2持妆遮瑕30ml</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:46:38</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液#L1</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】超方瓶流光美肌粉底液L1 30ml保湿滋润持久遮瑕</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:46:51</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>NARS 粉底液 LO色</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯/娜斯超方瓶粉底液L0/L1/L2持妆遮瑕30ml</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 14:32:23</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>NARS纳斯定妆散粉</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】NARS纳斯新版定妆散粉控油定妆持久隐形毛孔提亮11g</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:02:16</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>NARS纳斯定妆散粉</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯流光美肌轻透持久定妆散粉新版11g</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:02:30</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>NARS纳斯定妆散粉</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯流光美肌轻透持久定妆散粉新版11g 提亮肤色【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:02:44</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>NARS纳斯定妆散粉</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯新版定妆大白散粉11g持久定妆</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:02:59</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】NARS超方瓶超雾瓶粉底持妆控油油皮柔雾遮瑕自然服帖</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:11:09</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=18.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯超方瓶持妆粉底液流光美肌养肤遮瑕持久不脱妆干皮女L1L2</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:11:25</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=36.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>NARS/娜斯超方瓶持妆粉底液#L2#L0#L1#L1.25#L3细腻服帖遮瑕30ML【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:11:35</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=27.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>【现货正品】NARS超方瓶粉底液 轻薄润贴持妆不卡粉遮瑕混干皮</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:11:47</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=27.3%)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/商品校验调试记录.xlsx
+++ b/商品校验调试记录.xlsx
@@ -442,14 +442,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K147"/>
+  <dimension ref="A1:K162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -8245,6 +8245,793 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉686 lose control</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr"/>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:38:25</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉686 lose control</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr"/>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:38:39</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉686 lose control</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯纳斯空气唇釉空气柔雾唇霜唇釉Gipsy#684玫瑰豆沙色口红</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:38:53</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=35.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>NARS细管101 NO ANGEL</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯口红细管哑光唇膏101#No Angel奶咖土棕1.5g</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:40:01</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>NARS细管101 NO ANGEL</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】NARS娜斯细管口红#102 #116  #135 #133 #1011.5g/支</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:40:18</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=28.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>NARS细管116 START ME UP</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯细管口红哑光唇膏1.5g#116烟杏START ME UP</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:41:27</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>NARS细管116 START ME UP</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】NARS娜斯细管口红#102 #116  #135 #133 #1011.5g/支</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:41:43</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=18.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>NARS细管133 TOO HOT TO HOLD</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯细管口红#133日烧赤粽TOO HOT TO HOLD 1.5g</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:42:52</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇1</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Nature BOBO/漾然澳洲番木瓜膏16g*3瓶润唇膏保湿女唇膜霜油</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>澳洲NatureBOBO</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>澳洲NatureBOBO</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:44:11</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇1</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Nature BOBO/澳洲番木瓜膏16g*5瓶润唇膏保湿女唇膜霜油</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>澳洲NatureBOBO</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>澳洲NatureBOBO</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:44:21</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇2</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲原装进口番木瓜膏创伤湿疹膏孕妇婴儿修复唇部</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>澳洲NatureBOBO</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>澳洲NatureBOBO</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:45:37</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇2</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Nature BOBO/澳洲番木瓜膏16g*5瓶润唇膏保湿女唇膜霜油</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>澳洲NatureBOBO</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>澳洲NatureBOBO</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:45:48</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇2</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Nature BOBO/漾然澳洲番木瓜膏16g*1瓶润唇膏保湿女唇膜霜油</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>澳洲NatureBOBO</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>澳洲NatureBOBO</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:46:02</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>SK2 神仙水230ml</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII男士神仙水精华露护肤补水紧致抗皱晶透保湿舒缓</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:47:08</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>SK2 神仙水230ml</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>SKII/SK2/skll男士神仙水精华露控油爽肤水230ml控油收毛孔正品</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:47:23</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/商品校验调试记录.xlsx
+++ b/商品校验调试记录.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K162"/>
+  <dimension ref="A1:K177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9032,6 +9032,801 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润面霜100g</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II赋能焕彩精华霜100g全新大红瓶滋润紧致保湿sk2</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:21:48</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>SK2神仙水330ML</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】神仙水330ml抗皱精华液sk2化妆品护肤品水乳生日礼物女</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:23:05</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 男士保湿焕活洁面霜120g</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>SK-Ⅱ男士保湿焕活洁面霜120g</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:15</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 男士保湿焕活洁面霜120g</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>【专柜行货】SKII男士保湿焕活洁面霜 120g氨基酸洗面奶</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:27</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 男士保湿焕活洁面霜120g</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II男士焕活保湿洁面霜120g</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:37</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 男士焕活护肤精华露 230ml</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>SK-II/SK2 男士神仙水焕活护肤精华露 230ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:25:55</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 男士焕活护肤精华露 230ml</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】 男士焕活护肤精华露230ml 保湿补水 提亮肌肤【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:26:05</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:06:52</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】SK2小银瓶淡斑精华液美白提亮肌因光蕴祛斑精华露50ml正品</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:07:10</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】小银瓶面部精华露50ml 肌因光蕴美白提亮祛斑淡痘印【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:07:22</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>【新年礼物】SK-II小银瓶精华液肌因光蕴情人节保湿补水淡斑送礼</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:07:35</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H174" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:08:48</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】SK2小银瓶淡斑精华液美白提亮肌因光蕴祛斑精华露50ml正品</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H175" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:09:05</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】小银瓶面部精华露50ml 肌因光蕴美白提亮祛斑淡痘印【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:09:19</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>【新年礼物】SK-II小银瓶精华液肌因光蕴情人节保湿补水淡斑送礼</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H177" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:09:31</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/商品校验调试记录.xlsx
+++ b/商品校验调试记录.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K536"/>
+  <dimension ref="A1:K566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -24638,32 +24638,36 @@
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>欧珑赤霞橘光护手霜30ML</t>
-        </is>
-      </c>
-      <c r="C459" s="2" t="inlineStr"/>
+          <t>罗拉散粉经典款29G</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>Laura Mercier罗拉散粉新版Translucent柔光透明哑光控油定妆29g</t>
+        </is>
+      </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>罗拉</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罗拉</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H459" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
@@ -24672,12 +24676,12 @@
       </c>
       <c r="J459" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:34:58</t>
+          <t>2026-05-21 15:31:34</t>
         </is>
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品名相似不足(ratio=50.0%)</t>
         </is>
       </c>
     </row>
@@ -24687,46 +24691,50 @@
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  赤霞橘光 100ML</t>
-        </is>
-      </c>
-      <c r="C460" s="2" t="inlineStr"/>
+          <t>马丁马吉拉-慵懒周末100ml</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>【1.2万人回购该品牌】马丁梅森马吉拉慵懒周末100ml 持久留香</t>
+        </is>
+      </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>梅森马吉拉</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>梅森马吉拉</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H460" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J460" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:36:35</t>
+          <t>2026-05-21 15:32:46</t>
         </is>
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -24736,32 +24744,36 @@
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
-        </is>
-      </c>
-      <c r="C461" s="2" t="inlineStr"/>
+          <t>慕拉得塑颜修复A醇精华30ml</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>【Murad】慕拉得a醇面部精华30ml视黄醇紧致抗初老提亮肤色A醇抗氧化</t>
+        </is>
+      </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>慕拉得</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>慕拉得</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H461" s="3" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
@@ -24770,12 +24782,12 @@
       </c>
       <c r="J461" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:37:45</t>
+          <t>2026-05-21 15:33:58</t>
         </is>
       </c>
       <c r="K461" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品名相似不足(ratio=33.3%)</t>
         </is>
       </c>
     </row>
@@ -24785,7 +24797,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
+          <t>欧珑赤霞橘光护手霜30ML</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr"/>
@@ -24819,7 +24831,7 @@
       </c>
       <c r="J462" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:43:17</t>
+          <t>2026-05-21 15:34:58</t>
         </is>
       </c>
       <c r="K462" s="2" t="inlineStr">
@@ -24834,10 +24846,14 @@
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
-        </is>
-      </c>
-      <c r="C463" s="2" t="inlineStr"/>
+          <t>欧珑赤霞橘光护手霜30ML</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>大牌清仓欧珑无极莹润身体乳滋润保湿香体留香持久可做护手霜15ml</t>
+        </is>
+      </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
           <t>欧珑</t>
@@ -24845,12 +24861,12 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr">
@@ -24859,7 +24875,7 @@
         </is>
       </c>
       <c r="H463" s="3" t="n">
-        <v>0</v>
+        <v>42.86</v>
       </c>
       <c r="I463" s="2" t="inlineStr">
         <is>
@@ -24868,12 +24884,12 @@
       </c>
       <c r="J463" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:43:41</t>
+          <t>2026-05-21 15:35:11</t>
         </is>
       </c>
       <c r="K463" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配；品名相似不足(ratio=42.9%)</t>
         </is>
       </c>
     </row>
@@ -24883,46 +24899,50 @@
       </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
-          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
-        </is>
-      </c>
-      <c r="C464" s="2" t="inlineStr"/>
+          <t>欧珑赤霞橘光护手霜30ML</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>【欧珑】莹润护手霜赤霞橘光无极乌龙30ml两款可选择持久留香清新体验</t>
+        </is>
+      </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>潘婷</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H464" s="3" t="n">
-        <v>0</v>
+        <v>57.14</v>
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J464" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:44:45</t>
+          <t>2026-05-21 15:35:33</t>
         </is>
       </c>
       <c r="K464" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -24932,13 +24952,13 @@
       </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
+          <t>欧珑淡香精  赤霞橘光 100ML</t>
         </is>
       </c>
       <c r="C465" s="2" t="inlineStr"/>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>倩碧</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
@@ -24966,7 +24986,7 @@
       </c>
       <c r="J465" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:48:08</t>
+          <t>2026-05-21 15:36:35</t>
         </is>
       </c>
       <c r="K465" s="2" t="inlineStr">
@@ -24981,13 +25001,13 @@
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇净颜美肌洁面乳</t>
+          <t>欧珑淡香精  无极乌龙 100ML</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr"/>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -25002,7 +25022,7 @@
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H466" s="3" t="n">
@@ -25015,12 +25035,12 @@
       </c>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:49:14</t>
+          <t>2026-05-21 15:37:45</t>
         </is>
       </c>
       <c r="K466" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -25030,23 +25050,27 @@
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
-        </is>
-      </c>
-      <c r="C467" s="2" t="inlineStr"/>
+          <t>欧珑淡香精  无极乌龙 100ML</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>【欧珑】淡香精9ml 赤霞橘光无极乌龙浓香水EDP持久留香Q版 带喷头</t>
+        </is>
+      </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G467" s="2" t="inlineStr">
@@ -25055,7 +25079,7 @@
         </is>
       </c>
       <c r="H467" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I467" s="2" t="inlineStr">
         <is>
@@ -25064,12 +25088,12 @@
       </c>
       <c r="J467" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:51:55</t>
+          <t>2026-05-21 15:38:00</t>
         </is>
       </c>
       <c r="K467" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
@@ -25079,23 +25103,27 @@
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
-        </is>
-      </c>
-      <c r="C468" s="2" t="inlineStr"/>
+          <t>欧珑淡香精  无极乌龙 100ML</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>【欧珑】无极乌龙香水赤霞橘光香氛持久生日礼物中性香</t>
+        </is>
+      </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G468" s="2" t="inlineStr">
@@ -25104,7 +25132,7 @@
         </is>
       </c>
       <c r="H468" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
@@ -25113,12 +25141,12 @@
       </c>
       <c r="J468" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:52:26</t>
+          <t>2026-05-21 15:38:14</t>
         </is>
       </c>
       <c r="K468" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
@@ -25128,46 +25156,50 @@
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
-        </is>
-      </c>
-      <c r="C469" s="2" t="inlineStr"/>
+          <t>欧珑淡香精 赤霞橘光 30ML</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>【Atelier Cologne】欧珑淡香水赤霞橘光30ml持久留香</t>
+        </is>
+      </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H469" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J469" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:52:39</t>
+          <t>2026-05-21 15:39:17</t>
         </is>
       </c>
       <c r="K469" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -25177,46 +25209,50 @@
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
-        </is>
-      </c>
-      <c r="C470" s="2" t="inlineStr"/>
+          <t>欧珑淡香精 情柚独钟 30ML</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】欧珑赤霞橘光无极乌龙情柚独钟30ml香水高级感</t>
+        </is>
+      </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H470" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J470" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:54:15</t>
+          <t>2026-05-21 15:40:31</t>
         </is>
       </c>
       <c r="K470" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -25226,46 +25262,50 @@
       </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
-        </is>
-      </c>
-      <c r="C471" s="2" t="inlineStr"/>
+          <t>欧珑淡香精 情柚独钟 30ML</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】欧珑情柚独钟30ml香氛持久留香礼物送女友赠礼</t>
+        </is>
+      </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>香奈儿</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H471" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J471" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:55:45</t>
+          <t>2026-05-21 15:40:43</t>
         </is>
       </c>
       <c r="K471" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -25275,13 +25315,17 @@
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
-        </is>
-      </c>
-      <c r="C472" s="2" t="inlineStr"/>
+          <t>欧珑淡香精 无极乌龙 30ML</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>咕噜噜、丁香瓜马上拼</t>
+        </is>
+      </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -25309,7 +25353,7 @@
       </c>
       <c r="J472" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:57:13</t>
+          <t>2026-05-21 15:41:44</t>
         </is>
       </c>
       <c r="K472" s="2" t="inlineStr">
@@ -25324,46 +25368,50 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
-        </is>
-      </c>
-      <c r="C473" s="2" t="inlineStr"/>
+          <t>欧珑淡香精 无极乌龙 30ML</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>【Atelier Cologne】欧珑淡香水无极乌龙30ml持久留香</t>
+        </is>
+      </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H473" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J473" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:57:38</t>
+          <t>2026-05-21 15:41:58</t>
         </is>
       </c>
       <c r="K473" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -25373,13 +25421,17 @@
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
-        </is>
-      </c>
-      <c r="C474" s="2" t="inlineStr"/>
+          <t>欧珑淡香精 无极乌龙 30ML</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>不支持7天无理由退换</t>
+        </is>
+      </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -25398,7 +25450,7 @@
         </is>
       </c>
       <c r="H474" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
@@ -25407,12 +25459,12 @@
       </c>
       <c r="J474" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:57:48</t>
+          <t>2026-05-21 15:42:11</t>
         </is>
       </c>
       <c r="K474" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=20.0%)</t>
         </is>
       </c>
     </row>
@@ -25422,13 +25474,13 @@
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+          <t>欧珑淡香精 雪松之恋 30ML</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr"/>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
@@ -25456,7 +25508,7 @@
       </c>
       <c r="J475" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:58:56</t>
+          <t>2026-05-21 15:43:17</t>
         </is>
       </c>
       <c r="K475" s="2" t="inlineStr">
@@ -25471,28 +25523,32 @@
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
-        </is>
-      </c>
-      <c r="C476" s="2" t="inlineStr"/>
+          <t>欧珑淡香精 雪松之恋 30ML</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】欧珑赤霞橘光无极乌龙情柚独钟30ml香水高级感</t>
+        </is>
+      </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G476" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H476" s="3" t="n">
@@ -25505,12 +25561,12 @@
       </c>
       <c r="J476" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:01:25</t>
+          <t>2026-05-21 15:43:30</t>
         </is>
       </c>
       <c r="K476" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -25520,13 +25576,13 @@
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>欧珑淡香精 雪松之恋 30ML</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr"/>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>欧珑</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
@@ -25554,7 +25610,7 @@
       </c>
       <c r="J477" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:01:40</t>
+          <t>2026-05-21 15:43:41</t>
         </is>
       </c>
       <c r="K477" s="2" t="inlineStr">
@@ -25569,13 +25625,13 @@
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr"/>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>潘婷</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
@@ -25603,7 +25659,7 @@
       </c>
       <c r="J478" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:02:10</t>
+          <t>2026-05-21 15:44:45</t>
         </is>
       </c>
       <c r="K478" s="2" t="inlineStr">
@@ -25618,23 +25674,27 @@
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>罗拉散粉经典款29G</t>
-        </is>
-      </c>
-      <c r="C479" s="2" t="inlineStr"/>
+          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>【潘婷】三分钟奇迹护发素发膜胶原蛋白强效护发素450ml</t>
+        </is>
+      </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>罗拉</t>
+          <t>潘婷</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>潘婷</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr">
@@ -25643,7 +25703,7 @@
         </is>
       </c>
       <c r="H479" s="3" t="n">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
@@ -25652,12 +25712,12 @@
       </c>
       <c r="J479" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:31:21</t>
+          <t>2026-05-21 15:45:01</t>
         </is>
       </c>
       <c r="K479" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
@@ -25667,22 +25727,22 @@
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>罗拉散粉经典款29G</t>
+          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>Laura Mercier罗拉散粉新版Translucent柔光透明哑光控油定妆29g</t>
+          <t>【潘婷】三分钟奇迹护发素发膜胶原蛋白强效护发素450ml</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>罗拉</t>
+          <t>潘婷</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>罗拉</t>
+          <t>潘婷</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
@@ -25692,11 +25752,11 @@
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H480" s="3" t="n">
-        <v>50</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
@@ -25705,12 +25765,12 @@
       </c>
       <c r="J480" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:31:34</t>
+          <t>2026-05-21 15:45:15</t>
         </is>
       </c>
       <c r="K480" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=50.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
@@ -25720,22 +25780,22 @@
       </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
-          <t>马丁马吉拉-慵懒周末100ml</t>
+          <t>倩碧 紫胖子卸妆膏125ml</t>
         </is>
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>【1.2万人回购该品牌】马丁梅森马吉拉慵懒周末100ml 持久留香</t>
+          <t>Clinique倩碧紫胖子卸妆膏125ml*2 眼唇深层清洁温和</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>梅森马吉拉</t>
+          <t>倩碧</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>梅森马吉拉</t>
+          <t>倩碧</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr">
@@ -25749,7 +25809,7 @@
         </is>
       </c>
       <c r="H481" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
@@ -25758,7 +25818,7 @@
       </c>
       <c r="J481" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:32:46</t>
+          <t>2026-05-21 15:46:21</t>
         </is>
       </c>
       <c r="K481" s="2" t="inlineStr">
@@ -25773,22 +25833,22 @@
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>慕拉得塑颜修复A醇精华30ml</t>
+          <t>倩碧 紫胖子卸妆膏125ml</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>【Murad】慕拉得a醇面部精华30ml视黄醇紧致抗初老提亮肤色A醇抗氧化</t>
+          <t>Clinique倩碧紫胖子卸妆膏125ml*2 眼唇深层清洁温和</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>慕拉得</t>
+          <t>倩碧</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>慕拉得</t>
+          <t>倩碧</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
@@ -25802,21 +25862,21 @@
         </is>
       </c>
       <c r="H482" s="3" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:33:58</t>
+          <t>2026-05-21 15:46:40</t>
         </is>
       </c>
       <c r="K482" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=33.3%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -25826,46 +25886,50 @@
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>欧珑赤霞橘光护手霜30ML</t>
-        </is>
-      </c>
-      <c r="C483" s="2" t="inlineStr"/>
+          <t>倩碧小雏菊裸色阳光腮#05</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>【Clinique】倩碧小雏菊腮红#01#02#05#07#08#15提亮自然</t>
+        </is>
+      </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>倩碧</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>倩碧</t>
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H483" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J483" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:34:58</t>
+          <t>2026-05-21 15:47:49</t>
         </is>
       </c>
       <c r="K483" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -25875,27 +25939,23 @@
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>欧珑赤霞橘光护手霜30ML</t>
-        </is>
-      </c>
-      <c r="C484" s="2" t="inlineStr">
-        <is>
-          <t>大牌清仓欧珑无极莹润身体乳滋润保湿香体留香持久可做护手霜15ml</t>
-        </is>
-      </c>
+          <t>倩碧小雏菊裸色阳光腮#05</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr"/>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>倩碧</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr">
@@ -25904,7 +25964,7 @@
         </is>
       </c>
       <c r="H484" s="3" t="n">
-        <v>42.86</v>
+        <v>0</v>
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
@@ -25913,12 +25973,12 @@
       </c>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:35:11</t>
+          <t>2026-05-21 15:48:08</t>
         </is>
       </c>
       <c r="K484" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；品名相似不足(ratio=42.9%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -25928,27 +25988,23 @@
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t>欧珑赤霞橘光护手霜30ML</t>
-        </is>
-      </c>
-      <c r="C485" s="2" t="inlineStr">
-        <is>
-          <t>【欧珑】莹润护手霜赤霞橘光无极乌龙30ml两款可选择持久留香清新体验</t>
-        </is>
-      </c>
+          <t>薇迪薇奇净颜美肌洁面乳</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr"/>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>薇迪薇奇</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G485" s="2" t="inlineStr">
@@ -25957,21 +26013,21 @@
         </is>
       </c>
       <c r="H485" s="3" t="n">
-        <v>57.14</v>
+        <v>0</v>
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:35:33</t>
+          <t>2026-05-21 15:49:14</t>
         </is>
       </c>
       <c r="K485" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -25981,46 +26037,50 @@
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  赤霞橘光 100ML</t>
-        </is>
-      </c>
-      <c r="C486" s="2" t="inlineStr"/>
+          <t>薇迪薇奇净颜美肌洁面乳</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>VIDIVICI女神洗面奶净颜美肌洁面乳氨基酸温和保湿卸妆120ml正品</t>
+        </is>
+      </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>薇迪薇奇</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>薇迪薇奇</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H486" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J486" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:36:35</t>
+          <t>2026-05-21 15:49:29</t>
         </is>
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -26030,46 +26090,50 @@
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
-        </is>
-      </c>
-      <c r="C487" s="2" t="inlineStr"/>
+          <t>薇姿VICHY洗发水绿标硫化硒去屑止痒控油洗发乳390ml</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>【薇姿】绿标洗发水390ml二硫化硒去头屑控油深层清洁舒缓头皮洗发露</t>
+        </is>
+      </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>薇姿</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>薇姿</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H487" s="3" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="I487" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J487" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:37:45</t>
+          <t>2026-05-21 15:50:35</t>
         </is>
       </c>
       <c r="K487" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -26079,27 +26143,27 @@
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
+          <t>伟博金萃高纯度鱼油1100</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>【欧珑】淡香精9ml 赤霞橘光无极乌龙浓香水EDP持久留香Q版 带喷头</t>
+          <t>现货伟博深海鱼油Omega3 Webber三倍增强浓缩鱼油DHA900mg200粒</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>芭比布朗</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr">
@@ -26108,7 +26172,7 @@
         </is>
       </c>
       <c r="H488" s="3" t="n">
-        <v>100</v>
+        <v>28.57</v>
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
@@ -26117,12 +26181,12 @@
       </c>
       <c r="J488" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:38:00</t>
+          <t>2026-05-21 15:51:42</t>
         </is>
       </c>
       <c r="K488" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=28.6%)</t>
         </is>
       </c>
     </row>
@@ -26132,27 +26196,23 @@
       </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
-        </is>
-      </c>
-      <c r="C489" s="2" t="inlineStr">
-        <is>
-          <t>【欧珑】无极乌龙香水赤霞橘光香氛持久生日礼物中性香</t>
-        </is>
-      </c>
+          <t>伟博金萃高纯度鱼油1100</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr"/>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G489" s="2" t="inlineStr">
@@ -26161,7 +26221,7 @@
         </is>
       </c>
       <c r="H489" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
@@ -26170,12 +26230,12 @@
       </c>
       <c r="J489" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:38:14</t>
+          <t>2026-05-21 15:51:55</t>
         </is>
       </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -26185,50 +26245,50 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 赤霞橘光 30ML</t>
+          <t>伟博金萃高纯度鱼油1100</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>【Atelier Cologne】欧珑淡香水赤霞橘光30ml持久留香</t>
+          <t>Webber Naturals伟博深海鱼油Omega-3高浓度三倍浓缩DHA成人200粒</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>芭比布朗</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H490" s="3" t="n">
-        <v>80</v>
+        <v>28.57</v>
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J490" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:39:17</t>
+          <t>2026-05-21 15:52:12</t>
         </is>
       </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=28.6%)</t>
         </is>
       </c>
     </row>
@@ -26238,50 +26298,46 @@
       </c>
       <c r="B491" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 情柚独钟 30ML</t>
-        </is>
-      </c>
-      <c r="C491" s="2" t="inlineStr">
-        <is>
-          <t>【正品行货】欧珑赤霞橘光无极乌龙情柚独钟30ml香水高级感</t>
-        </is>
-      </c>
+          <t>伟博金萃高纯度鱼油1100</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr"/>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H491" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J491" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:40:31</t>
+          <t>2026-05-21 15:52:26</t>
         </is>
       </c>
       <c r="K491" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -26291,50 +26347,46 @@
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 情柚独钟 30ML</t>
-        </is>
-      </c>
-      <c r="C492" s="2" t="inlineStr">
-        <is>
-          <t>【正品行货】欧珑情柚独钟30ml香氛持久留香礼物送女友赠礼</t>
-        </is>
-      </c>
+          <t>伟博金萃高纯度鱼油1100</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr"/>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G492" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H492" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:40:43</t>
+          <t>2026-05-21 15:52:39</t>
         </is>
       </c>
       <c r="K492" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -26344,27 +26396,27 @@
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
         </is>
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>咕噜噜、丁香瓜马上拼</t>
+          <t>3瓶 伟博天然硫酸氨糖软骨素180粒强效MSM缓疼痛中老年人维骨力D3</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G493" s="2" t="inlineStr">
@@ -26373,7 +26425,7 @@
         </is>
       </c>
       <c r="H493" s="3" t="n">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
@@ -26382,12 +26434,12 @@
       </c>
       <c r="J493" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:41:44</t>
+          <t>2026-05-21 15:53:43</t>
         </is>
       </c>
       <c r="K493" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
@@ -26397,22 +26449,22 @@
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>【Atelier Cologne】欧珑淡香水无极乌龙30ml持久留香</t>
+          <t>伟博硫酸氨糖软骨素 中老年成人维骨力D3促吸收 加拿大进口 180粒</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr">
@@ -26422,25 +26474,25 @@
       </c>
       <c r="G494" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H494" s="3" t="n">
-        <v>80</v>
+        <v>45.45</v>
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:41:58</t>
+          <t>2026-05-21 15:53:58</t>
         </is>
       </c>
       <c r="K494" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>规格不匹配；品名相似不足(ratio=45.5%)</t>
         </is>
       </c>
     </row>
@@ -26450,17 +26502,13 @@
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
-        </is>
-      </c>
-      <c r="C495" s="2" t="inlineStr">
-        <is>
-          <t>不支持7天无理由退换</t>
-        </is>
-      </c>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr"/>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
@@ -26479,7 +26527,7 @@
         </is>
       </c>
       <c r="H495" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
@@ -26488,12 +26536,12 @@
       </c>
       <c r="J495" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:42:11</t>
+          <t>2026-05-21 15:54:15</t>
         </is>
       </c>
       <c r="K495" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=20.0%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -26503,23 +26551,27 @@
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
-        </is>
-      </c>
-      <c r="C496" s="2" t="inlineStr"/>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>加拿大伟博氨糖软骨素180粒中老年成人天然维骨力D3促钙吸收关节</t>
+        </is>
+      </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>伟博</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G496" s="2" t="inlineStr">
@@ -26528,7 +26580,7 @@
         </is>
       </c>
       <c r="H496" s="3" t="n">
-        <v>0</v>
+        <v>45.45</v>
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
@@ -26537,12 +26589,12 @@
       </c>
       <c r="J496" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:43:17</t>
+          <t>2026-05-21 15:54:29</t>
         </is>
       </c>
       <c r="K496" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配；品名相似不足(ratio=45.5%)</t>
         </is>
       </c>
     </row>
@@ -26552,22 +26604,22 @@
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
+          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
         </is>
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】欧珑赤霞橘光无极乌龙情柚独钟30ml香水高级感</t>
+          <t>【520礼物】CHANEL/香奈儿山茶花洗面奶清爽控油净肤泡沫洁面乳</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>香奈儿</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>香奈儿</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
@@ -26577,11 +26629,11 @@
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H497" s="3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
@@ -26590,12 +26642,12 @@
       </c>
       <c r="J497" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:43:30</t>
+          <t>2026-05-21 15:55:34</t>
         </is>
       </c>
       <c r="K497" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
@@ -26605,13 +26657,13 @@
       </c>
       <c r="B498" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
+          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
         </is>
       </c>
       <c r="C498" s="2" t="inlineStr"/>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>欧珑</t>
+          <t>香奈儿</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -26639,7 +26691,7 @@
       </c>
       <c r="J498" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:43:41</t>
+          <t>2026-05-21 15:55:45</t>
         </is>
       </c>
       <c r="K498" s="2" t="inlineStr">
@@ -26654,46 +26706,50 @@
       </c>
       <c r="B499" s="2" t="inlineStr">
         <is>
-          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
-        </is>
-      </c>
-      <c r="C499" s="2" t="inlineStr"/>
+          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】CHANEL香奈儿柔和净肤泡沫洁清洁 山茶花洁面 150ml</t>
+        </is>
+      </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>潘婷</t>
+          <t>香奈儿</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>香奈儿</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G499" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H499" s="3" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:44:45</t>
+          <t>2026-05-21 15:55:57</t>
         </is>
       </c>
       <c r="K499" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -26703,22 +26759,22 @@
       </c>
       <c r="B500" s="2" t="inlineStr">
         <is>
-          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
+          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
         </is>
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>【潘婷】三分钟奇迹护发素发膜胶原蛋白强效护发素450ml</t>
+          <t>Chanel香奈儿山茶花洗面奶150ml柔和净肤泡沫洁面乳</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>潘婷</t>
+          <t>香奈儿</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>潘婷</t>
+          <t>香奈儿</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
@@ -26728,25 +26784,25 @@
       </c>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H500" s="3" t="n">
-        <v>81.81999999999999</v>
+        <v>91.67</v>
       </c>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J500" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:45:01</t>
+          <t>2026-05-21 15:56:09</t>
         </is>
       </c>
       <c r="K500" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -26756,27 +26812,23 @@
       </c>
       <c r="B501" s="2" t="inlineStr">
         <is>
-          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
-        </is>
-      </c>
-      <c r="C501" s="2" t="inlineStr">
-        <is>
-          <t>【潘婷】三分钟奇迹护发素发膜胶原蛋白强效护发素450ml</t>
-        </is>
-      </c>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr"/>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>潘婷</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>潘婷</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G501" s="2" t="inlineStr">
@@ -26785,7 +26837,7 @@
         </is>
       </c>
       <c r="H501" s="3" t="n">
-        <v>81.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
@@ -26794,12 +26846,12 @@
       </c>
       <c r="J501" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:45:15</t>
+          <t>2026-05-21 15:57:13</t>
         </is>
       </c>
       <c r="K501" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -26809,22 +26861,22 @@
       </c>
       <c r="B502" s="2" t="inlineStr">
         <is>
-          <t>倩碧 紫胖子卸妆膏125ml</t>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>Clinique倩碧紫胖子卸妆膏125ml*2 眼唇深层清洁温和</t>
+          <t>【雅诗兰黛】小棕瓶精华100ml第七代特润促进夜间修复抗衰香港仓发【5天内发货】</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>倩碧</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>倩碧</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
@@ -26847,7 +26899,7 @@
       </c>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:46:21</t>
+          <t>2026-05-21 15:57:26</t>
         </is>
       </c>
       <c r="K502" s="2" t="inlineStr">
@@ -26862,50 +26914,46 @@
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>倩碧 紫胖子卸妆膏125ml</t>
-        </is>
-      </c>
-      <c r="C503" s="2" t="inlineStr">
-        <is>
-          <t>Clinique倩碧紫胖子卸妆膏125ml*2 眼唇深层清洁温和</t>
-        </is>
-      </c>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="inlineStr"/>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>倩碧</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>倩碧</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G503" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H503" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:46:40</t>
+          <t>2026-05-21 15:57:38</t>
         </is>
       </c>
       <c r="K503" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -26915,50 +26963,46 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
-        </is>
-      </c>
-      <c r="C504" s="2" t="inlineStr">
-        <is>
-          <t>【Clinique】倩碧小雏菊腮红#01#02#05#07#08#15提亮自然</t>
-        </is>
-      </c>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr"/>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>倩碧</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>倩碧</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H504" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:47:49</t>
+          <t>2026-05-21 15:57:48</t>
         </is>
       </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -26968,13 +27012,13 @@
       </c>
       <c r="B505" s="2" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
+          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
         </is>
       </c>
       <c r="C505" s="2" t="inlineStr"/>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>倩碧</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
@@ -27002,7 +27046,7 @@
       </c>
       <c r="J505" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:48:08</t>
+          <t>2026-05-21 15:58:56</t>
         </is>
       </c>
       <c r="K505" s="2" t="inlineStr">
@@ -27017,23 +27061,27 @@
       </c>
       <c r="B506" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇净颜美肌洁面乳</t>
-        </is>
-      </c>
-      <c r="C506" s="2" t="inlineStr"/>
+          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评451.2万+条】EsteeLauder雅诗兰黛净莹柔肤洁面乳蓝洁面150ml</t>
+        </is>
+      </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G506" s="2" t="inlineStr">
@@ -27042,21 +27090,21 @@
         </is>
       </c>
       <c r="H506" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:49:14</t>
+          <t>2026-05-21 15:59:11</t>
         </is>
       </c>
       <c r="K506" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -27066,22 +27114,22 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇净颜美肌洁面乳</t>
+          <t>雅诗兰黛DW  2c0</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>VIDIVICI女神洗面奶净颜美肌洁面乳氨基酸温和保湿卸妆120ml正品</t>
+          <t>【正品行货】雅诗兰黛DW方气垫2C0 持久遮瑕控油服帖</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
@@ -27104,7 +27152,7 @@
       </c>
       <c r="J507" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:49:29</t>
+          <t>2026-05-21 16:00:22</t>
         </is>
       </c>
       <c r="K507" s="2" t="inlineStr">
@@ -27119,50 +27167,46 @@
       </c>
       <c r="B508" s="2" t="inlineStr">
         <is>
-          <t>薇姿VICHY洗发水绿标硫化硒去屑止痒控油洗发乳390ml</t>
-        </is>
-      </c>
-      <c r="C508" s="2" t="inlineStr">
-        <is>
-          <t>【薇姿】绿标洗发水390ml二硫化硒去头屑控油深层清洁舒缓头皮洗发露</t>
-        </is>
-      </c>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr"/>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>薇姿</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>薇姿</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H508" s="3" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:50:35</t>
+          <t>2026-05-21 16:01:25</t>
         </is>
       </c>
       <c r="K508" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -27172,22 +27216,18 @@
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
-        </is>
-      </c>
-      <c r="C509" s="2" t="inlineStr">
-        <is>
-          <t>现货伟博深海鱼油Omega3 Webber三倍增强浓缩鱼油DHA900mg200粒</t>
-        </is>
-      </c>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr"/>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>芭比布朗</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
@@ -27201,7 +27241,7 @@
         </is>
       </c>
       <c r="H509" s="3" t="n">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="I509" s="2" t="inlineStr">
         <is>
@@ -27210,12 +27250,12 @@
       </c>
       <c r="J509" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:51:42</t>
+          <t>2026-05-21 16:01:40</t>
         </is>
       </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=28.6%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -27225,46 +27265,50 @@
       </c>
       <c r="B510" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
-        </is>
-      </c>
-      <c r="C510" s="2" t="inlineStr"/>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>【78.6万人回购该品牌】Estee Lauder雅诗兰黛大棕罐封愈膜霜65ml紧致面霜</t>
+        </is>
+      </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H510" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:51:55</t>
+          <t>2026-05-21 16:01:56</t>
         </is>
       </c>
       <c r="K510" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -27274,22 +27318,18 @@
       </c>
       <c r="B511" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
-        </is>
-      </c>
-      <c r="C511" s="2" t="inlineStr">
-        <is>
-          <t>Webber Naturals伟博深海鱼油Omega-3高浓度三倍浓缩DHA成人200粒</t>
-        </is>
-      </c>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr"/>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>芭比布朗</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr">
@@ -27303,7 +27343,7 @@
         </is>
       </c>
       <c r="H511" s="3" t="n">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
@@ -27312,12 +27352,12 @@
       </c>
       <c r="J511" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:52:12</t>
+          <t>2026-05-21 16:02:10</t>
         </is>
       </c>
       <c r="K511" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=28.6%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -27327,13 +27367,13 @@
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr"/>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
@@ -27361,7 +27401,7 @@
       </c>
       <c r="J512" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:52:26</t>
+          <t>2026-05-21 16:03:15</t>
         </is>
       </c>
       <c r="K512" s="2" t="inlineStr">
@@ -27376,13 +27416,13 @@
       </c>
       <c r="B513" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="C513" s="2" t="inlineStr"/>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
@@ -27410,7 +27450,7 @@
       </c>
       <c r="J513" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:52:39</t>
+          <t>2026-05-21 16:03:29</t>
         </is>
       </c>
       <c r="K513" s="2" t="inlineStr">
@@ -27425,22 +27465,22 @@
       </c>
       <c r="B514" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>3瓶 伟博天然硫酸氨糖软骨素180粒强效MSM缓疼痛中老年人维骨力D3</t>
+          <t>【正品行货】雅诗兰黛红石榴洁面洗面奶60ml  细致毛孔深层清洁</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="F514" s="2" t="inlineStr">
@@ -27450,25 +27490,25 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H514" s="3" t="n">
-        <v>63.64</v>
+        <v>100</v>
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:53:43</t>
+          <t>2026-05-21 16:03:45</t>
         </is>
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -27478,22 +27518,22 @@
       </c>
       <c r="B515" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>伟博硫酸氨糖软骨素 中老年成人维骨力D3促吸收 加拿大进口 180粒</t>
+          <t>【正品行货】雅诗兰黛鲜活亮采红石榴洗面奶60ml深层清洁</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="F515" s="2" t="inlineStr">
@@ -27503,11 +27543,11 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H515" s="3" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="I515" s="2" t="inlineStr">
         <is>
@@ -27516,12 +27556,12 @@
       </c>
       <c r="J515" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:53:58</t>
+          <t>2026-05-21 16:03:59</t>
         </is>
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；品名相似不足(ratio=45.5%)</t>
+          <t>品名相似不足(ratio=50.0%)</t>
         </is>
       </c>
     </row>
@@ -27531,13 +27571,13 @@
       </c>
       <c r="B516" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="C516" s="2" t="inlineStr"/>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -27565,7 +27605,7 @@
       </c>
       <c r="J516" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:54:15</t>
+          <t>2026-05-21 16:07:21</t>
         </is>
       </c>
       <c r="K516" s="2" t="inlineStr">
@@ -27580,22 +27620,22 @@
       </c>
       <c r="B517" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>加拿大伟博氨糖软骨素180粒中老年成人天然维骨力D3促钙吸收关节</t>
+          <t>【专柜礼盒】雅诗兰黛眼霜第七代小棕瓶特润修护紧致送礼盒礼物</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
         <is>
-          <t>伟博</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="F517" s="2" t="inlineStr">
@@ -27609,7 +27649,7 @@
         </is>
       </c>
       <c r="H517" s="3" t="n">
-        <v>45.45</v>
+        <v>75</v>
       </c>
       <c r="I517" s="2" t="inlineStr">
         <is>
@@ -27618,12 +27658,12 @@
       </c>
       <c r="J517" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:54:29</t>
+          <t>2026-05-21 16:07:38</t>
         </is>
       </c>
       <c r="K517" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；品名相似不足(ratio=45.5%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
@@ -27633,22 +27673,22 @@
       </c>
       <c r="B518" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>【520礼物】CHANEL/香奈儿山茶花洗面奶清爽控油净肤泡沫洁面乳</t>
+          <t>【专柜礼盒】雅诗兰黛眼霜第七代小棕瓶特润修护紧致送礼盒礼物</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>香奈儿</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
         <is>
-          <t>香奈儿</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="F518" s="2" t="inlineStr">
@@ -27671,7 +27711,7 @@
       </c>
       <c r="J518" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:55:34</t>
+          <t>2026-05-21 16:07:52</t>
         </is>
       </c>
       <c r="K518" s="2" t="inlineStr">
@@ -27686,13 +27726,13 @@
       </c>
       <c r="B519" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="C519" s="2" t="inlineStr"/>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>香奈儿</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
@@ -27720,7 +27760,7 @@
       </c>
       <c r="J519" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:55:45</t>
+          <t>2026-05-21 16:08:07</t>
         </is>
       </c>
       <c r="K519" s="2" t="inlineStr">
@@ -27735,22 +27775,22 @@
       </c>
       <c r="B520" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>【原装正品】CHANEL香奈儿柔和净肤泡沫洁清洁 山茶花洁面 150ml</t>
+          <t>【雅诗兰黛】第七代小棕瓶特润修护肌活精华液淡纹舒缓提亮紧致保湿</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>香奈儿</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>香奈儿</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr">
@@ -27760,25 +27800,25 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H520" s="3" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:55:57</t>
+          <t>2026-05-21 16:08:19</t>
         </is>
       </c>
       <c r="K520" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
@@ -27788,50 +27828,46 @@
       </c>
       <c r="B521" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
-        </is>
-      </c>
-      <c r="C521" s="2" t="inlineStr">
-        <is>
-          <t>Chanel香奈儿山茶花洗面奶150ml柔和净肤泡沫洁面乳</t>
-        </is>
-      </c>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="inlineStr"/>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>香奈儿</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>香奈儿</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H521" s="3" t="n">
-        <v>91.67</v>
+        <v>0</v>
       </c>
       <c r="I521" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J521" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:56:09</t>
+          <t>2026-05-21 16:10:07</t>
         </is>
       </c>
       <c r="K521" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -27841,10 +27877,14 @@
       </c>
       <c r="B522" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
-        </is>
-      </c>
-      <c r="C522" s="2" t="inlineStr"/>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛紧塑线雕精华液面部提拉祛黄提亮100ML淡纹</t>
+        </is>
+      </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
           <t>雅诗兰黛</t>
@@ -27852,12 +27892,12 @@
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G522" s="2" t="inlineStr">
@@ -27866,7 +27906,7 @@
         </is>
       </c>
       <c r="H522" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
@@ -27875,12 +27915,12 @@
       </c>
       <c r="J522" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:57:13</t>
+          <t>2026-05-21 16:10:27</t>
         </is>
       </c>
       <c r="K522" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
@@ -27890,12 +27930,12 @@
       </c>
       <c r="B523" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
         </is>
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>【雅诗兰黛】小棕瓶精华100ml第七代特润促进夜间修复抗衰香港仓发【5天内发货】</t>
+          <t>雅诗兰黛紧塑线雕精华面部提拉紧致淡法令纹100ML小银瓶抗衰老</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
@@ -27915,25 +27955,25 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H523" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I523" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J523" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:57:26</t>
+          <t>2026-05-21 16:10:46</t>
         </is>
       </c>
       <c r="K523" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
@@ -27943,7 +27983,7 @@
       </c>
       <c r="B524" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
         </is>
       </c>
       <c r="C524" s="2" t="inlineStr"/>
@@ -27977,7 +28017,7 @@
       </c>
       <c r="J524" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:57:38</t>
+          <t>2026-05-21 16:11:04</t>
         </is>
       </c>
       <c r="K524" s="2" t="inlineStr">
@@ -27992,7 +28032,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr"/>
@@ -28026,7 +28066,7 @@
       </c>
       <c r="J525" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:57:48</t>
+          <t>2026-05-21 16:53:00</t>
         </is>
       </c>
       <c r="K525" s="2" t="inlineStr">
@@ -28041,7 +28081,7 @@
       </c>
       <c r="B526" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
         </is>
       </c>
       <c r="C526" s="2" t="inlineStr"/>
@@ -28075,7 +28115,7 @@
       </c>
       <c r="J526" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:58:56</t>
+          <t>2026-05-21 16:53:29</t>
         </is>
       </c>
       <c r="K526" s="2" t="inlineStr">
@@ -28090,12 +28130,12 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>【品牌好评451.2万+条】EsteeLauder雅诗兰黛净莹柔肤洁面乳蓝洁面150ml</t>
+          <t>【雅诗兰黛】抗蓝光小棕瓶眼霜15ml/瓶</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
@@ -28128,7 +28168,7 @@
       </c>
       <c r="J527" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:59:11</t>
+          <t>2026-05-21 16:53:50</t>
         </is>
       </c>
       <c r="K527" s="2" t="inlineStr">
@@ -28143,12 +28183,12 @@
       </c>
       <c r="B528" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛DW  2c0</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛DW方气垫2C0 持久遮瑕控油服帖</t>
+          <t>【ESTEE LAUDER】雅诗兰黛智妍夜晚霜75ml抗老修护</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
@@ -28181,7 +28221,7 @@
       </c>
       <c r="J528" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:00:22</t>
+          <t>2026-05-21 16:54:58</t>
         </is>
       </c>
       <c r="K528" s="2" t="inlineStr">
@@ -28196,7 +28236,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr"/>
@@ -28230,7 +28270,7 @@
       </c>
       <c r="J529" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:01:25</t>
+          <t>2026-05-21 16:55:20</t>
         </is>
       </c>
       <c r="K529" s="2" t="inlineStr">
@@ -28245,7 +28285,7 @@
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="C530" s="2" t="inlineStr"/>
@@ -28279,7 +28319,7 @@
       </c>
       <c r="J530" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:01:40</t>
+          <t>2026-05-21 16:55:39</t>
         </is>
       </c>
       <c r="K530" s="2" t="inlineStr">
@@ -28294,12 +28334,12 @@
       </c>
       <c r="B531" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>【78.6万人回购该品牌】Estee Lauder雅诗兰黛大棕罐封愈膜霜65ml紧致面霜</t>
+          <t>【8.81万人评价品牌正品】ESTEELAUDER雅诗兰黛智妍夜胶原晚霜75ml 淡纹紧致</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
@@ -28332,7 +28372,7 @@
       </c>
       <c r="J531" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:01:56</t>
+          <t>2026-05-21 16:55:56</t>
         </is>
       </c>
       <c r="K531" s="2" t="inlineStr">
@@ -28347,46 +28387,50 @@
       </c>
       <c r="B532" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
-        </is>
-      </c>
-      <c r="C532" s="2" t="inlineStr"/>
+          <t>茵芙纱 三色遮瑕4.5g</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>【IPSA】茵芙莎三色遮瑕盘4.5g 遮瑕膏遮痘印痘痘黑眼圈持久妆效【5天内发货】</t>
+        </is>
+      </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>茵芙莎</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>茵芙莎</t>
         </is>
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G532" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H532" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I532" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J532" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:02:10</t>
+          <t>2026-05-21 16:56:45</t>
         </is>
       </c>
       <c r="K532" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -28396,46 +28440,50 @@
       </c>
       <c r="B533" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
-        </is>
-      </c>
-      <c r="C533" s="2" t="inlineStr"/>
+          <t>茵芙纱 三色遮瑕4.5g</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>【IPSA】茵芙莎三色遮瑕膏4.5g遮黑眼圈痘痘泪沟修饰肤色【5天内发货】</t>
+        </is>
+      </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>茵芙莎</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>茵芙莎</t>
         </is>
       </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H533" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I533" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J533" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:03:15</t>
+          <t>2026-05-21 16:56:54</t>
         </is>
       </c>
       <c r="K533" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -28445,18 +28493,22 @@
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
-        </is>
-      </c>
-      <c r="C534" s="2" t="inlineStr"/>
+          <t>资生堂安耐晒60ml新版</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>【4.55万人评价品牌正品】安耐晒小金瓶防晒霜24年新版60ML 防水防晒高倍防晒</t>
+        </is>
+      </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>资生堂</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>安耐晒</t>
         </is>
       </c>
       <c r="F534" s="2" t="inlineStr">
@@ -28466,11 +28518,11 @@
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H534" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I534" s="2" t="inlineStr">
         <is>
@@ -28479,12 +28531,12 @@
       </c>
       <c r="J534" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:03:29</t>
+          <t>2026-05-21 17:03:19</t>
         </is>
       </c>
       <c r="K534" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品牌不一致；品名相似不足(ratio=50.0%)</t>
         </is>
       </c>
     </row>
@@ -28494,22 +28546,22 @@
       </c>
       <c r="B535" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
+          <t>资生堂安耐晒60ml新版</t>
         </is>
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛红石榴洁面洗面奶60ml  细致毛孔深层清洁</t>
+          <t>正品Shiseido资生堂新款安耐晒防晒霜60ml高度防晒防水防汗SPF50+【5天内发货】</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>资生堂</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>资生堂</t>
         </is>
       </c>
       <c r="F535" s="2" t="inlineStr">
@@ -28523,7 +28575,7 @@
         </is>
       </c>
       <c r="H535" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I535" s="2" t="inlineStr">
         <is>
@@ -28532,7 +28584,7 @@
       </c>
       <c r="J535" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 16:03:45</t>
+          <t>2026-05-21 17:03:33</t>
         </is>
       </c>
       <c r="K535" s="2" t="inlineStr">
@@ -28547,22 +28599,22 @@
       </c>
       <c r="B536" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
+          <t>资生堂安耐晒60ml新版</t>
         </is>
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛鲜活亮采红石榴洗面奶60ml深层清洁</t>
+          <t>正品Shiseido资生堂新款安耐晒防晒霜60ml高度防晒防水防汗SPF50+【5天内发货】</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>资生堂</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛</t>
+          <t>资生堂</t>
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr">
@@ -28576,21 +28628,1607 @@
         </is>
       </c>
       <c r="H536" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I536" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:03:44</t>
+        </is>
+      </c>
+      <c r="K536" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="n">
+        <v>536</v>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>资生堂安耐晒60ml新版</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>【4.55万人评价品牌正品】安耐晒小金瓶防晒霜24年新版60ML 防水防晒高倍防晒</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H537" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="I536" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J536" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-21 16:03:59</t>
-        </is>
-      </c>
-      <c r="K536" s="2" t="inlineStr">
+      <c r="I537" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J537" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:03:56</t>
+        </is>
+      </c>
+      <c r="K537" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="n">
+        <v>537</v>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>资生堂安耐晒60ml新版</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr"/>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H538" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I538" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J538" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:04:10</t>
+        </is>
+      </c>
+      <c r="K538" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="n">
+        <v>538</v>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>资生堂百优面霜 75ml</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】百优精华面霜75ml补水保湿</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H539" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I539" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J539" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:05:11</t>
+        </is>
+      </c>
+      <c r="K539" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="n">
+        <v>539</v>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子150ml 新版</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂新版蓝胖子防晒霜150ml防晒乳防水防汗不油腻</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H540" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J540" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:06:15</t>
+        </is>
+      </c>
+      <c r="K540" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子150ml 新版</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子新艳阳夏臻效水动力防晒乳150ml 超强防护力新版防水【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H541" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I541" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J541" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:06:29</t>
+        </is>
+      </c>
+      <c r="K541" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="n">
+        <v>541</v>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子防晒50ml</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销429.6万+件】2支资生堂新版蓝胖子防晒霜50ml隔离防紫外线</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H542" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I542" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J542" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:07:34</t>
+        </is>
+      </c>
+      <c r="K542" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="n">
+        <v>542</v>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子防晒50ml（新版）</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子防晒霜50ml新版不油腻防水防晒乳艳阳清爽隔离SPF50+【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G543" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H543" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I543" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J543" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:08:36</t>
+        </is>
+      </c>
+      <c r="K543" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="n">
+        <v>543</v>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>资生堂琉璃洁面125ml</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】时光琉璃洁面125ml深层清洁保湿补水洗面奶</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H544" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I544" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J544" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:09:43</t>
+        </is>
+      </c>
+      <c r="K544" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="n">
+        <v>544</v>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>资生堂琉璃洁面125ml</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】时光琉璃洁面125ml温和保湿补水深层清洁洗面奶</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G545" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H545" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I545" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J545" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:10:01</t>
+        </is>
+      </c>
+      <c r="K545" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>资生堂琉璃洁面50ml新版</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂时光琉璃洁面50ml</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H546" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I546" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J546" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:11:09</t>
+        </is>
+      </c>
+      <c r="K546" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="n">
+        <v>546</v>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>资生堂琉璃爽肤水74ml新版</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评340.2万+条】Shiseido/资生堂时光琉璃爽肤水74ml改善暗沉保湿紧致修复提亮</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G547" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H547" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I547" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J547" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:12:16</t>
+        </is>
+      </c>
+      <c r="K547" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="n">
+        <v>547</v>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>资生堂琉璃爽肤水74ml新版</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销429.6万+件】Shiseido/资生堂时光琉璃爽肤水74ml补水保湿滋润紧致透亮修复</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H548" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J548" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:12:31</t>
+        </is>
+      </c>
+      <c r="K548" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="n">
+        <v>548</v>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>资生堂男生爽肤水150ml</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂男士活力均衡水150ml修护保湿清爽控油爽肤水</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H549" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J549" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:13:36</t>
+        </is>
+      </c>
+      <c r="K549" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="n">
+        <v>549</v>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>资生堂男生爽肤水150ml</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】男士活力均衡水150ml 男士补水保湿爽肤水</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H550" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I550" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J550" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:13:49</t>
+        </is>
+      </c>
+      <c r="K550" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>资生堂男士洁面乳125ml</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】时光琉璃洁面125ml温和保湿补水深层清洁洗面奶</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G551" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H551" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I551" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J551" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:14:56</t>
+        </is>
+      </c>
+      <c r="K551" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>资生堂男士洁面乳125ml</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】时光琉璃洁面125ml深层清洁保湿补水洗面奶</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H552" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I552" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J552" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:15:10</t>
+        </is>
+      </c>
+      <c r="K552" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="n">
+        <v>552</v>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>资生堂男士乳液100ml</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂男士焕能肌活滋润乳 100ml</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H553" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I553" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J553" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:16:13</t>
+        </is>
+      </c>
+      <c r="K553" s="2" t="inlineStr">
         <is>
           <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="n">
+        <v>553</v>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>资生堂男士乳液100ml</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂悦薇水颜亮肤滋润乳液老款滋润亮肤紧颜100ml</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H554" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J554" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:16:27</t>
+        </is>
+      </c>
+      <c r="K554" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>资生堂男士乳液100ml</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G555" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H555" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I555" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J555" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:16:43</t>
+        </is>
+      </c>
+      <c r="K555" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="n">
+        <v>555</v>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微清爽水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂第二代悦薇水+乳(清爽 /滋润)</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H556" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I556" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J556" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:17:33</t>
+        </is>
+      </c>
+      <c r="K556" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="n">
+        <v>556</v>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微清爽水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G557" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H557" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I557" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J557" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:17:43</t>
+        </is>
+      </c>
+      <c r="K557" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="n">
+        <v>557</v>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】资生堂悦薇珀翡紧颜亮肤水(滋润型)150ml</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H558" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I558" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J558" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:18:47</t>
+        </is>
+      </c>
+      <c r="K558" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="n">
+        <v>558</v>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G559" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H559" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I559" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J559" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:18:58</t>
+        </is>
+      </c>
+      <c r="K559" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H560" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I560" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J560" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:19:09</t>
+        </is>
+      </c>
+      <c r="K560" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】资生堂悦薇珀翡紧颜亮肤水(滋润型)150ml</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G561" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H561" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I561" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J561" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:19:23</t>
+        </is>
+      </c>
+      <c r="K561" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂第二代悦薇智感紧颜亮肤水150ml  补水提亮清爽版</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H562" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I562" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J562" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:19:37</t>
+        </is>
+      </c>
+      <c r="K562" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇纯A小针管眼霜20ml</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂悦薇智感视黄醇抗皱霜 20ml 新版小针管眼霜</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G563" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H563" s="3" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="I563" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J563" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:20:44</t>
+        </is>
+      </c>
+      <c r="K563" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H564" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I564" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J564" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:21:51</t>
+        </is>
+      </c>
+      <c r="K564" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂悦薇水颜亮肤滋润乳液老款滋润亮肤紧颜100ml</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H565" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I565" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J565" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:22:07</t>
+        </is>
+      </c>
+      <c r="K565" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇清爽乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H566" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I566" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J566" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:23:14</t>
+        </is>
+      </c>
+      <c r="K566" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
     </row>

--- a/商品校验调试记录.xlsx
+++ b/商品校验调试记录.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K566"/>
+  <dimension ref="A1:K587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30232,6 +30232,1119 @@
         </is>
       </c>
     </row>
+    <row r="567">
+      <c r="A567" s="2" t="n">
+        <v>566</v>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑 蓝风铃香水100ml</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>Jo Malone/祖玛珑蓝风铃100ml清新留香</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H567" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I567" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J567" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:24:23</t>
+        </is>
+      </c>
+      <c r="K567" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑鼠尾草与海盐香水30ml清新持久留香</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H568" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I568" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J568" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:25:32</t>
+        </is>
+      </c>
+      <c r="K568" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】JO MALONE/祖.玛珑鼠尾草与海盐30ml清新持久留香</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H569" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I569" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J569" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:25:50</t>
+        </is>
+      </c>
+      <c r="K569" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师蓝标粉底液2#</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】蓝标大师粉底液 2 号 30ml 保湿遮瑕持久干皮</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H570" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I570" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J570" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:26:59</t>
+        </is>
+      </c>
+      <c r="K570" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师蓝标粉底液2#</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼新款蓝标大师粉底液#1 #2 #3持久遮瑕细腻服帖</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F571" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G571" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H571" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I571" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J571" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:27:19</t>
+        </is>
+      </c>
+      <c r="K571" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底30ml#2</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>【正品保证】阿玛尼权力PRO粉底液2# 绒雾质感混油肌粉底遮瑕【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H572" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I572" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J572" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:28:38</t>
+        </is>
+      </c>
+      <c r="K572" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="n">
+        <v>572</v>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底30ml#2</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼权力无瑕持妆PRO粉底液(红标)30ml 绒雾感遮瑕</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F573" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H573" s="3" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I573" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J573" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:28:53</t>
+        </is>
+      </c>
+      <c r="K573" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="n">
+        <v>573</v>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底30ml#3</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】权力粉底液 3 号新款 30ml 持妆控油遮瑕油皮亲妈持久</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H574" s="3" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="I574" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J574" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:30:03</t>
+        </is>
+      </c>
+      <c r="K574" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="n">
+        <v>574</v>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼「大师」锁光粉底液#3</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】蓝标大师粉底液3#新版遮瑕轻薄透气持久30ml</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G575" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H575" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I575" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J575" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:31:12</t>
+        </is>
+      </c>
+      <c r="K575" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼气垫替换芯3号</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>GIORGIO ARMANI/阿玛尼红气垫替换芯15g#3号色单双个控油持妆新款</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H576" s="3" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I576" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J576" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:32:21</t>
+        </is>
+      </c>
+      <c r="K576" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼气垫替换芯3号</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】ARMANI阿玛尼红气垫替换芯3号15g新版 遮瑕养肤持久</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F577" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H577" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I577" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J577" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:32:39</t>
+        </is>
+      </c>
+      <c r="K577" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="n">
+        <v>577</v>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻全新菁纯柔雾哑光唇釉  275# 单支礼盒装</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H578" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I578" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J578" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:33:47</t>
+        </is>
+      </c>
+      <c r="K578" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】菁纯裸唇釉小蛮腰275 279 313 281 274哑光丝绒柔雾口红正品</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G579" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H579" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I579" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J579" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:34:05</t>
+        </is>
+      </c>
+      <c r="K579" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="n">
+        <v>579</v>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Lancome/兰蔻菁纯裸唇釉哑光丝绒轻盈质地显白有气色</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H580" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I580" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J580" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:34:22</t>
+        </is>
+      </c>
+      <c r="K580" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>【现货直发】兰蔻菁纯裸唇釉6ml  粉盖柔雾丝滑浓郁口红女生礼物</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G581" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H581" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I581" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J581" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:34:35</t>
+        </is>
+      </c>
+      <c r="K581" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="n">
+        <v>581</v>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水50ml 25年新品</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H582" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I582" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J582" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:35:45</t>
+        </is>
+      </c>
+      <c r="K582" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="n">
+        <v>582</v>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰绮梦馥栀香型女士香水50ml</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G583" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H583" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I583" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J583" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:36:03</t>
+        </is>
+      </c>
+      <c r="K583" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="n">
+        <v>583</v>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦馥栀女士香水红瓶馥郁版EDP 50ml</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H584" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I584" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J584" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:36:26</t>
+        </is>
+      </c>
+      <c r="K584" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="n">
+        <v>584</v>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>POLA 黑BA洁面</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>POLA/宝丽第七代洗面奶黑BA控油保湿抗衰老洁面2支</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>宝丽</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr">
+        <is>
+          <t>宝丽</t>
+        </is>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G585" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H585" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I585" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J585" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:37:33</t>
+        </is>
+      </c>
+      <c r="K585" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="n">
+        <v>585</v>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>POLA 黑BA洁面</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>日本本土版第七代POLA/宝丽黑BA抗糖保湿洁面洗面奶</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>宝丽</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>宝丽</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H586" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I586" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J586" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:37:52</t>
+        </is>
+      </c>
+      <c r="K586" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>POLA 黑BA洁面</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>【POLA】宝丽BA深层清洁洗面奶9g*5小样洁面乳温和不紧绷</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>宝丽</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr">
+        <is>
+          <t>宝丽</t>
+        </is>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G587" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H587" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I587" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J587" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:38:07</t>
+        </is>
+      </c>
+      <c r="K587" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/商品校验调试记录.xlsx
+++ b/商品校验调试记录.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K587"/>
+  <dimension ref="A1:K767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31345,6 +31345,9530 @@
         </is>
       </c>
     </row>
+    <row r="588">
+      <c r="A588" s="2" t="n">
+        <v>587</v>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>HR/赫莲娜绿宝瓶眼霜15ml+小样3ml*5眼部修复淡化黑眼圈【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H588" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I588" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J588" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:55:14</t>
+        </is>
+      </c>
+      <c r="K588" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>HR/赫莲娜绿宝瓶眼霜15ml眼部修复淡化黑眼圈【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G589" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H589" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I589" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J589" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:55:29</t>
+        </is>
+      </c>
+      <c r="K589" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="n">
+        <v>589</v>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>【HR】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈护肤品化妆品情人节520礼盒</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H590" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I590" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J590" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:55:46</t>
+        </is>
+      </c>
+      <c r="K590" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="n">
+        <v>590</v>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场三合一经典原味白咖啡525g</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F591" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H591" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I591" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J591" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:56:58</t>
+        </is>
+      </c>
+      <c r="K591" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="n">
+        <v>591</v>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F592" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H592" s="3" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="I592" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J592" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:58:07</t>
+        </is>
+      </c>
+      <c r="K592" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="n">
+        <v>592</v>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>进口马来西亚旧街场经典白咖啡三合一原味榛果少糖特浓15条装袋装</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G593" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H593" s="3" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="I593" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J593" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:58:24</t>
+        </is>
+      </c>
+      <c r="K593" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="n">
+        <v>593</v>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>进口马来西亚旧街场经典白咖啡三合一原味榛果少糖特浓15条装袋装</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H594" s="3" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="I594" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J594" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:58:42</t>
+        </is>
+      </c>
+      <c r="K594" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="n">
+        <v>594</v>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口三合一速溶白咖啡低糖醇厚条装525g</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>【正品保障】马来西亚旧街场咖啡原装进口三合一经典风味速溶榛果</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G595" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H595" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I595" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J595" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:59:50</t>
+        </is>
+      </c>
+      <c r="K595" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="n">
+        <v>595</v>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口三合一速溶白咖啡低糖醇厚条装525g</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>【多袋】马来西亚旧街场原装进口三合一原味咖啡袋装榛果速溶经典</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H596" s="3" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="I596" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J596" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:00:12</t>
+        </is>
+      </c>
+      <c r="K596" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="n">
+        <v>596</v>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F597" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G597" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H597" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I597" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J597" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:01:23</t>
+        </is>
+      </c>
+      <c r="K597" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="n">
+        <v>597</v>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口OLDTOWN旧街场速溶白咖啡粉老街特浓醇香咖啡饮品</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F598" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H598" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I598" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J598" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:01:38</t>
+        </is>
+      </c>
+      <c r="K598" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="n">
+        <v>598</v>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>进口马来西亚旧街场经典白咖啡三合一原味榛果少糖特浓15条装袋装</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F599" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G599" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H599" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="I599" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J599" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:01:57</t>
+        </is>
+      </c>
+      <c r="K599" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="n">
+        <v>599</v>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口咖啡粉OLDTOWN旧街场榛果味白咖啡速溶三合一3袋装</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H600" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I600" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J600" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:02:16</t>
+        </is>
+      </c>
+      <c r="K600" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G601" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H601" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I601" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J601" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:03:26</t>
+        </is>
+      </c>
+      <c r="K601" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="n">
+        <v>601</v>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口旧街场咖啡二合一无蔗糖白咖啡速溶咖啡粉30条</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H602" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I602" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J602" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:03:44</t>
+        </is>
+      </c>
+      <c r="K602" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="n">
+        <v>602</v>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>【旧街场】咖啡无蔗糖份二合一速溶白咖啡粉3袋马来西亚进口港版正品</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G603" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H603" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I603" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J603" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:04:04</t>
+        </is>
+      </c>
+      <c r="K603" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="n">
+        <v>603</v>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场咖啡无蔗糖二合一速溶白咖啡粉2袋装港版正品</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H604" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I604" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J604" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:04:22</t>
+        </is>
+      </c>
+      <c r="K604" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场咖啡无蔗糖二合一速溶白咖啡粉2袋装港版正品</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F605" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H605" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I605" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J605" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:04:41</t>
+        </is>
+      </c>
+      <c r="K605" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口白咖啡咸焦糖525g</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>【旧街场】马来西亚进口咖啡港版3合1速溶白咖啡咸焦糖味15条3袋装</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H606" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I606" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J606" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:05:49</t>
+        </is>
+      </c>
+      <c r="K606" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="n">
+        <v>606</v>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>【旧街场】丝滑含微研磨减少糖三合一速溶白咖啡粉375g*3袋装提神防困</t>
+        </is>
+      </c>
+      <c r="D607" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F607" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G607" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H607" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I607" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J607" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:07:01</t>
+        </is>
+      </c>
+      <c r="K607" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=30.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="n">
+        <v>607</v>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口旧街场咖啡二合一无蔗糖白咖啡速溶咖啡粉30条</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G608" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H608" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="I608" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J608" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:07:22</t>
+        </is>
+      </c>
+      <c r="K608" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="n">
+        <v>608</v>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
+        </is>
+      </c>
+      <c r="D609" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F609" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G609" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H609" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I609" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J609" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:07:40</t>
+        </is>
+      </c>
+      <c r="K609" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="n">
+        <v>609</v>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口速溶咖啡粉OLDTOWN旧街场三合一蔗糖白咖啡3袋装45条</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G610" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H610" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="I610" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J610" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:08:00</t>
+        </is>
+      </c>
+      <c r="K610" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="n">
+        <v>610</v>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口OLDTOWN旧街场速溶白咖啡粉老街特浓醇香咖啡饮品</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F611" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G611" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H611" s="3" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I611" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J611" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:09:06</t>
+        </is>
+      </c>
+      <c r="K611" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="n">
+        <v>611</v>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口速溶咖啡粉OLDTOWN旧街场三合一蔗糖白咖啡3袋装45条</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H612" s="3" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I612" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J612" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:09:27</t>
+        </is>
+      </c>
+      <c r="K612" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚进口咖啡粉OLDTOWN旧街场榛果味白咖啡速溶三合一3袋装</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F613" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G613" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H613" s="3" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I613" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J613" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:09:46</t>
+        </is>
+      </c>
+      <c r="K613" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="n">
+        <v>613</v>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>港版丨马来西亚进口咖啡粉OLDTOWN 旧街场榛果白咖啡速溶三合一</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>旧街场</t>
+        </is>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G614" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H614" s="3" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I614" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J614" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:10:01</t>
+        </is>
+      </c>
+      <c r="K614" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="n">
+        <v>614</v>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>植村秀持久保湿定妆喷雾100ml</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>SHU UEMURA 植村秀 羽纱持妆喷雾100ml 微光版小黑胶持久控油保湿</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="F615" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G615" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H615" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I615" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J615" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:11:11</t>
+        </is>
+      </c>
+      <c r="K615" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="n">
+        <v>615</v>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>植村秀持久保湿定妆喷雾100ml</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀新品元气小红喷定妆喷雾持久控油保湿100ml</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="F616" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H616" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I616" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J616" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:11:33</t>
+        </is>
+      </c>
+      <c r="K616" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶面霜80g滋润</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】全新大红瓶面霜80g清爽版+15ml*4补水保湿滋润护肤品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F617" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G617" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H617" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I617" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J617" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:12:41</t>
+        </is>
+      </c>
+      <c r="K617" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="n">
+        <v>617</v>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶面霜80g滋润</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g*2滋润型补水保湿滋润舒缓紧致sk2护肤品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F618" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H618" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I618" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J618" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:12:57</t>
+        </is>
+      </c>
+      <c r="K618" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="n">
+        <v>618</v>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶面霜80g滋润</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F619" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G619" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H619" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I619" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J619" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:13:18</t>
+        </is>
+      </c>
+      <c r="K619" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶面霜80g滋润</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】新版大红瓶面霜80g清爽型抗皱紧致滋润保湿【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H620" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I620" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J620" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:13:39</t>
+        </is>
+      </c>
+      <c r="K620" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="n">
+        <v>620</v>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>Embryolisse 大宝妆前乳75ml 法国进口</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>【Embryolisse】旗舰店妆前乳隔离补水保湿法国进口深浅蓝</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>大宝</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr">
+        <is>
+          <t>大宝</t>
+        </is>
+      </c>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H621" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I621" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J621" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:14:48</t>
+        </is>
+      </c>
+      <c r="K621" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="n">
+        <v>621</v>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】石榴洁面乳125ml洗面奶清洁二合一保湿控油</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F622" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H622" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I622" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J622" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:15:53</t>
+        </is>
+      </c>
+      <c r="K622" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子精华（新版）75ml</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>两瓶 单品 SHISEIDO资生堂第四代红腰子精华75ml</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F623" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G623" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H623" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I623" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J623" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:17:03</t>
+        </is>
+      </c>
+      <c r="K623" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="n">
+        <v>623</v>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子精华（新版）75ml</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>资生堂红腰子精华液75ml四代补水保湿滋润维稳修护【5月30日发完】</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F624" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G624" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H624" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I624" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J624" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:17:20</t>
+        </is>
+      </c>
+      <c r="K624" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="n">
+        <v>624</v>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/ SHISEIDO时光大琉璃水（新版）170ml</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂时光琉璃御藏柔肤水170ml保湿滋润紧致肌肤爽肤水</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F625" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G625" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H625" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I625" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J625" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:18:30</t>
+        </is>
+      </c>
+      <c r="K625" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="n">
+        <v>625</v>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO悦薇大抗糖面霜（清爽）50ml</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂悦薇大抗糖滋润面霜50ml补水紧致智感紧塑焕白霜</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F626" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G626" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H626" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I626" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J626" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:19:37</t>
+        </is>
+      </c>
+      <c r="K626" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="n">
+        <v>626</v>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO琉璃晚霜15ml（新版）</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO御藏臻萃奢养时光修护滋养琉璃晚霜15ml滋养 保湿</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F627" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G627" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H627" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I627" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J627" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:20:59</t>
+        </is>
+      </c>
+      <c r="K627" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="n">
+        <v>627</v>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO琉璃晚霜15ml（新版）</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】SHISEIDO新款时光琉璃御藏臻萃奢养晚霜15ml紧致夜霜面霜</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F628" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G628" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H628" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I628" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J628" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:21:11</t>
+        </is>
+      </c>
+      <c r="K628" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="n">
+        <v>628</v>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO百优面霜50ml</t>
+        </is>
+      </c>
+      <c r="C629" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】百优精纯面霜50ml保湿滋润增弹紧致抗衰老乳霜</t>
+        </is>
+      </c>
+      <c r="D629" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F629" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G629" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H629" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I629" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J629" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:22:20</t>
+        </is>
+      </c>
+      <c r="K629" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO百优面霜50ml</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】百优精纯面霜50ml保湿滋润增弹紧致抗衰老抗皱乳霜</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F630" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G630" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H630" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I630" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J630" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:22:40</t>
+        </is>
+      </c>
+      <c r="K630" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="n">
+        <v>630</v>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>范思哲 爱罗斯爱神男士香水 50ml EDP</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>【范思哲】爱罗斯爱神之水男士香水 淡香 50ML Eros木质馥奇调</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>范思哲</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="inlineStr">
+        <is>
+          <t>范思哲</t>
+        </is>
+      </c>
+      <c r="F631" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G631" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H631" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I631" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J631" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:23:49</t>
+        </is>
+      </c>
+      <c r="K631" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="n">
+        <v>631</v>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>范思哲 爱罗斯爱神男士香水 50ml EDP</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>【520礼物】Versace范思哲爱罗斯爱神之水男士淡香水Eros木质正品</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>范思哲</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr">
+        <is>
+          <t>范思哲</t>
+        </is>
+      </c>
+      <c r="F632" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G632" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H632" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I632" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J632" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:24:07</t>
+        </is>
+      </c>
+      <c r="K632" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>范思哲 爱罗斯爱神男士香水 100ml EDP 简装</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>【VERSACE】范思哲爱罗斯男士淡香水香氛爱神之水100ml简装EDT</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>范思哲</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="inlineStr">
+        <is>
+          <t>范思哲</t>
+        </is>
+      </c>
+      <c r="F633" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G633" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H633" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I633" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J633" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:25:17</t>
+        </is>
+      </c>
+      <c r="K633" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="n">
+        <v>633</v>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>范思哲 爱罗斯爱神男士香水 100ml EDP 简装</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>【VERSACE】范思哲爱罗斯男士淡香水香氛爱神之水100ml简装EDT</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>范思哲</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="inlineStr">
+        <is>
+          <t>范思哲</t>
+        </is>
+      </c>
+      <c r="F634" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G634" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H634" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I634" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J634" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:25:36</t>
+        </is>
+      </c>
+      <c r="K634" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="n">
+        <v>634</v>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>burberry新伦敦男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C635" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】BURBERRY博柏利伦敦男士香水琥珀木质馥奇调EDT 50ml</t>
+        </is>
+      </c>
+      <c r="D635" s="2" t="inlineStr">
+        <is>
+          <t>巴宝莉</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="inlineStr">
+        <is>
+          <t>巴宝莉</t>
+        </is>
+      </c>
+      <c r="F635" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G635" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H635" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I635" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J635" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:26:47</t>
+        </is>
+      </c>
+      <c r="K635" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="n">
+        <v>635</v>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>burberry新伦敦男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>博柏利(BURBERRY)伦敦男士淡香水EDT 50ML</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>巴宝莉</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="inlineStr">
+        <is>
+          <t>巴宝莉</t>
+        </is>
+      </c>
+      <c r="F636" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G636" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H636" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I636" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J636" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:27:05</t>
+        </is>
+      </c>
+      <c r="K636" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="n">
+        <v>636</v>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>burberry新伦敦男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C637" s="2" t="inlineStr">
+        <is>
+          <t>【礼盒礼袋 】BURBERRY博柏利巴宝莉新伦敦男士EDT淡香水送人礼物</t>
+        </is>
+      </c>
+      <c r="D637" s="2" t="inlineStr">
+        <is>
+          <t>巴宝莉</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="inlineStr">
+        <is>
+          <t>巴宝莉</t>
+        </is>
+      </c>
+      <c r="F637" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G637" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H637" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I637" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J637" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:27:23</t>
+        </is>
+      </c>
+      <c r="K637" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="n">
+        <v>637</v>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>burberry新伦敦男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】博柏利伦敦男士淡香水50ml</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>巴宝莉</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="inlineStr">
+        <is>
+          <t>巴宝莉</t>
+        </is>
+      </c>
+      <c r="F638" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G638" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H638" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I638" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J638" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:27:44</t>
+        </is>
+      </c>
+      <c r="K638" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="n">
+        <v>638</v>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>Calvin Klein/CK卡尔文克雷恩 自由男士EDT 50/100ML</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="F639" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G639" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H639" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I639" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J639" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:28:56</t>
+        </is>
+      </c>
+      <c r="K639" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="n">
+        <v>639</v>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>【50mlCK肆意男士香水EDT50ml</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="F640" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G640" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H640" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I640" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J640" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:29:17</t>
+        </is>
+      </c>
+      <c r="K640" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="n">
+        <v>640</v>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>Calvin Klein/CK凯文克莱 自由男士香水 50/100ML</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="F641" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G641" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H641" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I641" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J641" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:29:33</t>
+        </is>
+      </c>
+      <c r="K641" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="inlineStr">
+        <is>
+          <t>【50mlCK Man超凡男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D642" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="F642" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G642" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H642" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I642" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J642" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:29:53</t>
+        </is>
+      </c>
+      <c r="K642" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="n">
+        <v>642</v>
+      </c>
+      <c r="B643" s="2" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C643" s="2" t="inlineStr">
+        <is>
+          <t>【正品】CALVIN KLEIN CK be 男士香水 木质香调 淡香水EDT</t>
+        </is>
+      </c>
+      <c r="D643" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="F643" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G643" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H643" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I643" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J643" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:30:07</t>
+        </is>
+      </c>
+      <c r="K643" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
+        </is>
+      </c>
+      <c r="C644" s="2" t="inlineStr">
+        <is>
+          <t>【香港直发】Calvin Klein绝色女士香氛香水 EDP100ml CK女士香水【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D644" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="F644" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G644" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H644" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I644" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J644" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:31:09</t>
+        </is>
+      </c>
+      <c r="K644" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="n">
+        <v>644</v>
+      </c>
+      <c r="B645" s="2" t="inlineStr">
+        <is>
+          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
+        </is>
+      </c>
+      <c r="C645" s="2" t="inlineStr">
+        <is>
+          <t>【100mlCK绝色美丽女士香水EDP黄色100ml简装无盖</t>
+        </is>
+      </c>
+      <c r="D645" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="F645" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G645" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H645" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I645" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J645" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:31:26</t>
+        </is>
+      </c>
+      <c r="K645" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="n">
+        <v>645</v>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
+        </is>
+      </c>
+      <c r="C646" s="2" t="inlineStr">
+        <is>
+          <t>Calvin Klein/CK凯文克莱 激情女士EDP香水 50/100ml</t>
+        </is>
+      </c>
+      <c r="D646" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="inlineStr">
+        <is>
+          <t>卡尔文克雷恩</t>
+        </is>
+      </c>
+      <c r="F646" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G646" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H646" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I646" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J646" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:31:45</t>
+        </is>
+      </c>
+      <c r="K646" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
+        <is>
+          <t>杜鲁萨迪 雅逸玫瑰女士香水 30ml EDT</t>
+        </is>
+      </c>
+      <c r="C647" s="2" t="inlineStr"/>
+      <c r="D647" s="2" t="inlineStr">
+        <is>
+          <t>杜鲁萨迪</t>
+        </is>
+      </c>
+      <c r="E647" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F647" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G647" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H647" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I647" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J647" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:45:51</t>
+        </is>
+      </c>
+      <c r="K647" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="n">
+        <v>647</v>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>杜鲁萨迪 雅逸玫瑰女士香水 30ml EDT</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>【香港直发】TRUSSARDI杜鲁萨迪优雅浪漫玫瑰淡香水EDT 100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D648" s="2" t="inlineStr">
+        <is>
+          <t>杜鲁萨迪</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="inlineStr">
+        <is>
+          <t>杜鲁萨迪</t>
+        </is>
+      </c>
+      <c r="F648" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G648" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H648" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I648" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J648" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:46:04</t>
+        </is>
+      </c>
+      <c r="K648" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>【大卫杜夫】冷水男士香水海洋调男士淡香水男生节日礼物75ml</t>
+        </is>
+      </c>
+      <c r="D649" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫</t>
+        </is>
+      </c>
+      <c r="E649" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫</t>
+        </is>
+      </c>
+      <c r="F649" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G649" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H649" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I649" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J649" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:47:09</t>
+        </is>
+      </c>
+      <c r="K649" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="n">
+        <v>649</v>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>【】大卫杜夫(Davidoff)冷水男士淡香水</t>
+        </is>
+      </c>
+      <c r="D650" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫</t>
+        </is>
+      </c>
+      <c r="E650" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫</t>
+        </is>
+      </c>
+      <c r="F650" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G650" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H650" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I650" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J650" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:47:27</t>
+        </is>
+      </c>
+      <c r="K650" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="n">
+        <v>650</v>
+      </c>
+      <c r="B651" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="C651" s="2" t="inlineStr">
+        <is>
+          <t>【Davidoff】大卫杜夫冷水男士淡香水EDT40/75/125ml</t>
+        </is>
+      </c>
+      <c r="D651" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫</t>
+        </is>
+      </c>
+      <c r="E651" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫</t>
+        </is>
+      </c>
+      <c r="F651" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G651" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H651" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I651" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J651" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:47:46</t>
+        </is>
+      </c>
+      <c r="K651" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="n">
+        <v>651</v>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>【大卫杜夫】冷水极致版香水喷雾 EDP 125ml/4.2oz【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D652" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫</t>
+        </is>
+      </c>
+      <c r="F652" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G652" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H652" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I652" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J652" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:47:58</t>
+        </is>
+      </c>
+      <c r="K652" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="n">
+        <v>652</v>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
+        <is>
+          <t>古驰 竹韵女士香水浓香型50ml</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰竹韵女士浓香水持久花香木质调EDP 50ml</t>
+        </is>
+      </c>
+      <c r="D653" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E653" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F653" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G653" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H653" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I653" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J653" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:49:20</t>
+        </is>
+      </c>
+      <c r="K653" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="n">
+        <v>653</v>
+      </c>
+      <c r="B654" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃眼霜 20ml</t>
+        </is>
+      </c>
+      <c r="C654" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】双萃精华眼霜20ml紧致淡化细纹</t>
+        </is>
+      </c>
+      <c r="D654" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F654" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G654" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H654" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I654" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J654" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:50:30</t>
+        </is>
+      </c>
+      <c r="K654" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="n">
+        <v>654</v>
+      </c>
+      <c r="B655" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃眼霜 20ml</t>
+        </is>
+      </c>
+      <c r="C655" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】双萃精华眼霜20ml紧致淡化细纹</t>
+        </is>
+      </c>
+      <c r="D655" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E655" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F655" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G655" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H655" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I655" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J655" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:50:46</t>
+        </is>
+      </c>
+      <c r="K655" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="n">
+        <v>655</v>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销135.3万+件】新版娇韵诗第九代黄金双萃精华100ml滋润补水抗氧紧致修护护肤</t>
+        </is>
+      </c>
+      <c r="D656" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F656" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G656" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H656" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I656" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J656" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:52:06</t>
+        </is>
+      </c>
+      <c r="K656" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="n">
+        <v>656</v>
+      </c>
+      <c r="B657" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="C657" s="2" t="inlineStr">
+        <is>
+          <t>新版娇韵诗第九代黄金双萃精华100ml滋润补水抗氧</t>
+        </is>
+      </c>
+      <c r="D657" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E657" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F657" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G657" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H657" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I657" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J657" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:52:20</t>
+        </is>
+      </c>
+      <c r="K657" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="n">
+        <v>657</v>
+      </c>
+      <c r="B658" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="C658" s="2" t="inlineStr">
+        <is>
+          <t>【正品现货】CLARINS娇韵诗新版第九代黄金双萃精华75ml无盒自用</t>
+        </is>
+      </c>
+      <c r="D658" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E658" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F658" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G658" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H658" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I658" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J658" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:52:36</t>
+        </is>
+      </c>
+      <c r="K658" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="B659" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="C659" s="2" t="inlineStr">
+        <is>
+          <t>第九代娇韵诗双萃精华液紧致抗皱熬夜修护面部精华护肤轻盈清爽</t>
+        </is>
+      </c>
+      <c r="D659" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E659" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F659" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G659" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H659" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I659" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J659" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:52:50</t>
+        </is>
+      </c>
+      <c r="K659" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="B660" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="C660" s="2" t="inlineStr">
+        <is>
+          <t>新版娇韵诗第九代黄金双萃精华100ml滋润补水抗氧</t>
+        </is>
+      </c>
+      <c r="D660" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E660" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F660" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G660" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H660" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I660" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J660" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:53:04</t>
+        </is>
+      </c>
+      <c r="K660" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="n">
+        <v>660</v>
+      </c>
+      <c r="B661" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 棉花籽洁面 125ml 新版</t>
+        </is>
+      </c>
+      <c r="C661" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗温和泡沫洁面棉花籽清洁保湿油皮125ml</t>
+        </is>
+      </c>
+      <c r="D661" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E661" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F661" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G661" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H661" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I661" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J661" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:08:43</t>
+        </is>
+      </c>
+      <c r="K661" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="n">
+        <v>661</v>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 棉花籽洁面 125ml 新版</t>
+        </is>
+      </c>
+      <c r="C662" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗温和泡沫洁面棉花籽清洁保湿油皮125ml</t>
+        </is>
+      </c>
+      <c r="D662" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E662" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F662" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G662" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H662" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I662" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J662" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:08:59</t>
+        </is>
+      </c>
+      <c r="K662" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="n">
+        <v>662</v>
+      </c>
+      <c r="B663" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 抚纹油 100ml</t>
+        </is>
+      </c>
+      <c r="C663" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗身体护理油抚纹油100ml提拉紧致淡纹滋养【5月28日发完】</t>
+        </is>
+      </c>
+      <c r="D663" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E663" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F663" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G663" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H663" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I663" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J663" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:10:13</t>
+        </is>
+      </c>
+      <c r="K663" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="n">
+        <v>663</v>
+      </c>
+      <c r="B664" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 抚纹油 100ml</t>
+        </is>
+      </c>
+      <c r="C664" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】自然调和身体护理油100ml紧致提拉淡纹滋润</t>
+        </is>
+      </c>
+      <c r="D664" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E664" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F664" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G664" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H664" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I664" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J664" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:10:32</t>
+        </is>
+      </c>
+      <c r="K664" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="n">
+        <v>664</v>
+      </c>
+      <c r="B665" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 抚纹油 100ml</t>
+        </is>
+      </c>
+      <c r="C665" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】 娇韵诗天然调和身体护理油 抚纹油 100ml</t>
+        </is>
+      </c>
+      <c r="D665" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E665" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F665" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G665" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H665" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I665" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J665" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:10:51</t>
+        </is>
+      </c>
+      <c r="K665" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="n">
+        <v>665</v>
+      </c>
+      <c r="B666" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="C666" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Clarins/娇韵诗双萃精华液紧致面部精华30ml轻盈版</t>
+        </is>
+      </c>
+      <c r="D666" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E666" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F666" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G666" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H666" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I666" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J666" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:12:00</t>
+        </is>
+      </c>
+      <c r="K666" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="n">
+        <v>666</v>
+      </c>
+      <c r="B667" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="C667" s="2" t="inlineStr">
+        <is>
+          <t>第九代娇韵诗双萃精华液紧致抗皱熬夜修护面部精华护肤轻盈清爽</t>
+        </is>
+      </c>
+      <c r="D667" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E667" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F667" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G667" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H667" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I667" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J667" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:12:15</t>
+        </is>
+      </c>
+      <c r="K667" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="n">
+        <v>667</v>
+      </c>
+      <c r="B668" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】第九代双萃精华液抗皱抗衰老紧致淡纹熬夜面部抗皱精华护肤【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D668" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E668" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F668" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G668" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H668" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I668" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J668" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:12:30</t>
+        </is>
+      </c>
+      <c r="K668" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="n">
+        <v>668</v>
+      </c>
+      <c r="B669" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="C669" s="2" t="inlineStr">
+        <is>
+          <t>新版 娇韵诗第九代双萃精华经典轻盈双效修护滋润焕亮熬夜精华</t>
+        </is>
+      </c>
+      <c r="D669" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E669" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F669" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G669" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H669" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I669" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J669" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:12:44</t>
+        </is>
+      </c>
+      <c r="K669" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="n">
+        <v>669</v>
+      </c>
+      <c r="B670" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹樱花护手霜三支装</t>
+        </is>
+      </c>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>Loccitane 欧舒丹 甜蜜樱花护手霜30ml(新款)</t>
+        </is>
+      </c>
+      <c r="D670" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="E670" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="F670" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G670" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H670" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I670" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J670" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:13:51</t>
+        </is>
+      </c>
+      <c r="K670" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="B671" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="C671" s="2" t="inlineStr">
+        <is>
+          <t>法国L'OCCITANE欧舒丹嫩肤沐浴露身体乳全系列</t>
+        </is>
+      </c>
+      <c r="D671" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="E671" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="F671" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G671" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H671" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I671" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J671" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:15:07</t>
+        </is>
+      </c>
+      <c r="K671" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="n">
+        <v>671</v>
+      </c>
+      <c r="B672" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>【国内直售】欧舒丹身体乳乳木果身体润肤露滋润保湿250ml滋润</t>
+        </is>
+      </c>
+      <c r="D672" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="E672" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="F672" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G672" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H672" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I672" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J672" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:15:19</t>
+        </is>
+      </c>
+      <c r="K672" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="n">
+        <v>672</v>
+      </c>
+      <c r="B673" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="C673" s="2" t="inlineStr">
+        <is>
+          <t>【特价】欧舒丹乳木果身体润肤露250ML 滋润保湿身体乳</t>
+        </is>
+      </c>
+      <c r="D673" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="E673" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="F673" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G673" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H673" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I673" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J673" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:15:31</t>
+        </is>
+      </c>
+      <c r="K673" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>【国内直售】欧舒丹乳木果身体润肤露滋润保湿身体乳250ml滋润</t>
+        </is>
+      </c>
+      <c r="D674" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="E674" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="F674" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G674" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H674" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I674" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J674" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:15:44</t>
+        </is>
+      </c>
+      <c r="K674" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="n">
+        <v>674</v>
+      </c>
+      <c r="B675" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="C675" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳丰凝润肤露250ml舒缓滋润保湿补水正品【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="D675" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="E675" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="F675" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G675" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H675" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I675" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J675" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:15:59</t>
+        </is>
+      </c>
+      <c r="K675" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="n">
+        <v>675</v>
+      </c>
+      <c r="B676" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="inlineStr">
+        <is>
+          <t>【正品保证】欧舒丹乳木果身体乳250ml润肤露补水保湿滋润保湿霜</t>
+        </is>
+      </c>
+      <c r="D676" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="E676" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="F676" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G676" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H676" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I676" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J676" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:16:12</t>
+        </is>
+      </c>
+      <c r="K676" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="n">
+        <v>676</v>
+      </c>
+      <c r="B677" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹玫瑰身体乳250ml</t>
+        </is>
+      </c>
+      <c r="C677" s="2" t="inlineStr">
+        <is>
+          <t>Loccitane 欧舒丹 瑰香之心身体乳250ml 第二代新款</t>
+        </is>
+      </c>
+      <c r="D677" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="E677" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹</t>
+        </is>
+      </c>
+      <c r="F677" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G677" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H677" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I677" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J677" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:17:21</t>
+        </is>
+      </c>
+      <c r="K677" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="n">
+        <v>677</v>
+      </c>
+      <c r="B678" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜洁面125ml</t>
+        </is>
+      </c>
+      <c r="C678" s="2" t="inlineStr">
+        <is>
+          <t>【海蓝之谜】洁面125ml清洁焕亮洗面奶</t>
+        </is>
+      </c>
+      <c r="D678" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="E678" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="F678" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G678" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H678" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I678" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J678" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:18:31</t>
+        </is>
+      </c>
+      <c r="K678" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="n">
+        <v>678</v>
+      </c>
+      <c r="B679" s="2" t="inlineStr">
+        <is>
+          <t>CPB滋润洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="C679" s="2" t="inlineStr">
+        <is>
+          <t>【 正品行货】CPB/肌肤之钥洗面奶125ml光凝润采妆前隔离37ml</t>
+        </is>
+      </c>
+      <c r="D679" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E679" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F679" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G679" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H679" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I679" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J679" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:19:39</t>
+        </is>
+      </c>
+      <c r="K679" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="B680" s="2" t="inlineStr">
+        <is>
+          <t>CPB滋润洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="C680" s="2" t="inlineStr">
+        <is>
+          <t>【CPB】肌肤之钥光采洁面膏洗面奶滋润版125ml</t>
+        </is>
+      </c>
+      <c r="D680" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E680" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F680" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G680" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H680" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I680" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J680" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:19:58</t>
+        </is>
+      </c>
+      <c r="K680" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="n">
+        <v>680</v>
+      </c>
+      <c r="B681" s="2" t="inlineStr">
+        <is>
+          <t>CPB滋润洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="C681" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】肌肤之钥净采洁面膏125ml*2清爽型/湿润型补水保湿</t>
+        </is>
+      </c>
+      <c r="D681" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E681" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F681" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G681" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H681" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I681" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J681" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:20:15</t>
+        </is>
+      </c>
+      <c r="K681" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="n">
+        <v>681</v>
+      </c>
+      <c r="B682" s="2" t="inlineStr">
+        <is>
+          <t>CPB美白短管隔离30ml</t>
+        </is>
+      </c>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>【CPB】 肌肤之钥 白短管隔离30ml SPF38 高倍防晒</t>
+        </is>
+      </c>
+      <c r="D682" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E682" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F682" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G682" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H682" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I682" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J682" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:21:22</t>
+        </is>
+      </c>
+      <c r="K682" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="n">
+        <v>682</v>
+      </c>
+      <c r="B683" s="2" t="inlineStr">
+        <is>
+          <t>CPB美白短管隔离30ml</t>
+        </is>
+      </c>
+      <c r="C683" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】CPB肌肤之钥光透白焕采妆前乳防晒短管白隔离 30ml</t>
+        </is>
+      </c>
+      <c r="D683" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E683" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F683" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G683" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H683" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I683" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J683" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:21:40</t>
+        </is>
+      </c>
+      <c r="K683" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="n">
+        <v>683</v>
+      </c>
+      <c r="B684" s="2" t="inlineStr">
+        <is>
+          <t>FERRERO ROCHER 费列罗榛果巧克力制品T30</t>
+        </is>
+      </c>
+      <c r="C684" s="2" t="inlineStr">
+        <is>
+          <t>【费列罗】巧克力40粒礼盒装榛果威化金球结婚礼喜糖伴手礼情人节礼物</t>
+        </is>
+      </c>
+      <c r="D684" s="2" t="inlineStr">
+        <is>
+          <t>费列罗</t>
+        </is>
+      </c>
+      <c r="E684" s="2" t="inlineStr">
+        <is>
+          <t>费列罗</t>
+        </is>
+      </c>
+      <c r="F684" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G684" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H684" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I684" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J684" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:23:03</t>
+        </is>
+      </c>
+      <c r="K684" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=20.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="n">
+        <v>684</v>
+      </c>
+      <c r="B685" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
+        </is>
+      </c>
+      <c r="C685" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder雅诗兰黛红石榴光采能量保湿霜日霜旧版50ml</t>
+        </is>
+      </c>
+      <c r="D685" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E685" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F685" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G685" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H685" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I685" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J685" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:24:13</t>
+        </is>
+      </c>
+      <c r="K685" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="B686" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
+        </is>
+      </c>
+      <c r="C686" s="2" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER雅诗兰黛】红石榴面霜 鲜活亮采日霜50ml保湿补水</t>
+        </is>
+      </c>
+      <c r="D686" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E686" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F686" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G686" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H686" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I686" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J686" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:24:33</t>
+        </is>
+      </c>
+      <c r="K686" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="n">
+        <v>686</v>
+      </c>
+      <c r="B687" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
+        </is>
+      </c>
+      <c r="C687" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴精华面霜 提亮滋润淡化高保湿补水修护50ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D687" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E687" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F687" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G687" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H687" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I687" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J687" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:24:49</t>
+        </is>
+      </c>
+      <c r="K687" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="n">
+        <v>687</v>
+      </c>
+      <c r="B688" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
+        </is>
+      </c>
+      <c r="C688" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴面霜 晚霜50ml 抗氧化提亮肤色高保湿补水滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D688" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E688" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F688" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G688" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H688" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I688" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J688" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:25:03</t>
+        </is>
+      </c>
+      <c r="K688" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="n">
+        <v>688</v>
+      </c>
+      <c r="B689" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰爱心黑管唇釉620</t>
+        </is>
+      </c>
+      <c r="C689" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心七夕浮雕黑管唇釉610 620 442 443</t>
+        </is>
+      </c>
+      <c r="D689" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E689" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F689" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G689" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H689" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I689" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J689" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:26:15</t>
+        </is>
+      </c>
+      <c r="K689" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="n">
+        <v>689</v>
+      </c>
+      <c r="B690" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰爱心黑管唇釉620</t>
+        </is>
+      </c>
+      <c r="C690" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰爱心唇釉442 443 620限定浮雕黑管5.5ml</t>
+        </is>
+      </c>
+      <c r="D690" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E690" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F690" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G690" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H690" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I690" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J690" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:26:38</t>
+        </is>
+      </c>
+      <c r="K690" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="B691" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰黑色皮革气垫B10</t>
+        </is>
+      </c>
+      <c r="C691" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰黑皮革气垫羽毛B10白皮B20自然肤色遮瑕</t>
+        </is>
+      </c>
+      <c r="D691" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E691" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F691" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G691" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H691" s="3" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I691" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J691" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:27:49</t>
+        </is>
+      </c>
+      <c r="K691" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="n">
+        <v>691</v>
+      </c>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰黑色皮革气垫B10</t>
+        </is>
+      </c>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰黑皮革气垫b10# B20# 14g 混油挚爱细腻服帖自然无瑕</t>
+        </is>
+      </c>
+      <c r="D692" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E692" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F692" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G692" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H692" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I692" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J692" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:28:10</t>
+        </is>
+      </c>
+      <c r="K692" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="n">
+        <v>692</v>
+      </c>
+      <c r="B693" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯粉底液100</t>
+        </is>
+      </c>
+      <c r="C693" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻新菁纯粉底液均匀肤色隐形毛孔保湿持妆长效持妆</t>
+        </is>
+      </c>
+      <c r="D693" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E693" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F693" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G693" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H693" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I693" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J693" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:30:30</t>
+        </is>
+      </c>
+      <c r="K693" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="n">
+        <v>693</v>
+      </c>
+      <c r="B694" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯粉底液100</t>
+        </is>
+      </c>
+      <c r="C694" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻菁纯臻颜精华粉底液100#/110#35ml 新版礼物送人</t>
+        </is>
+      </c>
+      <c r="D694" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E694" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F694" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G694" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H694" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I694" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J694" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:30:51</t>
+        </is>
+      </c>
+      <c r="K694" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="n">
+        <v>694</v>
+      </c>
+      <c r="B695" s="2" t="inlineStr">
+        <is>
+          <t>SK2骨胶原乳液100g</t>
+        </is>
+      </c>
+      <c r="C695" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II骨胶原晶致活肤修护乳液补水保湿抗皱紧致舒缓</t>
+        </is>
+      </c>
+      <c r="D695" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E695" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F695" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G695" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H695" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I695" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J695" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:32:00</t>
+        </is>
+      </c>
+      <c r="K695" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="n">
+        <v>695</v>
+      </c>
+      <c r="B696" s="2" t="inlineStr">
+        <is>
+          <t>SK2骨胶原乳液100g</t>
+        </is>
+      </c>
+      <c r="C696" s="2" t="inlineStr">
+        <is>
+          <t>SK2晶致美肤乳液100g 骨胶原修护紧致活肤 保湿不油腻【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D696" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E696" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F696" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G696" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H696" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I696" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J696" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:32:16</t>
+        </is>
+      </c>
+      <c r="K696" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="n">
+        <v>696</v>
+      </c>
+      <c r="B697" s="2" t="inlineStr">
+        <is>
+          <t>SK2骨胶原乳液100g</t>
+        </is>
+      </c>
+      <c r="C697" s="2" t="inlineStr">
+        <is>
+          <t>SK-II/SK2 晶致活肤骨胶原乳液100g(无盒/不满瓶)【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D697" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E697" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F697" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G697" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H697" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I697" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J697" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:32:28</t>
+        </is>
+      </c>
+      <c r="K697" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="n">
+        <v>697</v>
+      </c>
+      <c r="B698" s="2" t="inlineStr">
+        <is>
+          <t>SK2骨胶原乳液100g</t>
+        </is>
+      </c>
+      <c r="C698" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】 晶致美肤乳液100ml 骨胶原修护活肤乳液紧致提亮保湿抗皱</t>
+        </is>
+      </c>
+      <c r="D698" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E698" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F698" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G698" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H698" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I698" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J698" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:32:42</t>
+        </is>
+      </c>
+      <c r="K698" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="B699" s="2" t="inlineStr">
+        <is>
+          <t>SK2清莹露230ml</t>
+        </is>
+      </c>
+      <c r="C699" s="2" t="inlineStr">
+        <is>
+          <t>首件19.12大促直降36.2元总售1319件</t>
+        </is>
+      </c>
+      <c r="D699" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E699" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F699" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G699" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H699" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I699" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J699" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:34:23</t>
+        </is>
+      </c>
+      <c r="K699" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>SK2清莹露230ml</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="inlineStr">
+        <is>
+          <t>【2.13万人评价品牌正品】SK-II/sk2护肤精华露嫩肤清莹露保湿修护抗皱紧致嫩滑230ml化妆水</t>
+        </is>
+      </c>
+      <c r="D700" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E700" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F700" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G700" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H700" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I700" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J700" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:34:43</t>
+        </is>
+      </c>
+      <c r="K700" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="B701" s="2" t="inlineStr">
+        <is>
+          <t>SK2立体修护眼霜15g两瓶装</t>
+        </is>
+      </c>
+      <c r="C701" s="2" t="inlineStr">
+        <is>
+          <t>【专柜行货】SK-II sk2大红瓶微肌因修护焕彩大眼眼霜15g</t>
+        </is>
+      </c>
+      <c r="D701" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E701" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F701" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G701" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H701" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I701" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J701" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:36:03</t>
+        </is>
+      </c>
+      <c r="K701" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="n">
+        <v>701</v>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>SK2立体修护眼霜15g两瓶装</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶眼霜15g赋能焕采大眼眼霜sk2提拉紧致抗皱淡纹正品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D702" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E702" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F702" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G702" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H702" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I702" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J702" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:36:17</t>
+        </is>
+      </c>
+      <c r="K702" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="B703" s="2" t="inlineStr">
+        <is>
+          <t>SK2小灯泡50ml两瓶装（25年款）</t>
+        </is>
+      </c>
+      <c r="C703" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】小灯泡精华50ml#无盒提亮肤色sk2淡斑美白修护面部精华液【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D703" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E703" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F703" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G703" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H703" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I703" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J703" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:37:33</t>
+        </is>
+      </c>
+      <c r="K703" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="n">
+        <v>703</v>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>SK2小灯泡50ml两瓶装（25年款）</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】小灯泡精华50ml美白光蕴臻采焕亮精华露sk2紧致淡纹正品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D704" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E704" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F704" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G704" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H704" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I704" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J704" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:37:44</t>
+        </is>
+      </c>
+      <c r="K704" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="B705" s="2" t="inlineStr">
+        <is>
+          <t>碧欧泉男士水动力乳液100ml</t>
+        </is>
+      </c>
+      <c r="C705" s="2" t="inlineStr">
+        <is>
+          <t>【碧欧泉】男士水动力保湿乳液100ml清爽提亮修护礼物【520礼物】</t>
+        </is>
+      </c>
+      <c r="D705" s="2" t="inlineStr">
+        <is>
+          <t>碧欧泉</t>
+        </is>
+      </c>
+      <c r="E705" s="2" t="inlineStr">
+        <is>
+          <t>碧欧泉</t>
+        </is>
+      </c>
+      <c r="F705" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G705" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H705" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I705" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J705" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:39:29</t>
+        </is>
+      </c>
+      <c r="K705" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="n">
+        <v>705</v>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油450ml两瓶装</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="inlineStr">
+        <is>
+          <t>【植村秀】绿茶新肌卸妆油450ml温和保湿深层清洁清透毛孔经典洁颜油【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D706" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="E706" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="F706" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G706" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H706" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I706" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J706" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:40:35</t>
+        </is>
+      </c>
+      <c r="K706" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="B707" s="2" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油450ml两瓶装</t>
+        </is>
+      </c>
+      <c r="C707" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀绿茶卸妆洁颜油  温和深层清洁彩妆保湿450ml</t>
+        </is>
+      </c>
+      <c r="D707" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="E707" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="F707" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G707" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H707" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I707" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J707" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:40:50</t>
+        </is>
+      </c>
+      <c r="K707" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="n">
+        <v>707</v>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰女神逆龄粉底液B20</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评229.4万+条】YSL/圣罗兰逆龄女神粉底液#B20持妆遮瑕控油节日礼物</t>
+        </is>
+      </c>
+      <c r="D708" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E708" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F708" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G708" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H708" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I708" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J708" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:42:01</t>
+        </is>
+      </c>
+      <c r="K708" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="B709" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰女神逆龄粉底液B20</t>
+        </is>
+      </c>
+      <c r="C709" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰逆龄女神粉底液恒久B20#遮瑕轻薄控油30ml</t>
+        </is>
+      </c>
+      <c r="D709" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E709" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F709" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G709" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H709" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I709" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J709" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:42:19</t>
+        </is>
+      </c>
+      <c r="K709" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="n">
+        <v>709</v>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯眼霜20ml两瓶装</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>LANCOME/兰蔻新版菁纯眼霜20ml滋润淡眼纹黑眼圈提拉紧致眼周【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E710" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F710" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G710" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H710" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I710" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J710" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:26</t>
+        </is>
+      </c>
+      <c r="K710" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="n">
+        <v>710</v>
+      </c>
+      <c r="B711" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻第三代肌底液100ml</t>
+        </is>
+      </c>
+      <c r="C711" s="2" t="inlineStr"/>
+      <c r="D711" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E711" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F711" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G711" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H711" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I711" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J711" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:44:33</t>
+        </is>
+      </c>
+      <c r="K711" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="n">
+        <v>711</v>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻第三代肌底液100ml</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】小黑瓶第三代肌底液精华水75ml/100ml</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E712" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F712" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G712" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H712" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I712" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J712" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:44:54</t>
+        </is>
+      </c>
+      <c r="K712" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="n">
+        <v>712</v>
+      </c>
+      <c r="B713" s="2" t="inlineStr">
+        <is>
+          <t>衰败城市牛郎眼影</t>
+        </is>
+      </c>
+      <c r="C713" s="2" t="inlineStr">
+        <is>
+          <t>Urban Decay 牛郎衰败城市ud牛郎眼影单色眼影打底经典牛郎 爆闪【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="D713" s="2" t="inlineStr">
+        <is>
+          <t>衰败城市</t>
+        </is>
+      </c>
+      <c r="E713" s="2" t="inlineStr">
+        <is>
+          <t>衰败城市</t>
+        </is>
+      </c>
+      <c r="F713" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G713" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H713" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I713" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J713" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:46:14</t>
+        </is>
+      </c>
+      <c r="K713" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="n">
+        <v>713</v>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t>衰败城市牛郎眼影</t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="inlineStr"/>
+      <c r="D714" s="2" t="inlineStr">
+        <is>
+          <t>衰败城市</t>
+        </is>
+      </c>
+      <c r="E714" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F714" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G714" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H714" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I714" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J714" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:46:31</t>
+        </is>
+      </c>
+      <c r="K714" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="n">
+        <v>714</v>
+      </c>
+      <c r="B715" s="2" t="inlineStr">
+        <is>
+          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
+        </is>
+      </c>
+      <c r="C715" s="2" t="inlineStr">
+        <is>
+          <t>【娇兰】第三代帝皇蜂姿复原蜜精华液50ml黄金保湿抗氧提亮</t>
+        </is>
+      </c>
+      <c r="D715" s="2" t="inlineStr">
+        <is>
+          <t>娇兰</t>
+        </is>
+      </c>
+      <c r="E715" s="2" t="inlineStr">
+        <is>
+          <t>娇兰</t>
+        </is>
+      </c>
+      <c r="F715" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G715" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H715" s="3" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="I715" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J715" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:47:36</t>
+        </is>
+      </c>
+      <c r="K715" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>【娇兰】第三代帝皇蜂姿复原蜜精华液50ml黄金保湿抗氧提亮</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="inlineStr">
+        <is>
+          <t>娇兰</t>
+        </is>
+      </c>
+      <c r="E716" s="2" t="inlineStr">
+        <is>
+          <t>娇兰</t>
+        </is>
+      </c>
+      <c r="F716" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G716" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H716" s="3" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="I716" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J716" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:48:43</t>
+        </is>
+      </c>
+      <c r="K716" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="n">
+        <v>716</v>
+      </c>
+      <c r="B717" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="C717" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕大地男士淡香水50ml经典淡香木质调正装男士香水</t>
+        </is>
+      </c>
+      <c r="D717" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="E717" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="F717" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G717" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H717" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I717" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J717" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:49:52</t>
+        </is>
+      </c>
+      <c r="K717" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="n">
+        <v>717</v>
+      </c>
+      <c r="B718" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="C718" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕大地男士淡香水50ml正装有盒木质调</t>
+        </is>
+      </c>
+      <c r="D718" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="E718" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="F718" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G718" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H718" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I718" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J718" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:50:11</t>
+        </is>
+      </c>
+      <c r="K718" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="n">
+        <v>718</v>
+      </c>
+      <c r="B719" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="C719" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕大地男士淡香水50ml经典中性馥郁清新持久留香</t>
+        </is>
+      </c>
+      <c r="D719" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="E719" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="F719" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G719" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H719" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I719" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J719" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:50:29</t>
+        </is>
+      </c>
+      <c r="K719" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="n">
+        <v>719</v>
+      </c>
+      <c r="B720" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="C720" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销59.6万+件】爱马仕(HERMES)大地男士淡香水EDT 30/50/100ML</t>
+        </is>
+      </c>
+      <c r="D720" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="E720" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="F720" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G720" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H720" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I720" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J720" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:50:47</t>
+        </is>
+      </c>
+      <c r="K720" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="B721" s="2" t="inlineStr">
+        <is>
+          <t>苏秘气垫1号</t>
+        </is>
+      </c>
+      <c r="C721" s="2" t="inlineStr"/>
+      <c r="D721" s="2" t="inlineStr">
+        <is>
+          <t>苏秘</t>
+        </is>
+      </c>
+      <c r="E721" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F721" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G721" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H721" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I721" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J721" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:52:00</t>
+        </is>
+      </c>
+      <c r="K721" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="n">
+        <v>721</v>
+      </c>
+      <c r="B722" s="2" t="inlineStr">
+        <is>
+          <t>苏秘气垫1号</t>
+        </is>
+      </c>
+      <c r="C722" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销14.3万+件】韩国SUM37°苏秘惊喜气垫BB霜粉底液提亮防晒清透1号色</t>
+        </is>
+      </c>
+      <c r="D722" s="2" t="inlineStr">
+        <is>
+          <t>苏秘</t>
+        </is>
+      </c>
+      <c r="E722" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗</t>
+        </is>
+      </c>
+      <c r="F722" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G722" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H722" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I722" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J722" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:52:20</t>
+        </is>
+      </c>
+      <c r="K722" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="B723" s="2" t="inlineStr">
+        <is>
+          <t>苏秘气垫1号</t>
+        </is>
+      </c>
+      <c r="C723" s="2" t="inlineStr">
+        <is>
+          <t>【苏秘】惊喜气垫粉底液CC霜01号色水感妆效提亮防晒遮瑕</t>
+        </is>
+      </c>
+      <c r="D723" s="2" t="inlineStr">
+        <is>
+          <t>苏秘</t>
+        </is>
+      </c>
+      <c r="E723" s="2" t="inlineStr">
+        <is>
+          <t>苏秘</t>
+        </is>
+      </c>
+      <c r="F723" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G723" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H723" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I723" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J723" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:52:37</t>
+        </is>
+      </c>
+      <c r="K723" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="n">
+        <v>723</v>
+      </c>
+      <c r="B724" s="2" t="inlineStr">
+        <is>
+          <t>苏秘气垫1号</t>
+        </is>
+      </c>
+      <c r="C724" s="2" t="inlineStr">
+        <is>
+          <t>苏秘呼吸孕妇气垫bb霜遮瑕防晒保湿控油提亮镁白轻透气垫BS</t>
+        </is>
+      </c>
+      <c r="D724" s="2" t="inlineStr">
+        <is>
+          <t>苏秘</t>
+        </is>
+      </c>
+      <c r="E724" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗</t>
+        </is>
+      </c>
+      <c r="F724" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G724" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H724" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I724" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J724" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:52:52</t>
+        </is>
+      </c>
+      <c r="K724" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="B725" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 鲜活亮采红石榴倍润水 200ml</t>
+        </is>
+      </c>
+      <c r="C725" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴水200ml滋润型 鲜活亮采精华水 补水保湿抗氧提亮</t>
+        </is>
+      </c>
+      <c r="D725" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E725" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F725" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G725" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H725" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I725" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J725" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:54:02</t>
+        </is>
+      </c>
+      <c r="K725" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="n">
+        <v>725</v>
+      </c>
+      <c r="B726" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰夜皇后50ml</t>
+        </is>
+      </c>
+      <c r="C726" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰夜皇后面霜50ml轻盈版舒缓淡纹节日礼物</t>
+        </is>
+      </c>
+      <c r="D726" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E726" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F726" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G726" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H726" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I726" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J726" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:55:13</t>
+        </is>
+      </c>
+      <c r="K726" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="n">
+        <v>726</v>
+      </c>
+      <c r="B727" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+        </is>
+      </c>
+      <c r="C727" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰Al Hours 粉盖恒久干皮滋润粉底液LC1 LN4</t>
+        </is>
+      </c>
+      <c r="D727" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E727" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F727" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G727" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H727" s="3" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I727" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J727" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:25</t>
+        </is>
+      </c>
+      <c r="K727" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="n">
+        <v>727</v>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+        </is>
+      </c>
+      <c r="C728" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰Al Hours 粉盖恒久干皮滋润粉底液LC1 LN4</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E728" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F728" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G728" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H728" s="3" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I728" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J728" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:39</t>
+        </is>
+      </c>
+      <c r="K728" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="n">
+        <v>728</v>
+      </c>
+      <c r="B729" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+        </is>
+      </c>
+      <c r="C729" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰恒久粉底液LC1粉盖干皮挚爱超薄雾面长久持妆控油25ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D729" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E729" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F729" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G729" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H729" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I729" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J729" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:51</t>
+        </is>
+      </c>
+      <c r="K729" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="n">
+        <v>729</v>
+      </c>
+      <c r="B730" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+        </is>
+      </c>
+      <c r="C730" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL粉底液恒久贴肤衣 遮瑕哑光粉盖LC1 LC2 LN4正品</t>
+        </is>
+      </c>
+      <c r="D730" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E730" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F730" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G730" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H730" s="3" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I730" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J730" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:57:03</t>
+        </is>
+      </c>
+      <c r="K730" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="n">
+        <v>730</v>
+      </c>
+      <c r="B731" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+        </is>
+      </c>
+      <c r="C731" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰粉盖恒久大牌滋润粉底液LC1 LC2滋润正品</t>
+        </is>
+      </c>
+      <c r="D731" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E731" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F731" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G731" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H731" s="3" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="I731" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J731" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:12</t>
+        </is>
+      </c>
+      <c r="K731" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="n">
+        <v>731</v>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="inlineStr">
+        <is>
+          <t>【520礼物】YSL/圣罗兰粉盖恒久大牌滋润粉底液LC1 LC2滋润型正品</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E732" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F732" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G732" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H732" s="3" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="I732" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J732" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:23</t>
+        </is>
+      </c>
+      <c r="K732" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="n">
+        <v>732</v>
+      </c>
+      <c r="B733" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+        </is>
+      </c>
+      <c r="C733" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰25年新款贴肤衣粉底液 混干持妆服帖遮瑕粉盖LC1/LC2【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D733" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E733" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F733" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G733" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H733" s="3" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="I733" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J733" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:39</t>
+        </is>
+      </c>
+      <c r="K733" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>【520礼物】YSL/圣罗兰粉盖恒久大牌滋润粉底液LC1 LC2滋润正品</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E734" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F734" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G734" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H734" s="3" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="I734" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J734" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+      <c r="K734" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="n">
+        <v>734</v>
+      </c>
+      <c r="B735" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻小白管轻适水漾防晒乳 50ml*2</t>
+        </is>
+      </c>
+      <c r="C735" s="2" t="inlineStr">
+        <is>
+          <t>【】两支 单品 兰蔻新版小白管轻透水漾防晒乳50ml</t>
+        </is>
+      </c>
+      <c r="D735" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E735" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F735" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G735" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H735" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I735" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J735" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:00:02</t>
+        </is>
+      </c>
+      <c r="K735" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="n">
+        <v>735</v>
+      </c>
+      <c r="B736" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+        </is>
+      </c>
+      <c r="C736" s="2" t="inlineStr">
+        <is>
+          <t>【圣罗兰】明彩粉光轻垫粉底液 BR20 #12g 正装粉气垫粉皮革 遮瑕细腻</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E736" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F736" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G736" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H736" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I736" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J736" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:01:15</t>
+        </is>
+      </c>
+      <c r="K736" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="B737" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+        </is>
+      </c>
+      <c r="C737" s="2" t="inlineStr">
+        <is>
+          <t>正品行货 YSL圣罗兰粉气垫B10/B20遮瑕保湿持久养肤干皮挚爱轻薄</t>
+        </is>
+      </c>
+      <c r="D737" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E737" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F737" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G737" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H737" s="3" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="I737" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J737" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:01:43</t>
+        </is>
+      </c>
+      <c r="K737" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=21.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="n">
+        <v>737</v>
+      </c>
+      <c r="B738" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+        </is>
+      </c>
+      <c r="C738" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰明彩轻垫粉底液B20 5g 皮气垫 遮瑕提亮 轻薄持妆</t>
+        </is>
+      </c>
+      <c r="D738" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E738" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F738" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G738" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H738" s="3" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="I738" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J738" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:01:58</t>
+        </is>
+      </c>
+      <c r="K738" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="n">
+        <v>738</v>
+      </c>
+      <c r="B739" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+        </is>
+      </c>
+      <c r="C739" s="2" t="inlineStr">
+        <is>
+          <t>【清仓特价】圣罗兰明彩气垫轻垫粉底液黑皮革B20#5g 提亮肤色</t>
+        </is>
+      </c>
+      <c r="D739" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E739" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F739" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G739" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H739" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I739" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J739" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:02:11</t>
+        </is>
+      </c>
+      <c r="K739" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="n">
+        <v>739</v>
+      </c>
+      <c r="B740" s="2" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子防晒50ml对装</t>
+        </is>
+      </c>
+      <c r="C740" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销429.9万+件】2支资生堂新版蓝胖子防晒霜50ml隔离防紫外线</t>
+        </is>
+      </c>
+      <c r="D740" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E740" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F740" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G740" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H740" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I740" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J740" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:04:58</t>
+        </is>
+      </c>
+      <c r="K740" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="B741" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="C741" s="2" t="inlineStr">
+        <is>
+          <t>【2.15万人评价品牌正品】Armani 阿玛尼权力PRO粉底液1.5号/2号色红标遮瑕控油滋润</t>
+        </is>
+      </c>
+      <c r="D741" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E741" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F741" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G741" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H741" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I741" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J741" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:06:10</t>
+        </is>
+      </c>
+      <c r="K741" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="n">
+        <v>741</v>
+      </c>
+      <c r="B742" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="C742" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】权力持久丝绒哑光粉底液#1.5#30ML红标权力PRO混油</t>
+        </is>
+      </c>
+      <c r="D742" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E742" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F742" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G742" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H742" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I742" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J742" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:06:30</t>
+        </is>
+      </c>
+      <c r="K742" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="n">
+        <v>742</v>
+      </c>
+      <c r="B743" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="C743" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼新款权力PRO权利1.5粉底液(亚洲人混油皮挚爱)</t>
+        </is>
+      </c>
+      <c r="D743" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E743" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F743" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G743" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H743" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I743" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J743" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:06:46</t>
+        </is>
+      </c>
+      <c r="K743" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="n">
+        <v>743</v>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼权力粉底液1.5#权利PRO粉底液1.6# 2# 30ml</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E744" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F744" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G744" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H744" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I744" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J744" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:07:01</t>
+        </is>
+      </c>
+      <c r="K744" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="n">
+        <v>744</v>
+      </c>
+      <c r="B745" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻小黑瓶眼霜20ml</t>
+        </is>
+      </c>
+      <c r="C745" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】肌底焕活修护眼霜20ml超修小黑瓶发光眼霜淡化细纹抗氧化修护</t>
+        </is>
+      </c>
+      <c r="D745" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E745" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F745" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G745" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H745" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I745" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J745" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:08:09</t>
+        </is>
+      </c>
+      <c r="K745" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="n">
+        <v>745</v>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻小黑瓶眼霜20ml</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻小黑瓶发光眼霜20m淡眼圈细纹</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E746" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F746" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G746" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H746" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I746" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J746" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:08:27</t>
+        </is>
+      </c>
+      <c r="K746" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="n">
+        <v>746</v>
+      </c>
+      <c r="B747" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻小黑瓶眼霜20ml</t>
+        </is>
+      </c>
+      <c r="C747" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻肌底焕活修护眼霜20ml超修小黑瓶发光眼霜【5月24日发完】</t>
+        </is>
+      </c>
+      <c r="D747" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E747" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F747" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G747" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H747" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I747" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J747" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:08:44</t>
+        </is>
+      </c>
+      <c r="K747" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="n">
+        <v>747</v>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻小黑瓶眼霜20ml</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻新版超修小黑眼霜20ml淡纹焕亮</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E748" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F748" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G748" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H748" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I748" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J748" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:09:00</t>
+        </is>
+      </c>
+      <c r="K748" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="n">
+        <v>748</v>
+      </c>
+      <c r="B749" s="2" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿眼霜对装</t>
+        </is>
+      </c>
+      <c r="C749" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评88.8万+条】HR/赫莲娜绿宝瓶眼霜15ml眼部修复淡化黑眼圈【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D749" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E749" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F749" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G749" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H749" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I749" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J749" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:10:20</t>
+        </is>
+      </c>
+      <c r="K749" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿眼霜对装</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>【HR】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈护肤品化妆品情人节520礼盒</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E750" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F750" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H750" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I750" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J750" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:10:41</t>
+        </is>
+      </c>
+      <c r="K750" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="B751" s="2" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="C751" s="2" t="inlineStr">
+        <is>
+          <t>【6.5万人回购该品牌】Gucci古驰花悦绽放淡香香水50ml</t>
+        </is>
+      </c>
+      <c r="D751" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E751" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F751" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G751" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H751" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I751" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J751" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:11:50</t>
+        </is>
+      </c>
+      <c r="K751" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="n">
+        <v>751</v>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>【6.5万人回购该品牌】GUCCI/古驰花悦绽放女士淡香水EDT50ml芬芳清香送礼</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E752" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F752" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H752" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I752" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J752" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:12:08</t>
+        </is>
+      </c>
+      <c r="K752" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="n">
+        <v>752</v>
+      </c>
+      <c r="B753" s="2" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="C753" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销73.8万+件】Gucci 古驰 花悦绽放女士淡香水 50ml 浪漫花香调</t>
+        </is>
+      </c>
+      <c r="D753" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E753" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F753" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G753" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H753" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I753" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J753" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:12:25</t>
+        </is>
+      </c>
+      <c r="K753" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N11 2.0</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 持妆控油遮瑕</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E754" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F754" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G754" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H754" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I754" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J754" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:13:56</t>
+        </is>
+      </c>
+      <c r="K754" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="n">
+        <v>754</v>
+      </c>
+      <c r="B755" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N11 2.0</t>
+        </is>
+      </c>
+      <c r="C755" s="2" t="inlineStr">
+        <is>
+          <t>正品MAC/魅可定制无暇粉底液2.0#NW11二代30ml持妆油皮控油遮瑕【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D755" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E755" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F755" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G755" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H755" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I755" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J755" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:14:16</t>
+        </is>
+      </c>
+      <c r="K755" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N11 2.0</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
+          <t>新版2.0MAC魅可定制无瑕粉底液二代控油持妆遮瑕NM11/N12试色油皮</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E756" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F756" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G756" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H756" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I756" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J756" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:14:28</t>
+        </is>
+      </c>
+      <c r="K756" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="n">
+        <v>756</v>
+      </c>
+      <c r="B757" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N11 2.0</t>
+        </is>
+      </c>
+      <c r="C757" s="2" t="inlineStr">
+        <is>
+          <t>油皮的神!升级版2.0 Mac魅可定制无暇粉底液30ml 雾面持妆控油</t>
+        </is>
+      </c>
+      <c r="D757" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E757" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F757" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G757" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H757" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I757" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J757" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:14:42</t>
+        </is>
+      </c>
+      <c r="K757" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="n">
+        <v>757</v>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N18 2.0</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="inlineStr">
+        <is>
+          <t>不支持7天无理由退换</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E758" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F758" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G758" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H758" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I758" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J758" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:16:13</t>
+        </is>
+      </c>
+      <c r="K758" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=12.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="B759" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N18 2.0</t>
+        </is>
+      </c>
+      <c r="C759" s="2" t="inlineStr">
+        <is>
+          <t>正品MAC/魅可定制无暇粉底液2.0二代#N18自然色30ml清透遮瑕持妆【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D759" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E759" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F759" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G759" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H759" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I759" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J759" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:16:28</t>
+        </is>
+      </c>
+      <c r="K759" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="n">
+        <v>759</v>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N18 2.0</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可无瑕粉底液2.0 #N18自然 油皮的神控油持妆遮瑕30ml正品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E760" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F760" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G760" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H760" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I760" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J760" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:16:38</t>
+        </is>
+      </c>
+      <c r="K760" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="n">
+        <v>760</v>
+      </c>
+      <c r="B761" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="C761" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 持妆控油遮瑕</t>
+        </is>
+      </c>
+      <c r="D761" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E761" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F761" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G761" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H761" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I761" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J761" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:17:33</t>
+        </is>
+      </c>
+      <c r="K761" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="n">
+        <v>761</v>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定制无暇粉底液2.0二代NW11持妆油皮控油持久</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E762" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F762" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G762" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H762" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I762" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J762" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:17:55</t>
+        </is>
+      </c>
+      <c r="K762" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="n">
+        <v>762</v>
+      </c>
+      <c r="B763" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="C763" s="2" t="inlineStr">
+        <is>
+          <t>正品 MAC/魅可无瑕粉底液2.0#NW11 30ml 油皮的神【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D763" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E763" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F763" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G763" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H763" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I763" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J763" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:18:10</t>
+        </is>
+      </c>
+      <c r="K763" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="n">
+        <v>763</v>
+      </c>
+      <c r="B764" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="inlineStr">
+        <is>
+          <t>正品MAC/魅可2.0二代定制无暇粉底液#NW11白皙肤色30ml清透持妆【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E764" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F764" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G764" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H764" s="3" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="I764" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J764" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:18:25</t>
+        </is>
+      </c>
+      <c r="K764" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=44.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="n">
+        <v>764</v>
+      </c>
+      <c r="B765" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="C765" s="2" t="inlineStr">
+        <is>
+          <t>【Givenchy】纪梵希 四宫格柔雾散粉0号1号2号3号 12g</t>
+        </is>
+      </c>
+      <c r="D765" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希</t>
+        </is>
+      </c>
+      <c r="E765" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希</t>
+        </is>
+      </c>
+      <c r="F765" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G765" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H765" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I765" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J765" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:19:30</t>
+        </is>
+      </c>
+      <c r="K765" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="n">
+        <v>765</v>
+      </c>
+      <c r="B766" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Givenchy/纪梵希 明星四宫格散粉1号 4*3g</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希</t>
+        </is>
+      </c>
+      <c r="E766" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希</t>
+        </is>
+      </c>
+      <c r="F766" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G766" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H766" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I766" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J766" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:19:49</t>
+        </is>
+      </c>
+      <c r="K766" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="n">
+        <v>766</v>
+      </c>
+      <c r="B767" s="2" t="inlineStr">
+        <is>
+          <t>黛珂牛油果乳液300ml*2</t>
+        </is>
+      </c>
+      <c r="C767" s="2" t="inlineStr">
+        <is>
+          <t>DECORTE黛珂 牛油果植萃乳液300ML老版保湿紧致弹润控油持久保湿</t>
+        </is>
+      </c>
+      <c r="D767" s="2" t="inlineStr">
+        <is>
+          <t>黛珂</t>
+        </is>
+      </c>
+      <c r="E767" s="2" t="inlineStr">
+        <is>
+          <t>黛珂</t>
+        </is>
+      </c>
+      <c r="F767" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G767" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H767" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I767" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J767" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:21:01</t>
+        </is>
+      </c>
+      <c r="K767" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/商品校验调试记录.xlsx
+++ b/商品校验调试记录.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K767"/>
+  <dimension ref="A1:K894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -40869,6 +40869,6689 @@
         </is>
       </c>
     </row>
+    <row r="768">
+      <c r="A768" s="2" t="n">
+        <v>767</v>
+      </c>
+      <c r="B768" s="2" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】肌肤之钥净采洁面膏125ml*2清爽型/湿润型补水保湿</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E768" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F768" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G768" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H768" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I768" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J768" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:38:23</t>
+        </is>
+      </c>
+      <c r="K768" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="B769" s="2" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="C769" s="2" t="inlineStr"/>
+      <c r="D769" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E769" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F769" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G769" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H769" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I769" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J769" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:38:46</t>
+        </is>
+      </c>
+      <c r="K769" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="n">
+        <v>769</v>
+      </c>
+      <c r="B770" s="2" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="inlineStr"/>
+      <c r="D770" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E770" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F770" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G770" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H770" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I770" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J770" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:39:01</t>
+        </is>
+      </c>
+      <c r="K770" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="B771" s="2" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="C771" s="2" t="inlineStr">
+        <is>
+          <t>【 正品行货】CPB/肌肤之钥洗面奶125ml光凝润采妆前隔离37ml</t>
+        </is>
+      </c>
+      <c r="D771" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="E771" s="2" t="inlineStr">
+        <is>
+          <t>肌肤之钥</t>
+        </is>
+      </c>
+      <c r="F771" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G771" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H771" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I771" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J771" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:39:17</t>
+        </is>
+      </c>
+      <c r="K771" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="n">
+        <v>771</v>
+      </c>
+      <c r="B772" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="C772" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦栀子香水爆款花香调简装EDP无盖 100ml</t>
+        </is>
+      </c>
+      <c r="D772" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E772" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F772" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G772" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H772" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I772" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J772" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:40:27</t>
+        </is>
+      </c>
+      <c r="K772" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="n">
+        <v>772</v>
+      </c>
+      <c r="B773" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="C773" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦花园系列馥栀女士香水花香调EDP100ml</t>
+        </is>
+      </c>
+      <c r="D773" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E773" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F773" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G773" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H773" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I773" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J773" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:40:45</t>
+        </is>
+      </c>
+      <c r="K773" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="n">
+        <v>773</v>
+      </c>
+      <c r="B774" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="C774" s="2" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+        </is>
+      </c>
+      <c r="D774" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E774" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F774" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G774" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H774" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I774" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J774" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:41:00</t>
+        </is>
+      </c>
+      <c r="K774" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="n">
+        <v>774</v>
+      </c>
+      <c r="B775" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="C775" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
+        </is>
+      </c>
+      <c r="D775" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E775" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F775" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G775" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H775" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I775" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J775" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:41:21</t>
+        </is>
+      </c>
+      <c r="K775" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="n">
+        <v>775</v>
+      </c>
+      <c r="B776" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰花悦绽放慕意香水女士优雅简装EDP 100ml</t>
+        </is>
+      </c>
+      <c r="D776" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E776" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F776" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G776" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H776" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I776" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J776" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:42:39</t>
+        </is>
+      </c>
+      <c r="K776" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="n">
+        <v>776</v>
+      </c>
+      <c r="B777" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="C777" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰花悦绽放浓香水100ml简装黑盖女士香氛正品持久留香</t>
+        </is>
+      </c>
+      <c r="D777" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E777" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F777" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G777" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H777" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I777" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J777" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:43:00</t>
+        </is>
+      </c>
+      <c r="K777" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="n">
+        <v>777</v>
+      </c>
+      <c r="B778" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰花悦绽放女士浓香水花香调持久留香送礼100ml</t>
+        </is>
+      </c>
+      <c r="D778" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E778" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F778" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G778" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H778" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I778" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J778" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:43:20</t>
+        </is>
+      </c>
+      <c r="K778" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="n">
+        <v>778</v>
+      </c>
+      <c r="B779" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
+        </is>
+      </c>
+      <c r="C779" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
+        </is>
+      </c>
+      <c r="D779" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E779" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F779" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G779" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H779" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I779" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J779" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:45:09</t>
+        </is>
+      </c>
+      <c r="K779" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="n">
+        <v>779</v>
+      </c>
+      <c r="B780" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+        </is>
+      </c>
+      <c r="D780" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E780" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F780" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G780" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H780" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I780" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J780" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:46:37</t>
+        </is>
+      </c>
+      <c r="K780" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="n">
+        <v>780</v>
+      </c>
+      <c r="B781" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="C781" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦栀子香水爆款花香调简装EDP无盖 100ml</t>
+        </is>
+      </c>
+      <c r="D781" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E781" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F781" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G781" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H781" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I781" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J781" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:46:54</t>
+        </is>
+      </c>
+      <c r="K781" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="n">
+        <v>781</v>
+      </c>
+      <c r="B782" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+        </is>
+      </c>
+      <c r="D782" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E782" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F782" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G782" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H782" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I782" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J782" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:47:09</t>
+        </is>
+      </c>
+      <c r="K782" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="n">
+        <v>782</v>
+      </c>
+      <c r="B783" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="C783" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
+        </is>
+      </c>
+      <c r="D783" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E783" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F783" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G783" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H783" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I783" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J783" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:47:30</t>
+        </is>
+      </c>
+      <c r="K783" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="B784" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香100ml</t>
+        </is>
+      </c>
+      <c r="C784" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦香草兰浓香水 甜美水生美食调 EDP30ml</t>
+        </is>
+      </c>
+      <c r="D784" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E784" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F784" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G784" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H784" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I784" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J784" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:49:06</t>
+        </is>
+      </c>
+      <c r="K784" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="n">
+        <v>784</v>
+      </c>
+      <c r="B785" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香100ml</t>
+        </is>
+      </c>
+      <c r="C785" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦香草兰香型女士浓香水水生调节日礼物【520礼物】</t>
+        </is>
+      </c>
+      <c r="D785" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E785" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F785" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G785" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H785" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I785" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J785" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:49:23</t>
+        </is>
+      </c>
+      <c r="K785" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="n">
+        <v>785</v>
+      </c>
+      <c r="B786" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香100ml</t>
+        </is>
+      </c>
+      <c r="C786" s="2" t="inlineStr">
+        <is>
+          <t>【100ml】古驰 绮梦兰花浓香水EDP简装无盖</t>
+        </is>
+      </c>
+      <c r="D786" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E786" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F786" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G786" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H786" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I786" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J786" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:49:41</t>
+        </is>
+      </c>
+      <c r="K786" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="n">
+        <v>786</v>
+      </c>
+      <c r="B787" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香50ml</t>
+        </is>
+      </c>
+      <c r="C787" s="2" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+        </is>
+      </c>
+      <c r="D787" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E787" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F787" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G787" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H787" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I787" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J787" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:51:17</t>
+        </is>
+      </c>
+      <c r="K787" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="n">
+        <v>787</v>
+      </c>
+      <c r="B788" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香50ml</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="inlineStr">
+        <is>
+          <t>【正品鉴定】GUCCI古驰 2024年新品 绮梦香草兰浓香水/兰花香草</t>
+        </is>
+      </c>
+      <c r="D788" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E788" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F788" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G788" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H788" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I788" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J788" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:51:42</t>
+        </is>
+      </c>
+      <c r="K788" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="n">
+        <v>788</v>
+      </c>
+      <c r="B789" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香50ml</t>
+        </is>
+      </c>
+      <c r="C789" s="2" t="inlineStr">
+        <is>
+          <t>【国内直售】GUCCI/古驰香水新品绮梦栀子花香草兰浓香EDP</t>
+        </is>
+      </c>
+      <c r="D789" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E789" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F789" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G789" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H789" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I789" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J789" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:51:56</t>
+        </is>
+      </c>
+      <c r="K789" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="n">
+        <v>789</v>
+      </c>
+      <c r="B790" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香50ml</t>
+        </is>
+      </c>
+      <c r="C790" s="2" t="inlineStr">
+        <is>
+          <t>【原盒正品】GUCCI古驰 2024年新品 绮梦香草兰浓香水/兰花香草</t>
+        </is>
+      </c>
+      <c r="D790" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E790" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F790" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G790" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H790" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I790" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J790" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:52:06</t>
+        </is>
+      </c>
+      <c r="K790" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="2" t="n">
+        <v>790</v>
+      </c>
+      <c r="B791" s="2" t="inlineStr">
+        <is>
+          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
+        </is>
+      </c>
+      <c r="C791" s="2" t="inlineStr">
+        <is>
+          <t>【卡诗】黑钻钥源洗发水鱼子酱滋养受损干枯毛躁润泽保湿黑金洗发露</t>
+        </is>
+      </c>
+      <c r="D791" s="2" t="inlineStr">
+        <is>
+          <t>卡诗</t>
+        </is>
+      </c>
+      <c r="E791" s="2" t="inlineStr">
+        <is>
+          <t>卡诗</t>
+        </is>
+      </c>
+      <c r="F791" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G791" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H791" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I791" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J791" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:53:37</t>
+        </is>
+      </c>
+      <c r="K791" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="n">
+        <v>791</v>
+      </c>
+      <c r="B792" s="2" t="inlineStr">
+        <is>
+          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
+        </is>
+      </c>
+      <c r="C792" s="2" t="inlineStr">
+        <is>
+          <t>【卡诗】黑钻钥源凝时鱼子酱洗发水250ml滋养修护柔顺温和清洁 专柜</t>
+        </is>
+      </c>
+      <c r="D792" s="2" t="inlineStr">
+        <is>
+          <t>卡诗</t>
+        </is>
+      </c>
+      <c r="E792" s="2" t="inlineStr">
+        <is>
+          <t>卡诗</t>
+        </is>
+      </c>
+      <c r="F792" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G792" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H792" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I792" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J792" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:54:00</t>
+        </is>
+      </c>
+      <c r="K792" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="2" t="n">
+        <v>792</v>
+      </c>
+      <c r="B793" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="C793" s="2" t="inlineStr">
+        <is>
+          <t>【赫莲娜】赫莲娜HR绿宝瓶新肌水400ml精华爽肤舒缓修护</t>
+        </is>
+      </c>
+      <c r="D793" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E793" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F793" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G793" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H793" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I793" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J793" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:55:31</t>
+        </is>
+      </c>
+      <c r="K793" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="n">
+        <v>793</v>
+      </c>
+      <c r="B794" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="C794" s="2" t="inlineStr">
+        <is>
+          <t>【赫莲娜】绿宝瓶新肌水200ml补水保湿精华水</t>
+        </is>
+      </c>
+      <c r="D794" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E794" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F794" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G794" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H794" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I794" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J794" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:55:48</t>
+        </is>
+      </c>
+      <c r="K794" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="n">
+        <v>794</v>
+      </c>
+      <c r="B795" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="C795" s="2" t="inlineStr">
+        <is>
+          <t>两瓶 单品 HR赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D795" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E795" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F795" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G795" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H795" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I795" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J795" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:56:04</t>
+        </is>
+      </c>
+      <c r="K795" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="n">
+        <v>795</v>
+      </c>
+      <c r="B796" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+        </is>
+      </c>
+      <c r="C796" s="2" t="inlineStr">
+        <is>
+          <t>HR/赫莲娜绿宝瓶新肌水200ml*2维稳补水保湿精华水</t>
+        </is>
+      </c>
+      <c r="D796" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E796" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F796" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G796" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H796" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I796" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J796" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:57:35</t>
+        </is>
+      </c>
+      <c r="K796" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="n">
+        <v>796</v>
+      </c>
+      <c r="B797" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+        </is>
+      </c>
+      <c r="C797" s="2" t="inlineStr">
+        <is>
+          <t>【赫莲娜】绿宝瓶新肌水200ml补水保湿精华水</t>
+        </is>
+      </c>
+      <c r="D797" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E797" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F797" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G797" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H797" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I797" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J797" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:57:53</t>
+        </is>
+      </c>
+      <c r="K797" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="n">
+        <v>797</v>
+      </c>
+      <c r="B798" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+        </is>
+      </c>
+      <c r="C798" s="2" t="inlineStr">
+        <is>
+          <t>两瓶 单品 HR赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D798" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="E798" s="2" t="inlineStr">
+        <is>
+          <t>赫莲娜</t>
+        </is>
+      </c>
+      <c r="F798" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G798" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H798" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I798" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J798" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:58:09</t>
+        </is>
+      </c>
+      <c r="K798" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="n">
+        <v>798</v>
+      </c>
+      <c r="B799" s="2" t="inlineStr">
+        <is>
+          <t>SK-II光子小灯泡精华露50ml</t>
+        </is>
+      </c>
+      <c r="C799" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+        </is>
+      </c>
+      <c r="D799" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E799" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F799" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G799" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H799" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I799" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J799" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:59:39</t>
+        </is>
+      </c>
+      <c r="K799" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="B800" s="2" t="inlineStr">
+        <is>
+          <t>SK-II晶致美肤乳液100g</t>
+        </is>
+      </c>
+      <c r="C800" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II骨胶原晶致活肤修护乳液补水保湿抗皱紧致舒缓</t>
+        </is>
+      </c>
+      <c r="D800" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E800" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F800" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G800" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H800" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I800" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J800" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:01:10</t>
+        </is>
+      </c>
+      <c r="K800" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="B801" s="2" t="inlineStr">
+        <is>
+          <t>SK-II晶致美肤乳液100g</t>
+        </is>
+      </c>
+      <c r="C801" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】 晶致美肤乳液100ml 骨胶原修护活肤乳液紧致提亮保湿抗皱</t>
+        </is>
+      </c>
+      <c r="D801" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E801" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F801" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G801" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H801" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I801" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J801" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:01:34</t>
+        </is>
+      </c>
+      <c r="K801" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="B802" s="2" t="inlineStr">
+        <is>
+          <t>SK-II晶致美肤乳液100g</t>
+        </is>
+      </c>
+      <c r="C802" s="2" t="inlineStr">
+        <is>
+          <t>SK-II/SK2 晶致活肤骨胶原乳液100g(无盒/不满瓶)【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D802" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E802" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F802" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G802" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H802" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I802" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J802" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:01:46</t>
+        </is>
+      </c>
+      <c r="K802" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="2" t="n">
+        <v>802</v>
+      </c>
+      <c r="B803" s="2" t="inlineStr">
+        <is>
+          <t>SK-II晶致美肤乳液100g</t>
+        </is>
+      </c>
+      <c r="C803" s="2" t="inlineStr">
+        <is>
+          <t>SK2晶致美肤乳液100g 骨胶原修护紧致活肤 保湿不油腻【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D803" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E803" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F803" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G803" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H803" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I803" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J803" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:02:00</t>
+        </is>
+      </c>
+      <c r="K803" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="n">
+        <v>803</v>
+      </c>
+      <c r="B804" s="2" t="inlineStr">
+        <is>
+          <t>SKII女士洗面奶120g/支</t>
+        </is>
+      </c>
+      <c r="C804" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II温和护肤洁面霜SK2舒透洗面奶洁净舒缓肌肤skll</t>
+        </is>
+      </c>
+      <c r="D804" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E804" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F804" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G804" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H804" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I804" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J804" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:03:31</t>
+        </is>
+      </c>
+      <c r="K804" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="2" t="n">
+        <v>804</v>
+      </c>
+      <c r="B805" s="2" t="inlineStr">
+        <is>
+          <t>SKII女士洗面奶120g/支</t>
+        </is>
+      </c>
+      <c r="C805" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】 女士氨基酸清洁洁面乳120g/支</t>
+        </is>
+      </c>
+      <c r="D805" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E805" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F805" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G805" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H805" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I805" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J805" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:03:49</t>
+        </is>
+      </c>
+      <c r="K805" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="n">
+        <v>805</v>
+      </c>
+      <c r="B806" s="2" t="inlineStr">
+        <is>
+          <t>SKII女士洗面奶120g/支</t>
+        </is>
+      </c>
+      <c r="C806" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII氨基酸洗面奶护肤洁面乳120g两瓶装温和控油清洁</t>
+        </is>
+      </c>
+      <c r="D806" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E806" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F806" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G806" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H806" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I806" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J806" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:04:08</t>
+        </is>
+      </c>
+      <c r="K806" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="2" t="n">
+        <v>806</v>
+      </c>
+      <c r="B807" s="2" t="inlineStr">
+        <is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="C807" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】 SK-II/SK2前男友面膜补水保湿急救护肤3/4/6/10片装【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D807" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E807" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F807" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G807" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H807" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I807" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J807" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:05:39</t>
+        </is>
+      </c>
+      <c r="K807" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="n">
+        <v>807</v>
+      </c>
+      <c r="B808" s="2" t="inlineStr">
+        <is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="C808" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK2前男友面膜10片装焕润嫩肤贴片女友送礼奢护礼盒</t>
+        </is>
+      </c>
+      <c r="D808" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E808" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F808" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G808" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H808" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I808" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J808" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:05:58</t>
+        </is>
+      </c>
+      <c r="K808" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="2" t="n">
+        <v>808</v>
+      </c>
+      <c r="B809" s="2" t="inlineStr">
+        <is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="C809" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】 SK-II/SK2前男友面膜补水保湿急救护肤3/4/6/10片装【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D809" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E809" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F809" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G809" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H809" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I809" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J809" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:07:29</t>
+        </is>
+      </c>
+      <c r="K809" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="B810" s="2" t="inlineStr">
+        <is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="C810" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK2前男友面膜10片装焕润嫩肤贴片女友送礼奢护礼盒</t>
+        </is>
+      </c>
+      <c r="D810" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E810" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F810" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G810" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H810" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I810" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J810" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:07:48</t>
+        </is>
+      </c>
+      <c r="K810" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="n">
+        <v>810</v>
+      </c>
+      <c r="B811" s="2" t="inlineStr">
+        <is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="C811" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII赋能焕采精华霜大红瓶面霜滋润轻盈保湿紧致养肤</t>
+        </is>
+      </c>
+      <c r="D811" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E811" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F811" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G811" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H811" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I811" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J811" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:09:19</t>
+        </is>
+      </c>
+      <c r="K811" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="n">
+        <v>811</v>
+      </c>
+      <c r="B812" s="2" t="inlineStr">
+        <is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="C812" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g 滋润版</t>
+        </is>
+      </c>
+      <c r="D812" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E812" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F812" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G812" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H812" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I812" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J812" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:09:39</t>
+        </is>
+      </c>
+      <c r="K812" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="n">
+        <v>812</v>
+      </c>
+      <c r="B813" s="2" t="inlineStr">
+        <is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="C813" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+        </is>
+      </c>
+      <c r="D813" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E813" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F813" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G813" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H813" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I813" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J813" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:09:58</t>
+        </is>
+      </c>
+      <c r="K813" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="B814" s="2" t="inlineStr">
+        <is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤滋润款</t>
+        </is>
+      </c>
+      <c r="D814" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E814" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F814" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G814" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H814" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I814" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J814" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:10:17</t>
+        </is>
+      </c>
+      <c r="K814" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="2" t="n">
+        <v>814</v>
+      </c>
+      <c r="B815" s="2" t="inlineStr">
+        <is>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+        </is>
+      </c>
+      <c r="C815" s="2" t="inlineStr"/>
+      <c r="D815" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="E815" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F815" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G815" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H815" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I815" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J815" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:33:34</t>
+        </is>
+      </c>
+      <c r="K815" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="n">
+        <v>815</v>
+      </c>
+      <c r="B816" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="C816" s="2" t="inlineStr"/>
+      <c r="D816" s="2" t="inlineStr">
+        <is>
+          <t>汤姆福特</t>
+        </is>
+      </c>
+      <c r="E816" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F816" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G816" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H816" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I816" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J816" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:35:24</t>
+        </is>
+      </c>
+      <c r="K816" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="n">
+        <v>816</v>
+      </c>
+      <c r="B817" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="C817" s="2" t="inlineStr"/>
+      <c r="D817" s="2" t="inlineStr">
+        <is>
+          <t>汤姆福特</t>
+        </is>
+      </c>
+      <c r="E817" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F817" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G817" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H817" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I817" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J817" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:36:14</t>
+        </is>
+      </c>
+      <c r="K817" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="n">
+        <v>817</v>
+      </c>
+      <c r="B818" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="C818" s="2" t="inlineStr"/>
+      <c r="D818" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E818" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F818" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G818" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H818" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I818" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J818" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:48:09</t>
+        </is>
+      </c>
+      <c r="K818" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="n">
+        <v>818</v>
+      </c>
+      <c r="B819" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="C819" s="2" t="inlineStr"/>
+      <c r="D819" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E819" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F819" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G819" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H819" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I819" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J819" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:57:35</t>
+        </is>
+      </c>
+      <c r="K819" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="n">
+        <v>819</v>
+      </c>
+      <c r="B820" s="2" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉GIPSY吉普赛</t>
+        </is>
+      </c>
+      <c r="C820" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯哑光唇釉空气柔雾唇霜#684 Gipsy吉普赛玫瑰</t>
+        </is>
+      </c>
+      <c r="D820" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E820" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F820" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G820" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H820" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I820" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J820" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:29:16</t>
+        </is>
+      </c>
+      <c r="K820" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="B821" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="C821" s="2" t="inlineStr">
+        <is>
+          <t>宏香记品牌官方正品，100%保障</t>
+        </is>
+      </c>
+      <c r="D821" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="E821" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F821" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G821" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H821" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I821" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J821" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:30:54</t>
+        </is>
+      </c>
+      <c r="K821" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="B822" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="C822" s="2" t="inlineStr">
+        <is>
+          <t>韩国直邮THEWHOO后天气丹PRO光耀焕活紧颜滋养水乳正装提拉抗皱白【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D822" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="E822" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="F822" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G822" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H822" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I822" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J822" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:31:13</t>
+        </is>
+      </c>
+      <c r="K822" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="2" t="n">
+        <v>822</v>
+      </c>
+      <c r="B823" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="C823" s="2" t="inlineStr">
+        <is>
+          <t>韩国whoo后天气丹PRO淡纹乳110ml 清透保湿亮肤紧致抗皱滋养乳【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D823" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="E823" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="F823" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G823" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H823" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I823" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J823" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:31:26</t>
+        </is>
+      </c>
+      <c r="K823" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="n">
+        <v>823</v>
+      </c>
+      <c r="B824" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】后天气丹PRO光耀焕活紧颜滋养乳50ml/瓶保湿紧致滋润</t>
+        </is>
+      </c>
+      <c r="D824" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="E824" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="F824" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G824" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H824" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I824" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J824" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:31:43</t>
+        </is>
+      </c>
+      <c r="K824" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="n">
+        <v>824</v>
+      </c>
+      <c r="B825" s="2" t="inlineStr">
+        <is>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+        </is>
+      </c>
+      <c r="C825" s="2" t="inlineStr">
+        <is>
+          <t>新款韩国whoo后拱辰享美奢华黄金气垫套盒粉底修容遮瑕提亮肤色</t>
+        </is>
+      </c>
+      <c r="D825" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="E825" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="F825" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G825" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H825" s="3" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="I825" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J825" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:33:10</t>
+        </is>
+      </c>
+      <c r="K825" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="B826" s="2" t="inlineStr">
+        <is>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="inlineStr"/>
+      <c r="D826" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="E826" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F826" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G826" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H826" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I826" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J826" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:33:34</t>
+        </is>
+      </c>
+      <c r="K826" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="B827" s="2" t="inlineStr">
+        <is>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+        </is>
+      </c>
+      <c r="C827" s="2" t="inlineStr">
+        <is>
+          <t>新款韩国whoo后拱辰享美奢华黄金气垫套盒粉底修容遮瑕提亮肤色</t>
+        </is>
+      </c>
+      <c r="D827" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="E827" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="F827" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G827" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H827" s="3" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="I827" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J827" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:33:47</t>
+        </is>
+      </c>
+      <c r="K827" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="n">
+        <v>827</v>
+      </c>
+      <c r="B828" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="inlineStr"/>
+      <c r="D828" s="2" t="inlineStr">
+        <is>
+          <t>汤姆福特</t>
+        </is>
+      </c>
+      <c r="E828" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F828" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G828" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H828" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I828" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J828" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:35:24</t>
+        </is>
+      </c>
+      <c r="K828" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="2" t="n">
+        <v>828</v>
+      </c>
+      <c r="B829" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="C829" s="2" t="inlineStr">
+        <is>
+          <t>正品TomFord汤姆福特TF幻魅四色眼影盘#35ROSE TOPAZ杏茶盘9g哑光【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D829" s="2" t="inlineStr">
+        <is>
+          <t>汤姆福特</t>
+        </is>
+      </c>
+      <c r="E829" s="2" t="inlineStr">
+        <is>
+          <t>汤姆福特</t>
+        </is>
+      </c>
+      <c r="F829" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G829" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H829" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I829" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J829" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:35:47</t>
+        </is>
+      </c>
+      <c r="K829" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="n">
+        <v>829</v>
+      </c>
+      <c r="B830" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="inlineStr">
+        <is>
+          <t>正品TomFord汤姆福特TF幻魅四色眼影盘#35ROSE TOPAZ杏茶盘9g哑光【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D830" s="2" t="inlineStr">
+        <is>
+          <t>汤姆福特</t>
+        </is>
+      </c>
+      <c r="E830" s="2" t="inlineStr">
+        <is>
+          <t>汤姆福特</t>
+        </is>
+      </c>
+      <c r="F830" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G830" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H830" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I830" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J830" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:36:01</t>
+        </is>
+      </c>
+      <c r="K830" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="2" t="n">
+        <v>830</v>
+      </c>
+      <c r="B831" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="C831" s="2" t="inlineStr"/>
+      <c r="D831" s="2" t="inlineStr">
+        <is>
+          <t>汤姆福特</t>
+        </is>
+      </c>
+      <c r="E831" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F831" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G831" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H831" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I831" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J831" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:36:14</t>
+        </is>
+      </c>
+      <c r="K831" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="B832" s="2" t="inlineStr">
+        <is>
+          <t>SK-II小灯泡新版50ml</t>
+        </is>
+      </c>
+      <c r="C832" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+        </is>
+      </c>
+      <c r="D832" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E832" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F832" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G832" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H832" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I832" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J832" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:37:51</t>
+        </is>
+      </c>
+      <c r="K832" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="2" t="n">
+        <v>832</v>
+      </c>
+      <c r="B833" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="C833" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+        </is>
+      </c>
+      <c r="D833" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E833" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F833" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G833" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H833" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I833" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J833" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:39:31</t>
+        </is>
+      </c>
+      <c r="K833" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="B834" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="inlineStr">
+        <is>
+          <t>【正品】SK-II光子小灯泡75ml美白护肤精华液淡斑提亮【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D834" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E834" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F834" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G834" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H834" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I834" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J834" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:39:51</t>
+        </is>
+      </c>
+      <c r="K834" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="B835" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="C835" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡精华75ml套装礼盒礼物淡斑提亮紧致</t>
+        </is>
+      </c>
+      <c r="D835" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E835" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F835" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G835" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H835" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I835" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J835" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:40:05</t>
+        </is>
+      </c>
+      <c r="K835" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="B836" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡新款焕亮精华露75ml 美白淡斑紧致</t>
+        </is>
+      </c>
+      <c r="D836" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E836" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F836" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G836" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H836" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I836" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J836" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:40:20</t>
+        </is>
+      </c>
+      <c r="K836" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="n">
+        <v>836</v>
+      </c>
+      <c r="B837" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="C837" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】氨基酸洗面奶sk2洁面温和洁净调节肌肤平衡水油护肤嫩肤舒缓【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D837" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E837" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F837" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G837" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H837" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I837" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J837" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:41:53</t>
+        </is>
+      </c>
+      <c r="K837" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="n">
+        <v>837</v>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】洗面奶深层清洁温和洁面补水控油舒透护肤洁面</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E838" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F838" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G838" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H838" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I838" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J838" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:42:10</t>
+        </is>
+      </c>
+      <c r="K838" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="n">
+        <v>838</v>
+      </c>
+      <c r="B839" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="inlineStr">
+        <is>
+          <t>正品SK-II护肤洁面油skll卸妆油250ml深层净透温和清洁【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="D839" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E839" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F839" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G839" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H839" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I839" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J839" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:42:29</t>
+        </is>
+      </c>
+      <c r="K839" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="n">
+        <v>839</v>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】护肤洁面油卸妆油250ml 卸妆洁面二合一深层清洁温和洁净【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E840" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F840" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G840" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H840" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I840" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J840" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:42:42</t>
+        </is>
+      </c>
+      <c r="K840" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="n">
+        <v>840</v>
+      </c>
+      <c r="B841" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】护肤洁面油250ml卸妆油温和洁净深层清洁控油【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D841" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E841" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F841" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G841" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H841" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I841" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J841" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:42:53</t>
+        </is>
+      </c>
+      <c r="K841" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="n">
+        <v>841</v>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希粉丝绒N37</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】纪梵希口红粉丝绒口红N37小羊皮N319双支口红大牌女</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希</t>
+        </is>
+      </c>
+      <c r="E842" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希</t>
+        </is>
+      </c>
+      <c r="F842" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G842" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H842" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I842" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J842" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:44:17</t>
+        </is>
+      </c>
+      <c r="K842" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="n">
+        <v>842</v>
+      </c>
+      <c r="B843" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希粉丝绒N37</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】纪梵希高定粉丝绒唇膏口红N37滋润显白持久大牌正品</t>
+        </is>
+      </c>
+      <c r="D843" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希</t>
+        </is>
+      </c>
+      <c r="E843" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希</t>
+        </is>
+      </c>
+      <c r="F843" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G843" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H843" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I843" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J843" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:44:33</t>
+        </is>
+      </c>
+      <c r="K843" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰爱心黑管唇釉440</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉440 610 416 622限定浮雕黑管</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E844" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F844" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G844" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H844" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I844" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J844" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:46:18</t>
+        </is>
+      </c>
+      <c r="K844" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="n">
+        <v>844</v>
+      </c>
+      <c r="B845" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销542.3万+件】两支 单品 雅诗兰黛新款红石榴洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="D845" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E845" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F845" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G845" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H845" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I845" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J845" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:47:50</t>
+        </is>
+      </c>
+      <c r="K845" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="n">
+        <v>845</v>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr"/>
+      <c r="D846" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E846" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F846" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G846" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H846" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I846" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J846" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:48:09</t>
+        </is>
+      </c>
+      <c r="K846" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="n">
+        <v>846</v>
+      </c>
+      <c r="B847" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="inlineStr">
+        <is>
+          <t>【】双支雅诗兰黛红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="D847" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E847" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F847" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G847" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H847" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I847" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J847" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:48:28</t>
+        </is>
+      </c>
+      <c r="K847" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="n">
+        <v>847</v>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E848" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F848" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G848" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H848" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I848" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J848" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:48:49</t>
+        </is>
+      </c>
+      <c r="K848" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="n">
+        <v>848</v>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴水200ml两支装</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER雅诗兰黛】红石榴爽肤水200ml滋润型</t>
+        </is>
+      </c>
+      <c r="D849" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F849" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G849" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H849" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I849" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J849" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:50:26</t>
+        </is>
+      </c>
+      <c r="K849" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="n">
+        <v>849</v>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II神仙水补水保湿sk2护肤精华露30ml爽肤水保湿</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E850" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G850" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H850" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I850" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J850" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:51:54</t>
+        </is>
+      </c>
+      <c r="K850" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="B851" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II小银瓶精华50ml淡斑保湿护肤品送女朋友礼物sk2</t>
+        </is>
+      </c>
+      <c r="D851" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F851" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G851" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H851" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I851" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J851" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:52:13</t>
+        </is>
+      </c>
+      <c r="K851" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="n">
+        <v>851</v>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II淡斑小银瓶精华50ml美白提亮祛斑sk2护肤品送礼</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E852" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F852" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G852" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H852" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I852" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J852" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:52:25</t>
+        </is>
+      </c>
+      <c r="K852" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="n">
+        <v>852</v>
+      </c>
+      <c r="B853" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="inlineStr">
+        <is>
+          <t>【送礼佳品】SK-II/sk2小银瓶精华液淡化斑印提亮肤色50ml礼盒款【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="D853" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E853" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F853" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G853" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H853" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I853" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J853" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:52:39</t>
+        </is>
+      </c>
+      <c r="K853" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="B854" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润面霜50g</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】sk2大红瓶面霜50g面部护肤套装礼盒</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E854" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F854" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G854" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H854" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I854" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J854" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:54:06</t>
+        </is>
+      </c>
+      <c r="K854" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="n">
+        <v>854</v>
+      </c>
+      <c r="B855" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="D855" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E855" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G855" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H855" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I855" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J855" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:55:35</t>
+        </is>
+      </c>
+      <c r="K855" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="n">
+        <v>855</v>
+      </c>
+      <c r="B856" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E856" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F856" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G856" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H856" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I856" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J856" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:55:50</t>
+        </is>
+      </c>
+      <c r="K856" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="n">
+        <v>856</v>
+      </c>
+      <c r="B857" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="D857" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E857" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G857" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H857" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I857" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J857" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:56:06</t>
+        </is>
+      </c>
+      <c r="K857" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="n">
+        <v>857</v>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr"/>
+      <c r="D858" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E858" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F858" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G858" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H858" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I858" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J858" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:57:35</t>
+        </is>
+      </c>
+      <c r="K858" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="n">
+        <v>858</v>
+      </c>
+      <c r="B859" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="C859" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗 大马士革玫瑰花瓣润泽密集保湿爽肤水400ml高保湿深层滋润【5月31日发完】</t>
+        </is>
+      </c>
+      <c r="D859" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E859" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G859" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H859" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I859" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J859" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:57:57</t>
+        </is>
+      </c>
+      <c r="K859" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="n">
+        <v>859</v>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>【馥蕾诗】 大马士革玫瑰花瓣润泽密集保湿爽肤水400ml高保湿深层滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F860" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G860" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H860" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I860" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J860" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:58:08</t>
+        </is>
+      </c>
+      <c r="K860" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="n">
+        <v>860</v>
+      </c>
+      <c r="B861" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗玫瑰花瓣水250ml大马士革玫瑰润泽保湿爽肤水调理肌肤【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D861" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G861" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H861" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I861" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J861" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:58:21</t>
+        </is>
+      </c>
+      <c r="K861" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="n">
+        <v>861</v>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶紧致面霜50ml</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】馥蕾诗红茶凝时焕活面霜50ml淡纹紧致增加光泽</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E862" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G862" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H862" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I862" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J862" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:00:03</t>
+        </is>
+      </c>
+      <c r="K862" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="n">
+        <v>862</v>
+      </c>
+      <c r="B863" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗睡莲日霜50ml</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】馥蕾诗睡莲青春赋活面霜50ml修护淡纹柔润光采</t>
+        </is>
+      </c>
+      <c r="D863" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E863" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G863" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H863" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I863" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J863" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:01:39</t>
+        </is>
+      </c>
+      <c r="K863" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="n">
+        <v>863</v>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗玫瑰保湿面霜50ml  密集保湿舒缓补水</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E864" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F864" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G864" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H864" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I864" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J864" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:03:06</t>
+        </is>
+      </c>
+      <c r="K864" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="n">
+        <v>864</v>
+      </c>
+      <c r="B865" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="D865" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E865" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G865" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H865" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I865" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J865" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:04:33</t>
+        </is>
+      </c>
+      <c r="K865" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="n">
+        <v>865</v>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="D866" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E866" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F866" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G866" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H866" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I866" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J866" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:04:52</t>
+        </is>
+      </c>
+      <c r="K866" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="n">
+        <v>866</v>
+      </c>
+      <c r="B867" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="C867" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛白金级养肤粉底液宝石粉底光感保湿透亮遮瑕</t>
+        </is>
+      </c>
+      <c r="D867" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E867" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F867" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G867" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H867" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I867" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J867" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:06:41</t>
+        </is>
+      </c>
+      <c r="K867" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="n">
+        <v>867</v>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛白金级养肤粉底液宝石粉底光感保湿透亮遮瑕</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E868" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F868" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G868" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H868" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I868" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J868" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:06:55</t>
+        </is>
+      </c>
+      <c r="K868" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="n">
+        <v>868</v>
+      </c>
+      <c r="B869" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="C869" s="2" t="inlineStr">
+        <is>
+          <t>【专柜行货】雅诗兰黛白金养肤粉底液 持久遮瑕保湿抗氧化服帖</t>
+        </is>
+      </c>
+      <c r="D869" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E869" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H869" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I869" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J869" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:07:07</t>
+        </is>
+      </c>
+      <c r="K869" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="n">
+        <v>869</v>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶精粹水250ml</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗酵母酵萃红茶水250ml保湿补水清爽滋润爽肤水精华水</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E870" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F870" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H870" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I870" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J870" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:08:44</t>
+        </is>
+      </c>
+      <c r="K870" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="n">
+        <v>870</v>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1CO</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】白金粉底液1C0养肤透亮持久保湿遮瑕服帖【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D871" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G871" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H871" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I871" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J871" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:10:17</t>
+        </is>
+      </c>
+      <c r="K871" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="n">
+        <v>871</v>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】美白三件套(水200ml+乳液100ml+精华50ml)</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E872" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F872" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G872" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H872" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I872" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J872" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:11:59</t>
+        </is>
+      </c>
+      <c r="K872" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="n">
+        <v>872</v>
+      </c>
+      <c r="B873" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Clarins/娇韵诗牛奶美白水乳组礼盒装淡斑祛黄提亮</t>
+        </is>
+      </c>
+      <c r="D873" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G873" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H873" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I873" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J873" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:12:22</t>
+        </is>
+      </c>
+      <c r="K873" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="n">
+        <v>873</v>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗牛奶水减黄提亮美白淡斑清爽200ml保湿细腻</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E874" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F874" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G874" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H874" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I874" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J874" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:12:38</t>
+        </is>
+      </c>
+      <c r="K874" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="n">
+        <v>874</v>
+      </c>
+      <c r="B875" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗牛奶水清透润白柔肤水清爽滋润型焕亮净白柔嫩【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D875" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E875" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G875" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H875" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I875" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J875" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:13:01</t>
+        </is>
+      </c>
+      <c r="K875" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>【澳洲专柜】娇韵诗丰润型牛奶水透亮焕白淡斑美白保湿爽肤水【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E876" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F876" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G876" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H876" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I876" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J876" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:13:11</t>
+        </is>
+      </c>
+      <c r="K876" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="n">
+        <v>876</v>
+      </c>
+      <c r="B877" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】美白水乳套组牛奶水200ml+乳液75ml+</t>
+        </is>
+      </c>
+      <c r="D877" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E877" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G877" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H877" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I877" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J877" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:13:22</t>
+        </is>
+      </c>
+      <c r="K877" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="n">
+        <v>877</v>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E878" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F878" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G878" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H878" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I878" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J878" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:15:08</t>
+        </is>
+      </c>
+      <c r="K878" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n">
+        <v>878</v>
+      </c>
+      <c r="B879" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="inlineStr">
+        <is>
+          <t>CLARINS/娇韵诗焕颜紧致弹簧霜晚霜 50ml修护提亮 娇韵诗弹簧晚霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D879" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E879" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G879" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H879" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I879" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J879" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:15:20</t>
+        </is>
+      </c>
+      <c r="K879" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E880" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F880" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G880" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H880" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I880" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J880" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:15:34</t>
+        </is>
+      </c>
+      <c r="K880" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="B881" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D881" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G881" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H881" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I881" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J881" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:17:21</t>
+        </is>
+      </c>
+      <c r="K881" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="n">
+        <v>881</v>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】娇韵诗焕颜弹力晚霜面霜50ml保湿提拉紧致滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E882" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F882" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G882" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H882" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I882" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J882" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:17:35</t>
+        </is>
+      </c>
+      <c r="K882" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="n">
+        <v>882</v>
+      </c>
+      <c r="B883" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D883" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F883" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G883" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H883" s="3" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I883" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J883" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:17:48</t>
+        </is>
+      </c>
+      <c r="K883" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="n">
+        <v>883</v>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】多效智妍面霜75ml 新款清爽款保湿</t>
+        </is>
+      </c>
+      <c r="D884" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E884" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F884" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H884" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I884" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J884" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:19:19</t>
+        </is>
+      </c>
+      <c r="K884" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="n">
+        <v>884</v>
+      </c>
+      <c r="B885" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="C885" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】梅森马吉拉慵懒周末身体乳50ml*2</t>
+        </is>
+      </c>
+      <c r="D885" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="E885" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="F885" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G885" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H885" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I885" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J885" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:20:57</t>
+        </is>
+      </c>
+      <c r="K885" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="B886" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="C886" s="2" t="inlineStr">
+        <is>
+          <t>【Maison Margiela】梅森马吉拉 慵懒周末身体乳 滋润芳香200ml/400ml</t>
+        </is>
+      </c>
+      <c r="D886" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="E886" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="F886" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G886" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H886" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I886" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J886" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:21:19</t>
+        </is>
+      </c>
+      <c r="K886" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="n">
+        <v>886</v>
+      </c>
+      <c r="B887" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】Maison Margiela/梅森马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D887" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G887" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H887" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I887" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J887" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:21:33</t>
+        </is>
+      </c>
+      <c r="K887" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="inlineStr">
+        <is>
+          <t>【正品原装】Maison Margiela/梅森马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D888" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="E888" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="F888" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G888" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H888" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I888" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J888" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:21:46</t>
+        </is>
+      </c>
+      <c r="K888" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="n">
+        <v>888</v>
+      </c>
+      <c r="B889" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水粉底 PO01正装30ml养肤柔光新款水润水啵啵【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="D889" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G889" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H889" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I889" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J889" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:23:33</t>
+        </is>
+      </c>
+      <c r="K889" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="n">
+        <v>889</v>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】水粉底养肤柔光粉底液PO-01#30ml水啵啵干皮持妆遮瑕</t>
+        </is>
+      </c>
+      <c r="D890" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E890" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G890" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H890" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I890" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J890" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:23:46</t>
+        </is>
+      </c>
+      <c r="K890" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n">
+        <v>890</v>
+      </c>
+      <c r="B891" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】水粉底养肤柔光粉底液PO-03#30ml正装P01水啵啵PO-01持妆遮瑕</t>
+        </is>
+      </c>
+      <c r="D891" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E891" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G891" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H891" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I891" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J891" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:23:57</t>
+        </is>
+      </c>
+      <c r="K891" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="n">
+        <v>891</v>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>【Kiehl's】科颜氏男士保湿乳液125ml活力清爽控油补水收缩毛孔送男友</t>
+        </is>
+      </c>
+      <c r="D892" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="E892" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G892" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H892" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I892" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J892" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:25:25</t>
+        </is>
+      </c>
+      <c r="K892" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="n">
+        <v>892</v>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="inlineStr">
+        <is>
+          <t>【科颜氏】男士保湿乳液125ml补水保湿清爽改善暗沉礼物</t>
+        </is>
+      </c>
+      <c r="D893" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="E893" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G893" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H893" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I893" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J893" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:25:42</t>
+        </is>
+      </c>
+      <c r="K893" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="n">
+        <v>893</v>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】科颜氏Kiehl高保湿清爽凝霜滋润补水果冻面霜50ml</t>
+        </is>
+      </c>
+      <c r="D894" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="E894" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G894" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H894" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I894" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J894" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 16:27:12</t>
+        </is>
+      </c>
+      <c r="K894" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/商品校验调试记录.xlsx
+++ b/商品校验调试记录.xlsx
@@ -442,11 +442,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M730"/>
+  <dimension ref="A1:M883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -455,7 +455,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="33" customWidth="1" min="11" max="11"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
   </cols>
@@ -36205,10 +36205,8 @@
           <t>已选择： 100mL 绮梦香草兰女士香水 1瓶 古驰绮梦香草兰</t>
         </is>
       </c>
-      <c r="M675" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+      <c r="M675" s="2" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="676">
@@ -36264,10 +36262,8 @@
           <t>已选择： 100mL 古驰 绮梦香草兰 浓香 个人款</t>
         </is>
       </c>
-      <c r="M676" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
+      <c r="M676" s="2" t="n">
+        <v>532</v>
       </c>
     </row>
     <row r="677">
@@ -36429,10 +36425,8 @@
           <t>已选择： 洗发水250ml  两瓶</t>
         </is>
       </c>
-      <c r="M679" s="2" t="inlineStr">
-        <is>
-          <t>317.98</t>
-        </is>
+      <c r="M679" s="2" t="n">
+        <v>317.98</v>
       </c>
     </row>
     <row r="680">
@@ -36590,10 +36584,8 @@
           <t>已选择： 新肌水200ml*2</t>
         </is>
       </c>
-      <c r="M682" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
+      <c r="M682" s="2" t="n">
+        <v>989</v>
       </c>
     </row>
     <row r="683">
@@ -36802,10 +36794,8 @@
           <t>已选择： 骨胶原乳液100g</t>
         </is>
       </c>
-      <c r="M686" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
+      <c r="M686" s="2" t="n">
+        <v>432</v>
       </c>
     </row>
     <row r="687">
@@ -37277,10 +37267,8 @@
           <t>已选择： 大红瓶经典面霜滋润版80g</t>
         </is>
       </c>
-      <c r="M695" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
+      <c r="M695" s="2" t="n">
+        <v>701</v>
       </c>
     </row>
     <row r="696">
@@ -37540,10 +37528,8 @@
           <t>已选择： 吉普赛GIPSY#684 7.5mL</t>
         </is>
       </c>
-      <c r="M700" s="2" t="inlineStr">
-        <is>
-          <t>69.8</t>
-        </is>
+      <c r="M700" s="2" t="n">
+        <v>69.8</v>
       </c>
     </row>
     <row r="701">
@@ -37603,10 +37589,8 @@
           <t>已选择： 684 Gipsy 吉普赛玫瑰 7.5mL 【23年4月产】国际效期5年</t>
         </is>
       </c>
-      <c r="M701" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="M701" s="2" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="702">
@@ -37815,10 +37799,8 @@
           <t>已选择： 后黄金气垫13g*3【21号】</t>
         </is>
       </c>
-      <c r="M705" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+      <c r="M705" s="2" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="706">
@@ -38086,10 +38068,8 @@
           <t>已选择： 新版光子小灯泡75ml【正品保证】</t>
         </is>
       </c>
-      <c r="M710" s="2" t="inlineStr">
-        <is>
-          <t>1398</t>
-        </is>
+      <c r="M710" s="2" t="n">
+        <v>1398</v>
       </c>
     </row>
     <row r="711">
@@ -38408,10 +38388,8 @@
           <t>已选择： 复古丝绒 N37 6.5mL</t>
         </is>
       </c>
-      <c r="M716" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="M716" s="2" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="717">
@@ -38518,10 +38496,8 @@
           <t>已选择： 440 野玫瑰 5.5mL</t>
         </is>
       </c>
-      <c r="M718" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="M718" s="2" t="n">
+        <v>156</v>
       </c>
     </row>
     <row r="719">
@@ -39139,6 +39115,8335 @@
       <c r="K730" s="2" t="inlineStr"/>
       <c r="L730" s="2" t="inlineStr"/>
       <c r="M730" s="2" t="inlineStr"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="n">
+        <v>730</v>
+      </c>
+      <c r="B731" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="C731" s="2" t="inlineStr">
+        <is>
+          <t>【42.1万人收藏该品牌】FRESH/馥蕾诗玫瑰花瓣水250ml*2瓶</t>
+        </is>
+      </c>
+      <c r="D731" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E731" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F731" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G731" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H731" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I731" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J731" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:23:16</t>
+        </is>
+      </c>
+      <c r="K731" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+      <c r="L731" s="2" t="inlineStr"/>
+      <c r="M731" s="2" t="inlineStr"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="n">
+        <v>731</v>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="inlineStr">
+        <is>
+          <t>超粘超软 JNM GL70Ultra 升级款羽毛球拍手胶吸汗防滑减震</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E732" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F732" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G732" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H732" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I732" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J732" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:23:42</t>
+        </is>
+      </c>
+      <c r="K732" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+      <c r="L732" s="2" t="inlineStr"/>
+      <c r="M732" s="2" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="n">
+        <v>732</v>
+      </c>
+      <c r="B733" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="C733" s="2" t="inlineStr">
+        <is>
+          <t>【馥蕾诗】 大马士革玫瑰花瓣润泽密集保湿爽肤水400ml高保湿深层滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D733" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E733" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F733" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G733" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H733" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I733" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J733" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:24:04</t>
+        </is>
+      </c>
+      <c r="K733" s="2" t="inlineStr"/>
+      <c r="L733" s="2" t="inlineStr"/>
+      <c r="M733" s="2" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗玫瑰花瓣水250ml大马士革玫瑰润泽保湿爽肤水调理肌肤【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E734" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F734" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G734" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H734" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I734" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J734" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:24:22</t>
+        </is>
+      </c>
+      <c r="K734" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+      <c r="L734" s="2" t="inlineStr"/>
+      <c r="M734" s="2" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="n">
+        <v>734</v>
+      </c>
+      <c r="B735" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶紧致面霜50ml</t>
+        </is>
+      </c>
+      <c r="C735" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】馥蕾诗红茶凝时焕活面霜50ml淡纹紧致增加光泽</t>
+        </is>
+      </c>
+      <c r="D735" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E735" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F735" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G735" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H735" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I735" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J735" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:25:56</t>
+        </is>
+      </c>
+      <c r="K735" s="2" t="inlineStr"/>
+      <c r="L735" s="2" t="inlineStr"/>
+      <c r="M735" s="2" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="n">
+        <v>735</v>
+      </c>
+      <c r="B736" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗睡莲日霜50ml</t>
+        </is>
+      </c>
+      <c r="C736" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗青春赋活面霜日霜紧致肌肤抗皱提亮深度保湿香港仓发【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E736" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F736" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G736" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H736" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I736" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J736" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:27:41</t>
+        </is>
+      </c>
+      <c r="K736" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+      <c r="L736" s="2" t="inlineStr"/>
+      <c r="M736" s="2" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="B737" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗睡莲日霜50ml</t>
+        </is>
+      </c>
+      <c r="C737" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗睡莲青春赋活面霜Lotus面霜保湿滋养修护提亮肤色50ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D737" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E737" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F737" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G737" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H737" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I737" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J737" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:28:00</t>
+        </is>
+      </c>
+      <c r="K737" s="2" t="inlineStr"/>
+      <c r="L737" s="2" t="inlineStr"/>
+      <c r="M737" s="2" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="n">
+        <v>737</v>
+      </c>
+      <c r="B738" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="C738" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗玫瑰保湿面霜50ml  密集保湿舒缓补水</t>
+        </is>
+      </c>
+      <c r="D738" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E738" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F738" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G738" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H738" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I738" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J738" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:29:34</t>
+        </is>
+      </c>
+      <c r="K738" s="2" t="inlineStr"/>
+      <c r="L738" s="2" t="inlineStr"/>
+      <c r="M738" s="2" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="n">
+        <v>738</v>
+      </c>
+      <c r="B739" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="C739" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="D739" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E739" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F739" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G739" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H739" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I739" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J739" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:31:03</t>
+        </is>
+      </c>
+      <c r="K739" s="2" t="inlineStr"/>
+      <c r="L739" s="2" t="inlineStr"/>
+      <c r="M739" s="2" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="n">
+        <v>739</v>
+      </c>
+      <c r="B740" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="C740" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="D740" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E740" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F740" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G740" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H740" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I740" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J740" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:31:24</t>
+        </is>
+      </c>
+      <c r="K740" s="2" t="inlineStr"/>
+      <c r="L740" s="2" t="inlineStr"/>
+      <c r="M740" s="2" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="B741" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="C741" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="D741" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E741" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F741" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G741" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H741" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I741" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J741" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:31:44</t>
+        </is>
+      </c>
+      <c r="K741" s="2" t="inlineStr"/>
+      <c r="L741" s="2" t="inlineStr"/>
+      <c r="M741" s="2" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="n">
+        <v>741</v>
+      </c>
+      <c r="B742" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="C742" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛白金级养肤粉底液宝石粉底光感保湿透亮遮瑕</t>
+        </is>
+      </c>
+      <c r="D742" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E742" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F742" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G742" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H742" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I742" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J742" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:33:16</t>
+        </is>
+      </c>
+      <c r="K742" s="2" t="inlineStr"/>
+      <c r="L742" s="2" t="inlineStr"/>
+      <c r="M742" s="2" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="n">
+        <v>742</v>
+      </c>
+      <c r="B743" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="C743" s="2" t="inlineStr">
+        <is>
+          <t>【专柜行货】雅诗兰黛白金养肤粉底液 持久遮瑕保湿抗氧化服帖</t>
+        </is>
+      </c>
+      <c r="D743" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E743" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F743" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G743" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H743" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I743" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J743" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:33:28</t>
+        </is>
+      </c>
+      <c r="K743" s="2" t="inlineStr"/>
+      <c r="L743" s="2" t="inlineStr"/>
+      <c r="M743" s="2" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="n">
+        <v>743</v>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛白金级养肤粉底液宝石粉底光感保湿透亮遮瑕</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E744" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F744" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G744" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H744" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I744" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J744" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:33:46</t>
+        </is>
+      </c>
+      <c r="K744" s="2" t="inlineStr"/>
+      <c r="L744" s="2" t="inlineStr"/>
+      <c r="M744" s="2" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="n">
+        <v>744</v>
+      </c>
+      <c r="B745" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶精粹水250ml</t>
+        </is>
+      </c>
+      <c r="C745" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗酵母酵萃红茶水250ml保湿补水清爽滋润爽肤水精华水</t>
+        </is>
+      </c>
+      <c r="D745" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="E745" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗</t>
+        </is>
+      </c>
+      <c r="F745" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G745" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H745" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I745" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J745" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:36:14</t>
+        </is>
+      </c>
+      <c r="K745" s="2" t="inlineStr"/>
+      <c r="L745" s="2" t="inlineStr"/>
+      <c r="M745" s="2" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="n">
+        <v>745</v>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1CO</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】白金粉底液1C0养肤透亮持久保湿遮瑕服帖【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E746" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F746" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G746" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H746" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I746" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J746" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:37:55</t>
+        </is>
+      </c>
+      <c r="K746" s="2" t="inlineStr"/>
+      <c r="L746" s="2" t="inlineStr"/>
+      <c r="M746" s="2" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="n">
+        <v>746</v>
+      </c>
+      <c r="B747" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="C747" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗牛奶水减黄提亮美白淡斑清爽200ml保湿细腻</t>
+        </is>
+      </c>
+      <c r="D747" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E747" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F747" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G747" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H747" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I747" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J747" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:39:32</t>
+        </is>
+      </c>
+      <c r="K747" s="2" t="inlineStr"/>
+      <c r="L747" s="2" t="inlineStr"/>
+      <c r="M747" s="2" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="n">
+        <v>747</v>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>CLARINS/娇韵诗焕颜紧致弹簧霜晚霜 50ml修护提亮 娇韵诗弹簧晚霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E748" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F748" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G748" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H748" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I748" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J748" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:41:19</t>
+        </is>
+      </c>
+      <c r="K748" s="2" t="inlineStr"/>
+      <c r="L748" s="2" t="inlineStr"/>
+      <c r="M748" s="2" t="inlineStr"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="n">
+        <v>748</v>
+      </c>
+      <c r="B749" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C749" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D749" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E749" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F749" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G749" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H749" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I749" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J749" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:41:34</t>
+        </is>
+      </c>
+      <c r="K749" s="2" t="inlineStr"/>
+      <c r="L749" s="2" t="inlineStr"/>
+      <c r="M749" s="2" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>【正品】娇韵诗焕颜紧致弹簧晚霜淡纹胶原回弹滋润抗皱面霜女50ml</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E750" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F750" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H750" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I750" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J750" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:41:49</t>
+        </is>
+      </c>
+      <c r="K750" s="2" t="inlineStr"/>
+      <c r="L750" s="2" t="inlineStr"/>
+      <c r="M750" s="2" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="B751" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C751" s="2" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D751" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E751" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F751" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G751" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H751" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I751" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J751" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:43:39</t>
+        </is>
+      </c>
+      <c r="K751" s="2" t="inlineStr"/>
+      <c r="L751" s="2" t="inlineStr"/>
+      <c r="M751" s="2" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="n">
+        <v>751</v>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E752" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F752" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H752" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I752" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J752" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:43:54</t>
+        </is>
+      </c>
+      <c r="K752" s="2" t="inlineStr"/>
+      <c r="L752" s="2" t="inlineStr"/>
+      <c r="M752" s="2" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="n">
+        <v>752</v>
+      </c>
+      <c r="B753" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="C753" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】娇韵诗焕颜弹力晚霜面霜50ml保湿提拉紧致滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D753" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E753" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F753" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G753" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H753" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I753" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J753" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:44:09</t>
+        </is>
+      </c>
+      <c r="K753" s="2" t="inlineStr"/>
+      <c r="L753" s="2" t="inlineStr"/>
+      <c r="M753" s="2" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】多效智妍面霜(清爽版)75ml双支</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E754" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F754" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G754" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H754" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I754" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J754" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:45:42</t>
+        </is>
+      </c>
+      <c r="K754" s="2" t="inlineStr"/>
+      <c r="L754" s="2" t="inlineStr"/>
+      <c r="M754" s="2" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="n">
+        <v>754</v>
+      </c>
+      <c r="B755" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="C755" s="2" t="inlineStr">
+        <is>
+          <t>【梅森马吉拉】慵懒周末身体乳200ml润肤乳保湿补水</t>
+        </is>
+      </c>
+      <c r="D755" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="E755" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="F755" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G755" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H755" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I755" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J755" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:47:50</t>
+        </is>
+      </c>
+      <c r="K755" s="2" t="inlineStr"/>
+      <c r="L755" s="2" t="inlineStr"/>
+      <c r="M755" s="2" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻新款持妆粉底液30ml PO-01</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E756" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F756" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G756" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H756" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I756" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J756" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:49:42</t>
+        </is>
+      </c>
+      <c r="K756" s="2" t="inlineStr"/>
+      <c r="L756" s="2" t="inlineStr"/>
+      <c r="M756" s="2" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="n">
+        <v>756</v>
+      </c>
+      <c r="B757" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="C757" s="2" t="inlineStr">
+        <is>
+          <t>【Kiehl's】科颜氏男士保湿乳液125ml活力清爽控油补水收缩毛孔送男友</t>
+        </is>
+      </c>
+      <c r="D757" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="E757" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="F757" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G757" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H757" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I757" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J757" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:51:13</t>
+        </is>
+      </c>
+      <c r="K757" s="2" t="inlineStr"/>
+      <c r="L757" s="2" t="inlineStr"/>
+      <c r="M757" s="2" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="n">
+        <v>757</v>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="inlineStr">
+        <is>
+          <t>【科颜氏】男士保湿乳液125ml补水保湿清爽改善暗沉</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="E758" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="F758" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G758" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H758" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I758" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J758" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:51:29</t>
+        </is>
+      </c>
+      <c r="K758" s="2" t="inlineStr"/>
+      <c r="L758" s="2" t="inlineStr"/>
+      <c r="M758" s="2" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="B759" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="C759" s="2" t="inlineStr">
+        <is>
+          <t>【科颜氏】男士保湿乳液125ml补水保湿清爽改善暗沉礼物</t>
+        </is>
+      </c>
+      <c r="D759" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="E759" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="F759" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G759" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H759" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I759" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J759" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:51:49</t>
+        </is>
+      </c>
+      <c r="K759" s="2" t="inlineStr"/>
+      <c r="L759" s="2" t="inlineStr"/>
+      <c r="M759" s="2" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="n">
+        <v>759</v>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评322.1万+条】Kiehl's/科颜氏男士活力保湿乳液125ml补水保湿润肤改善干燥</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="E760" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="F760" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G760" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H760" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I760" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J760" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:52:07</t>
+        </is>
+      </c>
+      <c r="K760" s="2" t="inlineStr"/>
+      <c r="L760" s="2" t="inlineStr"/>
+      <c r="M760" s="2" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="n">
+        <v>760</v>
+      </c>
+      <c r="B761" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
+        </is>
+      </c>
+      <c r="C761" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】科颜氏Kiehl高保湿清爽凝霜滋润补水果冻面霜50ml</t>
+        </is>
+      </c>
+      <c r="D761" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="E761" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏</t>
+        </is>
+      </c>
+      <c r="F761" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G761" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H761" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I761" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J761" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:53:42</t>
+        </is>
+      </c>
+      <c r="K761" s="2" t="inlineStr"/>
+      <c r="L761" s="2" t="inlineStr"/>
+      <c r="M761" s="2" t="inlineStr"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="n">
+        <v>761</v>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗第九代全新双萃焕活修护精华 100ML</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】双萃焕活修护精华露100ml清爽九代补水</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E762" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F762" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G762" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H762" s="3" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="I762" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J762" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:55:20</t>
+        </is>
+      </c>
+      <c r="K762" s="2" t="inlineStr"/>
+      <c r="L762" s="2" t="inlineStr"/>
+      <c r="M762" s="2" t="inlineStr"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="n">
+        <v>762</v>
+      </c>
+      <c r="B763" s="2" t="inlineStr">
+        <is>
+          <t>资生堂安耐晒90ml</t>
+        </is>
+      </c>
+      <c r="C763" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】安耐晒防晒霜安热沙隔离小金瓶90ml防水防汗资生堂女</t>
+        </is>
+      </c>
+      <c r="D763" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E763" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F763" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G763" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H763" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I763" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J763" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:56:53</t>
+        </is>
+      </c>
+      <c r="K763" s="2" t="inlineStr"/>
+      <c r="L763" s="2" t="inlineStr"/>
+      <c r="M763" s="2" t="inlineStr"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="n">
+        <v>763</v>
+      </c>
+      <c r="B764" s="2" t="inlineStr">
+        <is>
+          <t>资生堂安耐晒90ml</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂安耐晒防晒霜清爽不油面部防紫外线敏感肌正品</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E764" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F764" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G764" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H764" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I764" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J764" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:57:19</t>
+        </is>
+      </c>
+      <c r="K764" s="2" t="inlineStr"/>
+      <c r="L764" s="2" t="inlineStr">
+        <is>
+          <t>已选: 软管90ml [盒装版]防晒霜+绵羊乳霜6g</t>
+        </is>
+      </c>
+      <c r="M764" s="2" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="n">
+        <v>764</v>
+      </c>
+      <c r="B765" s="2" t="inlineStr">
+        <is>
+          <t>资生堂安耐晒90ml</t>
+        </is>
+      </c>
+      <c r="C765" s="2" t="inlineStr">
+        <is>
+          <t>【保税原装】资生堂安耐晒防晒霜安热沙防晒霜小金瓶防水防汗隔离</t>
+        </is>
+      </c>
+      <c r="D765" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E765" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F765" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G765" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H765" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I765" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J765" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:57:46</t>
+        </is>
+      </c>
+      <c r="K765" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L765" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M765" s="2" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="n">
+        <v>765</v>
+      </c>
+      <c r="B766" s="2" t="inlineStr">
+        <is>
+          <t>资生堂安耐晒90ml</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="inlineStr">
+        <is>
+          <t>【保税原装】资生堂安耐晒防晒霜紫外线防水防汗防晒乳隔离霜正品</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E766" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F766" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G766" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H766" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I766" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J766" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:58:16</t>
+        </is>
+      </c>
+      <c r="K766" s="2" t="inlineStr"/>
+      <c r="L766" s="2" t="inlineStr">
+        <is>
+          <t>已选: [原装保税]防晒霜90ml+面霜乳6g</t>
+        </is>
+      </c>
+      <c r="M766" s="2" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="n">
+        <v>766</v>
+      </c>
+      <c r="B767" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒金钻高效防晒90ml</t>
+        </is>
+      </c>
+      <c r="C767" s="2" t="inlineStr">
+        <is>
+          <t>【20.9万人回购该品牌】ANESSA/安热沙/安耐晒小金瓶防晒霜60ML</t>
+        </is>
+      </c>
+      <c r="D767" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒</t>
+        </is>
+      </c>
+      <c r="E767" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒</t>
+        </is>
+      </c>
+      <c r="F767" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G767" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H767" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I767" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J767" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:59:52</t>
+        </is>
+      </c>
+      <c r="K767" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L767" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M767" s="2" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="n">
+        <v>767</v>
+      </c>
+      <c r="B768" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒金钻高效防晒90ml</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="inlineStr">
+        <is>
+          <t>安热沙Anessa安耐晒防晒霜面部防晒男女军训防晒清爽防晒小金软管【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒</t>
+        </is>
+      </c>
+      <c r="E768" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒</t>
+        </is>
+      </c>
+      <c r="F768" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G768" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H768" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I768" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J768" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 12:00:18</t>
+        </is>
+      </c>
+      <c r="K768" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L768" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M768" s="2" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="B769" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒金钻高效防晒90ml</t>
+        </is>
+      </c>
+      <c r="C769" s="2" t="inlineStr">
+        <is>
+          <t>【保税原装】安耐晒安热沙防晒霜90ml水润清爽防水防汗户外小金瓶</t>
+        </is>
+      </c>
+      <c r="D769" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒</t>
+        </is>
+      </c>
+      <c r="E769" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒</t>
+        </is>
+      </c>
+      <c r="F769" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G769" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H769" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I769" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J769" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 12:00:34</t>
+        </is>
+      </c>
+      <c r="K769" s="2" t="inlineStr"/>
+      <c r="L769" s="2" t="inlineStr"/>
+      <c r="M769" s="2" t="inlineStr"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="n">
+        <v>769</v>
+      </c>
+      <c r="B770" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒金钻高效防晒90ml</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="inlineStr">
+        <is>
+          <t>【20.9万人回购该品牌】ANESSA/安热沙/安耐晒小金瓶防晒霜60ML</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒</t>
+        </is>
+      </c>
+      <c r="E770" s="2" t="inlineStr">
+        <is>
+          <t>安耐晒</t>
+        </is>
+      </c>
+      <c r="F770" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G770" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H770" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I770" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J770" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 12:01:00</t>
+        </is>
+      </c>
+      <c r="K770" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L770" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M770" s="2" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="B771" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛樱花微精华原生液400ml</t>
+        </is>
+      </c>
+      <c r="C771" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛樱花微精华原生液400ml 肌肤赋活保湿滋润提亮修护爽肤水【12天内发货】</t>
+        </is>
+      </c>
+      <c r="D771" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E771" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F771" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G771" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H771" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I771" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J771" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 12:02:51</t>
+        </is>
+      </c>
+      <c r="K771" s="2" t="inlineStr"/>
+      <c r="L771" s="2" t="inlineStr"/>
+      <c r="M771" s="2" t="inlineStr"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="n">
+        <v>771</v>
+      </c>
+      <c r="B772" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛樱花微精华原生液400ml</t>
+        </is>
+      </c>
+      <c r="C772" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】樱花微精华原生液400ml肌肤赋活保湿滋润提亮修护爽肤水【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D772" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E772" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F772" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G772" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H772" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I772" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J772" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 12:03:07</t>
+        </is>
+      </c>
+      <c r="K772" s="2" t="inlineStr"/>
+      <c r="L772" s="2" t="inlineStr"/>
+      <c r="M772" s="2" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="n">
+        <v>772</v>
+      </c>
+      <c r="B773" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛樱花微精华原生液400ml</t>
+        </is>
+      </c>
+      <c r="C773" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】樱花水微精华原生液补水保湿提亮肤色收缩毛孔湿敷精华水</t>
+        </is>
+      </c>
+      <c r="D773" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E773" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F773" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G773" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H773" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I773" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J773" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 12:03:27</t>
+        </is>
+      </c>
+      <c r="K773" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L773" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M773" s="2" t="inlineStr"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="n">
+        <v>773</v>
+      </c>
+      <c r="B774" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰小金条细管口红21号复古正红色</t>
+        </is>
+      </c>
+      <c r="C774" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰口红小金条21复古红小黑条大牌杨树林哑光</t>
+        </is>
+      </c>
+      <c r="D774" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E774" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F774" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G774" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H774" s="3" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="I774" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J774" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 12:04:59</t>
+        </is>
+      </c>
+      <c r="K774" s="2" t="inlineStr"/>
+      <c r="L774" s="2" t="inlineStr"/>
+      <c r="M774" s="2" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="n">
+        <v>774</v>
+      </c>
+      <c r="B775" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰小金条细管口红21号复古正红色</t>
+        </is>
+      </c>
+      <c r="C775" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰口红小金条 21复古红显白大牌正品礼盒装</t>
+        </is>
+      </c>
+      <c r="D775" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E775" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F775" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G775" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H775" s="3" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="I775" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J775" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 12:05:18</t>
+        </is>
+      </c>
+      <c r="K775" s="2" t="inlineStr"/>
+      <c r="L775" s="2" t="inlineStr"/>
+      <c r="M775" s="2" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="n">
+        <v>775</v>
+      </c>
+      <c r="B776" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗清润舒盈新版卸妆油200ml/瓶 温和卸妆</t>
+        </is>
+      </c>
+      <c r="D776" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗</t>
+        </is>
+      </c>
+      <c r="E776" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗</t>
+        </is>
+      </c>
+      <c r="F776" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G776" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H776" s="3" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="I776" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J776" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:26:51</t>
+        </is>
+      </c>
+      <c r="K776" s="2" t="inlineStr"/>
+      <c r="L776" s="2" t="inlineStr"/>
+      <c r="M776" s="2" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="n">
+        <v>776</v>
+      </c>
+      <c r="B777" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+        </is>
+      </c>
+      <c r="C777" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗清润舒盈新版卸妆油200ml 温和卸妆</t>
+        </is>
+      </c>
+      <c r="D777" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗</t>
+        </is>
+      </c>
+      <c r="E777" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗</t>
+        </is>
+      </c>
+      <c r="F777" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G777" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H777" s="3" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="I777" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J777" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:27:12</t>
+        </is>
+      </c>
+      <c r="K777" s="2" t="inlineStr"/>
+      <c r="L777" s="2" t="inlineStr"/>
+      <c r="M777" s="2" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="n">
+        <v>777</v>
+      </c>
+      <c r="B778" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="inlineStr">
+        <is>
+          <t>两瓶 单品 芭比布朗清透舒盈卸妆油200ml/瓶</t>
+        </is>
+      </c>
+      <c r="D778" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗</t>
+        </is>
+      </c>
+      <c r="E778" s="2" t="inlineStr">
+        <is>
+          <t>芭比布朗</t>
+        </is>
+      </c>
+      <c r="F778" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G778" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H778" s="3" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="I778" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J778" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:27:29</t>
+        </is>
+      </c>
+      <c r="K778" s="2" t="inlineStr"/>
+      <c r="L778" s="2" t="inlineStr"/>
+      <c r="M778" s="2" t="inlineStr"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="n">
+        <v>778</v>
+      </c>
+      <c r="B779" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗双萃焕活修护精华露100ml</t>
+        </is>
+      </c>
+      <c r="C779" s="2" t="inlineStr">
+        <is>
+          <t>【海外直采】顺丰Clarins娇韵诗第九代双萃赋活精华露100ml</t>
+        </is>
+      </c>
+      <c r="D779" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E779" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F779" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G779" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H779" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I779" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J779" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:29:04</t>
+        </is>
+      </c>
+      <c r="K779" s="2" t="inlineStr"/>
+      <c r="L779" s="2" t="inlineStr"/>
+      <c r="M779" s="2" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="n">
+        <v>779</v>
+      </c>
+      <c r="B780" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗双萃焕活修护精华露100ml</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】双萃焕活修护精华露100ml清爽九代补水</t>
+        </is>
+      </c>
+      <c r="D780" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="E780" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗</t>
+        </is>
+      </c>
+      <c r="F780" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G780" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H780" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I780" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J780" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:29:27</t>
+        </is>
+      </c>
+      <c r="K780" s="2" t="inlineStr"/>
+      <c r="L780" s="2" t="inlineStr"/>
+      <c r="M780" s="2" t="inlineStr"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="n">
+        <v>780</v>
+      </c>
+      <c r="B781" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力口红410色</t>
+        </is>
+      </c>
+      <c r="C781" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】权利红黑管唇膏410瞩目绯红3.1g 显白提气色口红【26年8月</t>
+        </is>
+      </c>
+      <c r="D781" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E781" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F781" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G781" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H781" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I781" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J781" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:31:06</t>
+        </is>
+      </c>
+      <c r="K781" s="2" t="inlineStr"/>
+      <c r="L781" s="2" t="inlineStr"/>
+      <c r="M781" s="2" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="n">
+        <v>781</v>
+      </c>
+      <c r="B782" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管13色</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】ysl/圣罗兰大牌口红nm裸缪斯黑金浮雕方管大牌礼盒装</t>
+        </is>
+      </c>
+      <c r="D782" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E782" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F782" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G782" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H782" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I782" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J782" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:32:43</t>
+        </is>
+      </c>
+      <c r="K782" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L782" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M782" s="2" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="n">
+        <v>782</v>
+      </c>
+      <c r="B783" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管13色</t>
+        </is>
+      </c>
+      <c r="C783" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰黑金浮雕方管大牌口红R1966杨树林唇膏正品</t>
+        </is>
+      </c>
+      <c r="D783" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E783" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F783" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G783" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H783" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I783" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J783" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:33:11</t>
+        </is>
+      </c>
+      <c r="K783" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L783" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M783" s="2" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="B784" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管13色</t>
+        </is>
+      </c>
+      <c r="C784" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰黑金方管口红 釉光新品10/06/11 裸色温柔</t>
+        </is>
+      </c>
+      <c r="D784" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E784" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F784" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G784" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H784" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I784" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J784" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:33:29</t>
+        </is>
+      </c>
+      <c r="K784" s="2" t="inlineStr"/>
+      <c r="L784" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 推荐#13-偏执</t>
+        </is>
+      </c>
+      <c r="M784" s="2" t="n">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="n">
+        <v>784</v>
+      </c>
+      <c r="B785" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管13色</t>
+        </is>
+      </c>
+      <c r="C785" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】ysl/圣罗兰大牌口红nm裸缪斯黑金浮雕方管大牌礼盒装</t>
+        </is>
+      </c>
+      <c r="D785" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E785" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F785" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G785" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H785" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I785" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J785" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:33:57</t>
+        </is>
+      </c>
+      <c r="K785" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L785" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M785" s="2" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="n">
+        <v>785</v>
+      </c>
+      <c r="B786" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="C786" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉440 610 416 622限定浮雕黑管</t>
+        </is>
+      </c>
+      <c r="D786" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E786" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F786" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G786" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H786" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I786" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J786" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:35:47</t>
+        </is>
+      </c>
+      <c r="K786" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L786" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M786" s="2" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="n">
+        <v>786</v>
+      </c>
+      <c r="B787" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="C787" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D787" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E787" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F787" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G787" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H787" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I787" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J787" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:36:17</t>
+        </is>
+      </c>
+      <c r="K787" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L787" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M787" s="2" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="n">
+        <v>787</v>
+      </c>
+      <c r="B788" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰黑金浮雕方管大牌口红R1966杨树林唇膏正品</t>
+        </is>
+      </c>
+      <c r="D788" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E788" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F788" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G788" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H788" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I788" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J788" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:36:47</t>
+        </is>
+      </c>
+      <c r="K788" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L788" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M788" s="2" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="n">
+        <v>788</v>
+      </c>
+      <c r="B789" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="C789" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新黑金方管口红 缎光质地显白</t>
+        </is>
+      </c>
+      <c r="D789" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E789" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F789" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G789" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H789" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I789" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J789" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:37:09</t>
+        </is>
+      </c>
+      <c r="K789" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L789" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M789" s="2" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="n">
+        <v>789</v>
+      </c>
+      <c r="B790" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="C790" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】圣罗兰/YSL方管口红黑金浮雕NM裸缪斯大牌正品礼盒装</t>
+        </is>
+      </c>
+      <c r="D790" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E790" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F790" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G790" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H790" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I790" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J790" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:37:31</t>
+        </is>
+      </c>
+      <c r="K790" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L790" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M790" s="2" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="2" t="n">
+        <v>790</v>
+      </c>
+      <c r="B791" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="C791" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉440 610 416 622限定浮雕黑管</t>
+        </is>
+      </c>
+      <c r="D791" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E791" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F791" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G791" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H791" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I791" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J791" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:39:19</t>
+        </is>
+      </c>
+      <c r="K791" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L791" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M791" s="2" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="n">
+        <v>791</v>
+      </c>
+      <c r="B792" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="C792" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰全新黑管唇釉610 416 442 443爱心限量版</t>
+        </is>
+      </c>
+      <c r="D792" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E792" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F792" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G792" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H792" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I792" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J792" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:39:42</t>
+        </is>
+      </c>
+      <c r="K792" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L792" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M792" s="2" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="2" t="n">
+        <v>792</v>
+      </c>
+      <c r="B793" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="C793" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰口红1966小金条314小黑条杨树林大牌正品</t>
+        </is>
+      </c>
+      <c r="D793" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E793" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F793" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G793" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H793" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I793" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J793" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:40:05</t>
+        </is>
+      </c>
+      <c r="K793" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=25.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L793" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M793" s="2" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="n">
+        <v>793</v>
+      </c>
+      <c r="B794" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="C794" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰口红碎花25金管哑光滋润505大牌正品礼物</t>
+        </is>
+      </c>
+      <c r="D794" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E794" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F794" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G794" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H794" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I794" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J794" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:40:31</t>
+        </is>
+      </c>
+      <c r="K794" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L794" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M794" s="2" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="n">
+        <v>794</v>
+      </c>
+      <c r="B795" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="C795" s="2" t="inlineStr">
+        <is>
+          <t>YSL/圣罗兰黑金浮雕方管釉光滋润质感唇膏口红06偏见高定礼盒包装</t>
+        </is>
+      </c>
+      <c r="D795" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E795" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F795" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G795" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H795" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I795" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J795" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:40:58</t>
+        </is>
+      </c>
+      <c r="K795" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L795" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M795" s="2" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="n">
+        <v>795</v>
+      </c>
+      <c r="B796" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="C796" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰黑金浮雕方管唇膏口红1968透视1971 14 11礼盒装520礼物</t>
+        </is>
+      </c>
+      <c r="D796" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E796" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F796" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G796" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H796" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I796" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J796" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:41:15</t>
+        </is>
+      </c>
+      <c r="K796" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L796" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M796" s="2" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="n">
+        <v>796</v>
+      </c>
+      <c r="B797" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="C797" s="2" t="inlineStr">
+        <is>
+          <t>YSL/圣罗兰黑金浮雕方管釉光唇膏口红1971流言06裸缪斯NM1968正品</t>
+        </is>
+      </c>
+      <c r="D797" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E797" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F797" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G797" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H797" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I797" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J797" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:41:34</t>
+        </is>
+      </c>
+      <c r="K797" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L797" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M797" s="2" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="n">
+        <v>797</v>
+      </c>
+      <c r="B798" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰银管02色</t>
+        </is>
+      </c>
+      <c r="C798" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰啵啵丰盈唇冻光耀丰盈唇釉银盖日常通勤提升气色6ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D798" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E798" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F798" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G798" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H798" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I798" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J798" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:43:11</t>
+        </is>
+      </c>
+      <c r="K798" s="2" t="inlineStr"/>
+      <c r="L798" s="2" t="inlineStr">
+        <is>
+          <t>已选择： YSL啵啵唇冻#02 霜冻粉色 6mL</t>
+        </is>
+      </c>
+      <c r="M798" s="2" t="n">
+        <v>112.1</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="n">
+        <v>798</v>
+      </c>
+      <c r="B799" s="2" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="C799" s="2" t="inlineStr">
+        <is>
+          <t>【Clinique】倩碧黄油滋润(有油)125ml</t>
+        </is>
+      </c>
+      <c r="D799" s="2" t="inlineStr">
+        <is>
+          <t>倩碧</t>
+        </is>
+      </c>
+      <c r="E799" s="2" t="inlineStr">
+        <is>
+          <t>倩碧</t>
+        </is>
+      </c>
+      <c r="F799" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G799" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H799" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I799" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J799" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:44:42</t>
+        </is>
+      </c>
+      <c r="K799" s="2" t="inlineStr"/>
+      <c r="L799" s="2" t="inlineStr"/>
+      <c r="M799" s="2" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="B800" s="2" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="C800" s="2" t="inlineStr">
+        <is>
+          <t>【Clinique】倩碧黄油滋润(有油)125ml</t>
+        </is>
+      </c>
+      <c r="D800" s="2" t="inlineStr">
+        <is>
+          <t>倩碧</t>
+        </is>
+      </c>
+      <c r="E800" s="2" t="inlineStr">
+        <is>
+          <t>倩碧</t>
+        </is>
+      </c>
+      <c r="F800" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G800" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H800" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I800" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J800" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:45:03</t>
+        </is>
+      </c>
+      <c r="K800" s="2" t="inlineStr"/>
+      <c r="L800" s="2" t="inlineStr"/>
+      <c r="M800" s="2" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="B801" s="2" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="C801" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Clinique/倩碧黄油无油有油乳液保湿滋润滋养</t>
+        </is>
+      </c>
+      <c r="D801" s="2" t="inlineStr">
+        <is>
+          <t>倩碧</t>
+        </is>
+      </c>
+      <c r="E801" s="2" t="inlineStr">
+        <is>
+          <t>倩碧</t>
+        </is>
+      </c>
+      <c r="F801" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G801" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H801" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I801" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J801" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:45:27</t>
+        </is>
+      </c>
+      <c r="K801" s="2" t="inlineStr"/>
+      <c r="L801" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 倩碧黄油125ml无油</t>
+        </is>
+      </c>
+      <c r="M801" s="2" t="n">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="B802" s="2" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="C802" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Clinique/倩碧黄油无油有油乳液保湿滋润滋养125ml*2</t>
+        </is>
+      </c>
+      <c r="D802" s="2" t="inlineStr">
+        <is>
+          <t>倩碧</t>
+        </is>
+      </c>
+      <c r="E802" s="2" t="inlineStr">
+        <is>
+          <t>倩碧</t>
+        </is>
+      </c>
+      <c r="F802" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G802" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H802" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I802" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J802" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:45:49</t>
+        </is>
+      </c>
+      <c r="K802" s="2" t="inlineStr"/>
+      <c r="L802" s="2" t="inlineStr"/>
+      <c r="M802" s="2" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="2" t="n">
+        <v>802</v>
+      </c>
+      <c r="B803" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜 臻璨焕活精华油30ml （万能油）</t>
+        </is>
+      </c>
+      <c r="C803" s="2" t="inlineStr">
+        <is>
+          <t>LA MER/海蓝之谜臻璨焕活精华油30ml抗老淡纹</t>
+        </is>
+      </c>
+      <c r="D803" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="E803" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="F803" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G803" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H803" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I803" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J803" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:47:17</t>
+        </is>
+      </c>
+      <c r="K803" s="2" t="inlineStr"/>
+      <c r="L803" s="2" t="inlineStr"/>
+      <c r="M803" s="2" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="n">
+        <v>803</v>
+      </c>
+      <c r="B804" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶清爽版80g</t>
+        </is>
+      </c>
+      <c r="C804" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+        </is>
+      </c>
+      <c r="D804" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E804" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F804" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G804" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H804" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I804" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J804" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:48:49</t>
+        </is>
+      </c>
+      <c r="K804" s="2" t="inlineStr"/>
+      <c r="L804" s="2" t="inlineStr"/>
+      <c r="M804" s="2" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="2" t="n">
+        <v>804</v>
+      </c>
+      <c r="B805" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润版80g</t>
+        </is>
+      </c>
+      <c r="C805" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g 滋润版</t>
+        </is>
+      </c>
+      <c r="D805" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E805" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F805" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G805" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H805" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I805" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J805" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:50:19</t>
+        </is>
+      </c>
+      <c r="K805" s="2" t="inlineStr"/>
+      <c r="L805" s="2" t="inlineStr"/>
+      <c r="M805" s="2" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="n">
+        <v>805</v>
+      </c>
+      <c r="B806" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润版80g</t>
+        </is>
+      </c>
+      <c r="C806" s="2" t="inlineStr">
+        <is>
+          <t>SKII大红瓶面霜80g滋润版保湿紧致肌肤</t>
+        </is>
+      </c>
+      <c r="D806" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E806" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F806" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G806" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H806" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I806" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J806" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:50:40</t>
+        </is>
+      </c>
+      <c r="K806" s="2" t="inlineStr"/>
+      <c r="L806" s="2" t="inlineStr"/>
+      <c r="M806" s="2" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="2" t="n">
+        <v>806</v>
+      </c>
+      <c r="B807" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润版80g</t>
+        </is>
+      </c>
+      <c r="C807" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+        </is>
+      </c>
+      <c r="D807" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E807" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F807" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G807" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H807" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I807" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J807" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:51:01</t>
+        </is>
+      </c>
+      <c r="K807" s="2" t="inlineStr"/>
+      <c r="L807" s="2" t="inlineStr"/>
+      <c r="M807" s="2" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="n">
+        <v>807</v>
+      </c>
+      <c r="B808" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛ESTEE LAUDER新版红石榴能量水清爽型 200ML</t>
+        </is>
+      </c>
+      <c r="C808" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】新款红石榴滋润精华水200ml保湿补水</t>
+        </is>
+      </c>
+      <c r="D808" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E808" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F808" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G808" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H808" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I808" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J808" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:52:31</t>
+        </is>
+      </c>
+      <c r="K808" s="2" t="inlineStr"/>
+      <c r="L808" s="2" t="inlineStr"/>
+      <c r="M808" s="2" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="2" t="n">
+        <v>808</v>
+      </c>
+      <c r="B809" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛ESTEE LAUDER新版红石榴能量水清爽型 200ML</t>
+        </is>
+      </c>
+      <c r="C809" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】新款红石榴滋润精华水200ml保湿补水</t>
+        </is>
+      </c>
+      <c r="D809" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E809" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F809" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G809" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H809" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I809" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J809" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:52:52</t>
+        </is>
+      </c>
+      <c r="K809" s="2" t="inlineStr"/>
+      <c r="L809" s="2" t="inlineStr"/>
+      <c r="M809" s="2" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="B810" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶精华50ML</t>
+        </is>
+      </c>
+      <c r="C810" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
+        </is>
+      </c>
+      <c r="D810" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E810" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F810" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G810" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H810" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I810" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J810" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:54:25</t>
+        </is>
+      </c>
+      <c r="K810" s="2" t="inlineStr"/>
+      <c r="L810" s="2" t="inlineStr"/>
+      <c r="M810" s="2" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="n">
+        <v>810</v>
+      </c>
+      <c r="B811" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶精华50ML</t>
+        </is>
+      </c>
+      <c r="C811" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】小银瓶精华液50ml美白淡斑精华露护肤品送女友生日礼物【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D811" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="E811" s="2" t="inlineStr">
+        <is>
+          <t>SK-II</t>
+        </is>
+      </c>
+      <c r="F811" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G811" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H811" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I811" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J811" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:54:44</t>
+        </is>
+      </c>
+      <c r="K811" s="2" t="inlineStr"/>
+      <c r="L811" s="2" t="inlineStr"/>
+      <c r="M811" s="2" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="n">
+        <v>811</v>
+      </c>
+      <c r="B812" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师粉底液2号</t>
+        </is>
+      </c>
+      <c r="C812" s="2" t="inlineStr">
+        <is>
+          <t>正品行货|新版阿玛尼粉底液大师蓝标遮瑕持久不脱妆滋润干皮</t>
+        </is>
+      </c>
+      <c r="D812" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E812" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F812" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G812" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H812" s="3" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="I812" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J812" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:56:15</t>
+        </is>
+      </c>
+      <c r="K812" s="2" t="inlineStr"/>
+      <c r="L812" s="2" t="inlineStr"/>
+      <c r="M812" s="2" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="n">
+        <v>812</v>
+      </c>
+      <c r="B813" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师粉底液2号</t>
+        </is>
+      </c>
+      <c r="C813" s="2" t="inlineStr">
+        <is>
+          <t>ARMANI阿玛尼蓝标大师造型紧颜粉底液2号色30ml持久遮瑕</t>
+        </is>
+      </c>
+      <c r="D813" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E813" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F813" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G813" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H813" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I813" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J813" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:56:37</t>
+        </is>
+      </c>
+      <c r="K813" s="2" t="inlineStr"/>
+      <c r="L813" s="2" t="inlineStr"/>
+      <c r="M813" s="2" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="B814" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师粉底液2号</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="inlineStr">
+        <is>
+          <t>ARMANII阿玛尼大师蓝标粉底液2号30ml/瓶</t>
+        </is>
+      </c>
+      <c r="D814" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="E814" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼</t>
+        </is>
+      </c>
+      <c r="F814" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G814" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H814" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I814" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J814" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:56:59</t>
+        </is>
+      </c>
+      <c r="K814" s="2" t="inlineStr"/>
+      <c r="L814" s="2" t="inlineStr"/>
+      <c r="M814" s="2" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="2" t="n">
+        <v>814</v>
+      </c>
+      <c r="B815" s="2" t="inlineStr">
+        <is>
+          <t>Lancome兰蔻美丽人生馥郁版100ml</t>
+        </is>
+      </c>
+      <c r="C815" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】 兰蔻 美丽人生女士香水EDP 30/100ML</t>
+        </is>
+      </c>
+      <c r="D815" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E815" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F815" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G815" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H815" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I815" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J815" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:58:40</t>
+        </is>
+      </c>
+      <c r="K815" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L815" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M815" s="2" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="n">
+        <v>815</v>
+      </c>
+      <c r="B816" s="2" t="inlineStr">
+        <is>
+          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
+        </is>
+      </c>
+      <c r="C816" s="2" t="inlineStr">
+        <is>
+          <t>【专柜行货】兰蔻新品美丽人生香水50ml 浓香版EDP 女士香水</t>
+        </is>
+      </c>
+      <c r="D816" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E816" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F816" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G816" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H816" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I816" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J816" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:00:30</t>
+        </is>
+      </c>
+      <c r="K816" s="2" t="inlineStr"/>
+      <c r="L816" s="2" t="inlineStr"/>
+      <c r="M816" s="2" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="n">
+        <v>816</v>
+      </c>
+      <c r="B817" s="2" t="inlineStr">
+        <is>
+          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
+        </is>
+      </c>
+      <c r="C817" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻美丽人生馥郁版女士浓香香水EDP 30-100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D817" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E817" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F817" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G817" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H817" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I817" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J817" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:00:53</t>
+        </is>
+      </c>
+      <c r="K817" s="2" t="inlineStr"/>
+      <c r="L817" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 50ml</t>
+        </is>
+      </c>
+      <c r="M817" s="2" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="n">
+        <v>817</v>
+      </c>
+      <c r="B818" s="2" t="inlineStr">
+        <is>
+          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
+        </is>
+      </c>
+      <c r="C818" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻美丽人生馥郁版女士浓香EDP 30-50-100ml【法国直发】【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D818" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E818" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F818" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G818" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H818" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I818" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J818" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:01:15</t>
+        </is>
+      </c>
+      <c r="K818" s="2" t="inlineStr"/>
+      <c r="L818" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 50ml</t>
+        </is>
+      </c>
+      <c r="M818" s="2" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="n">
+        <v>818</v>
+      </c>
+      <c r="B819" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+        </is>
+      </c>
+      <c r="C819" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻美丽人生馥郁版女浓香EDP 30-100ml【法国直发【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D819" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E819" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F819" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G819" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H819" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I819" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J819" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:03:06</t>
+        </is>
+      </c>
+      <c r="K819" s="2" t="inlineStr"/>
+      <c r="L819" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 50mL</t>
+        </is>
+      </c>
+      <c r="M819" s="2" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="n">
+        <v>819</v>
+      </c>
+      <c r="B820" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+        </is>
+      </c>
+      <c r="C820" s="2" t="inlineStr">
+        <is>
+          <t>LANCOME兰蔻美丽人生女士淡香精EDP30/50/100ML精装</t>
+        </is>
+      </c>
+      <c r="D820" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E820" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F820" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G820" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H820" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I820" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J820" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:03:28</t>
+        </is>
+      </c>
+      <c r="K820" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L820" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M820" s="2" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="B821" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+        </is>
+      </c>
+      <c r="C821" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻 美丽人生女士浓香水 30/50/100ml【法国直发】【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D821" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E821" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F821" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G821" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H821" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I821" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J821" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:03:50</t>
+        </is>
+      </c>
+      <c r="K821" s="2" t="inlineStr"/>
+      <c r="L821" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 50ml</t>
+        </is>
+      </c>
+      <c r="M821" s="2" t="n">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="B822" s="2" t="inlineStr">
+        <is>
+          <t>Lancome/兰蔻是我IDOLE偶像香水 50ml</t>
+        </is>
+      </c>
+      <c r="C822" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻idole偶像是我淡香水50ml留香清新约会高级礼物</t>
+        </is>
+      </c>
+      <c r="D822" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E822" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F822" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G822" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H822" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I822" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J822" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:05:20</t>
+        </is>
+      </c>
+      <c r="K822" s="2" t="inlineStr"/>
+      <c r="L822" s="2" t="inlineStr"/>
+      <c r="M822" s="2" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="2" t="n">
+        <v>822</v>
+      </c>
+      <c r="B823" s="2" t="inlineStr">
+        <is>
+          <t>Lancome 兰蔻是我 浓情版 100ml</t>
+        </is>
+      </c>
+      <c r="C823" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】唯我浓香水100ml花果香调清新持久馥郁迷人节日礼物</t>
+        </is>
+      </c>
+      <c r="D823" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E823" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F823" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G823" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H823" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I823" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J823" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:06:59</t>
+        </is>
+      </c>
+      <c r="K823" s="2" t="inlineStr"/>
+      <c r="L823" s="2" t="inlineStr"/>
+      <c r="M823" s="2" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="n">
+        <v>823</v>
+      </c>
+      <c r="B824" s="2" t="inlineStr">
+        <is>
+          <t>Lancome 兰蔻是我 浓情版 100ml</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】是我偶像经典浓香水EDP100ML补充装花香调新版</t>
+        </is>
+      </c>
+      <c r="D824" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="E824" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻</t>
+        </is>
+      </c>
+      <c r="F824" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G824" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H824" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I824" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J824" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:07:21</t>
+        </is>
+      </c>
+      <c r="K824" s="2" t="inlineStr"/>
+      <c r="L824" s="2" t="inlineStr"/>
+      <c r="M824" s="2" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="n">
+        <v>824</v>
+      </c>
+      <c r="B825" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI 香水 茉莉100ML</t>
+        </is>
+      </c>
+      <c r="C825" s="2" t="inlineStr">
+        <is>
+          <t>古驰(GUCCI)绮梦茉莉女士香水EDP 30/50/100ML</t>
+        </is>
+      </c>
+      <c r="D825" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E825" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F825" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G825" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H825" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I825" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J825" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:08:56</t>
+        </is>
+      </c>
+      <c r="K825" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L825" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M825" s="2" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="B826" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕李先生的花园淡香水100ml</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕李先生的花园淡香水EDT100ml</t>
+        </is>
+      </c>
+      <c r="D826" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="E826" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="F826" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G826" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H826" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I826" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J826" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:10:27</t>
+        </is>
+      </c>
+      <c r="K826" s="2" t="inlineStr"/>
+      <c r="L826" s="2" t="inlineStr"/>
+      <c r="M826" s="2" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="B827" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕绯红火参古龙水100ml</t>
+        </is>
+      </c>
+      <c r="C827" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕绯红火参/血色大黄古龙水香水节日礼物</t>
+        </is>
+      </c>
+      <c r="D827" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="E827" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="F827" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G827" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H827" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I827" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J827" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:12:03</t>
+        </is>
+      </c>
+      <c r="K827" s="2" t="inlineStr"/>
+      <c r="L827" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 100mL 血色大黄 EDC 古龙水</t>
+        </is>
+      </c>
+      <c r="M827" s="2" t="n">
+        <v>308.03</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="n">
+        <v>827</v>
+      </c>
+      <c r="B828" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕绯红火参古龙水100ml</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕绯红火参/血色大黄古龙水香水简装礼物</t>
+        </is>
+      </c>
+      <c r="D828" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="E828" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕</t>
+        </is>
+      </c>
+      <c r="F828" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G828" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H828" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I828" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J828" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:12:23</t>
+        </is>
+      </c>
+      <c r="K828" s="2" t="inlineStr"/>
+      <c r="L828" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 100mL 血色大黄 EDC 古龙水【简装】</t>
+        </is>
+      </c>
+      <c r="M828" s="2" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="2" t="n">
+        <v>828</v>
+      </c>
+      <c r="B829" s="2" t="inlineStr">
+        <is>
+          <t>NARS小粉金细管唇膏1.5G #321 Turned on</t>
+        </is>
+      </c>
+      <c r="C829" s="2" t="inlineStr">
+        <is>
+          <t>纳斯小粉金口红321TURNED ON#透茶玫瑰1.5g节日礼物</t>
+        </is>
+      </c>
+      <c r="D829" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E829" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F829" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G829" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H829" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I829" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J829" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:14:00</t>
+        </is>
+      </c>
+      <c r="K829" s="2" t="inlineStr"/>
+      <c r="L829" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 1.5g #321 Turned On 透茶玫瑰</t>
+        </is>
+      </c>
+      <c r="M829" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="n">
+        <v>829</v>
+      </c>
+      <c r="B830" s="2" t="inlineStr">
+        <is>
+          <t>NARS小粉金细管唇膏1.5G #321 Turned on</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】氛围娜斯小粉唇膏#321透茶玫瑰丝滑显色保湿滋润水感通透1.5g</t>
+        </is>
+      </c>
+      <c r="D830" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E830" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F830" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G830" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H830" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I830" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J830" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:14:13</t>
+        </is>
+      </c>
+      <c r="K830" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=20.0%)</t>
+        </is>
+      </c>
+      <c r="L830" s="2" t="inlineStr"/>
+      <c r="M830" s="2" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="2" t="n">
+        <v>830</v>
+      </c>
+      <c r="B831" s="2" t="inlineStr">
+        <is>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+        </is>
+      </c>
+      <c r="C831" s="2" t="inlineStr">
+        <is>
+          <t>MAC/魅可大子弹头口红唇膏#646   3.5g</t>
+        </is>
+      </c>
+      <c r="D831" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E831" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F831" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G831" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H831" s="3" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="I831" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J831" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:15:41</t>
+        </is>
+      </c>
+      <c r="K831" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=11.8%)</t>
+        </is>
+      </c>
+      <c r="L831" s="2" t="inlineStr"/>
+      <c r="M831" s="2" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="B832" s="2" t="inlineStr">
+        <is>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+        </is>
+      </c>
+      <c r="C832" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可大子弹头口红 662大辣椒唇膏 显色哑光滋润</t>
+        </is>
+      </c>
+      <c r="D832" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E832" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F832" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G832" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H832" s="3" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="I832" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J832" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:16:13</t>
+        </is>
+      </c>
+      <c r="K832" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=11.8%)</t>
+        </is>
+      </c>
+      <c r="L832" s="2" t="inlineStr">
+        <is>
+          <t>已选择： #646*大女主+专柜礼盒 正品行货-送礼好物-可代写祝福贺卡</t>
+        </is>
+      </c>
+      <c r="M832" s="2" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="2" t="n">
+        <v>832</v>
+      </c>
+      <c r="B833" s="2" t="inlineStr">
+        <is>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+        </is>
+      </c>
+      <c r="C833" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可新品哑光大子弹头唇膏口红666大宠粉 683大玩咖 682 646【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D833" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E833" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F833" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G833" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H833" s="3" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="I833" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J833" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:16:36</t>
+        </is>
+      </c>
+      <c r="K833" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=29.4%)</t>
+        </is>
+      </c>
+      <c r="L833" s="2" t="inlineStr">
+        <is>
+          <t>已选择： #646MARRAKESH 大女主</t>
+        </is>
+      </c>
+      <c r="M833" s="2" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="B834" s="2" t="inlineStr">
+        <is>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="inlineStr">
+        <is>
+          <t>【鉴定正品】MAC/魅可新经典哑光唇膏 柔雾 气色 3.5g 大子弹头</t>
+        </is>
+      </c>
+      <c r="D834" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E834" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F834" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G834" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H834" s="3" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="I834" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J834" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:16:58</t>
+        </is>
+      </c>
+      <c r="K834" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=23.5%)</t>
+        </is>
+      </c>
+      <c r="L834" s="2" t="inlineStr">
+        <is>
+          <t>已选择：#646 3.5g MAC 经典大子弹头</t>
+        </is>
+      </c>
+      <c r="M834" s="2" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="B835" s="2" t="inlineStr">
+        <is>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+        </is>
+      </c>
+      <c r="C835" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Lamer海蓝之谜修护焕新精萃水100ml 修护舒缓精华水</t>
+        </is>
+      </c>
+      <c r="D835" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="E835" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="F835" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G835" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H835" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I835" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J835" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:18:34</t>
+        </is>
+      </c>
+      <c r="K835" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=20.0%)</t>
+        </is>
+      </c>
+      <c r="L835" s="2" t="inlineStr"/>
+      <c r="M835" s="2" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="B836" s="2" t="inlineStr">
+        <is>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="inlineStr">
+        <is>
+          <t>【LA MER】 海蓝之谜焕肤水100ML 舒缓提亮滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D836" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="E836" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="F836" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G836" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H836" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I836" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J836" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:18:56</t>
+        </is>
+      </c>
+      <c r="K836" s="2" t="inlineStr"/>
+      <c r="L836" s="2" t="inlineStr"/>
+      <c r="M836" s="2" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="n">
+        <v>836</v>
+      </c>
+      <c r="B837" s="2" t="inlineStr">
+        <is>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+        </is>
+      </c>
+      <c r="C837" s="2" t="inlineStr">
+        <is>
+          <t>【海蓝之谜】精粹柔酸水肌底液精华换肤调理液100ml 控油保湿改善闭口【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D837" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="E837" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="F837" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G837" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H837" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I837" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J837" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:19:13</t>
+        </is>
+      </c>
+      <c r="K837" s="2" t="inlineStr"/>
+      <c r="L837" s="2" t="inlineStr"/>
+      <c r="M837" s="2" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="n">
+        <v>837</v>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>【LA MER】海蓝之谜鞣酸水柔酸肌底液100ml复合精华细致毛孔调理焕肤【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="E838" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜</t>
+        </is>
+      </c>
+      <c r="F838" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G838" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H838" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I838" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J838" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:19:28</t>
+        </is>
+      </c>
+      <c r="K838" s="2" t="inlineStr"/>
+      <c r="L838" s="2" t="inlineStr"/>
+      <c r="M838" s="2" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="n">
+        <v>838</v>
+      </c>
+      <c r="B839" s="2" t="inlineStr">
+        <is>
+          <t>MAC魅可保湿定妆喷雾Fix+100mL</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定妆保湿喷雾白瓶100ml补水控油持久干皮油皮滋养清爽正品</t>
+        </is>
+      </c>
+      <c r="D839" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E839" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F839" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G839" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H839" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I839" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J839" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:27:40</t>
+        </is>
+      </c>
+      <c r="K839" s="2" t="inlineStr"/>
+      <c r="L839" s="2" t="inlineStr"/>
+      <c r="M839" s="2" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="n">
+        <v>839</v>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>宏香记品牌官方正品，100%保障</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E840" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F840" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G840" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H840" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I840" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J840" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:29:19</t>
+        </is>
+      </c>
+      <c r="K840" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L840" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M840" s="2" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="n">
+        <v>840</v>
+      </c>
+      <c r="B841" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定妆紫喷喷雾持久锁妆防水保湿控油不拔干不刺激干皮100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D841" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E841" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F841" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G841" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H841" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I841" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J841" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:29:43</t>
+        </is>
+      </c>
+      <c r="K841" s="2" t="inlineStr"/>
+      <c r="L841" s="2" t="inlineStr"/>
+      <c r="M841" s="2" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="n">
+        <v>841</v>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>MAC/魅可定妆妆前保湿喷雾原味长效定妆防水不黏腻</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E842" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F842" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G842" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H842" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I842" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J842" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:30:03</t>
+        </is>
+      </c>
+      <c r="K842" s="2" t="inlineStr"/>
+      <c r="L842" s="2" t="inlineStr">
+        <is>
+          <t>已选: 100mL 妆前保湿喷雾[24.1产]</t>
+        </is>
+      </c>
+      <c r="M842" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="n">
+        <v>842</v>
+      </c>
+      <c r="B843" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定妆紫喷喷雾持久锁妆防水保湿控油不拔干不刺激干皮100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D843" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E843" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F843" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G843" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H843" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I843" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J843" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:30:19</t>
+        </is>
+      </c>
+      <c r="K843" s="2" t="inlineStr"/>
+      <c r="L843" s="2" t="inlineStr"/>
+      <c r="M843" s="2" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>MAC 无暇粉底液NC12 30ML</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可 新升级定制无瑕粉底液NC12#30ml</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E844" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F844" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G844" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H844" s="3" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="I844" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J844" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:31:49</t>
+        </is>
+      </c>
+      <c r="K844" s="2" t="inlineStr"/>
+      <c r="L844" s="2" t="inlineStr">
+        <is>
+          <t>已选: NC12 黄二白</t>
+        </is>
+      </c>
+      <c r="M844" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="n">
+        <v>844</v>
+      </c>
+      <c r="B845" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴面霜50ml</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER雅诗兰黛】红石榴面霜 鲜活亮采日霜50ml保湿补水</t>
+        </is>
+      </c>
+      <c r="D845" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E845" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F845" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G845" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H845" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I845" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J845" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:33:23</t>
+        </is>
+      </c>
+      <c r="K845" s="2" t="inlineStr"/>
+      <c r="L845" s="2" t="inlineStr"/>
+      <c r="M845" s="2" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="n">
+        <v>845</v>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="D846" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E846" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F846" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G846" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H846" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I846" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J846" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:34:58</t>
+        </is>
+      </c>
+      <c r="K846" s="2" t="inlineStr"/>
+      <c r="L846" s="2" t="inlineStr"/>
+      <c r="M846" s="2" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="n">
+        <v>846</v>
+      </c>
+      <c r="B847" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="inlineStr">
+        <is>
+          <t>【861.8万人收藏该品牌】双支 单品 雅诗兰黛新款红石榴洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="D847" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E847" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F847" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G847" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H847" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I847" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J847" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:35:22</t>
+        </is>
+      </c>
+      <c r="K847" s="2" t="inlineStr"/>
+      <c r="L847" s="2" t="inlineStr"/>
+      <c r="M847" s="2" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="n">
+        <v>847</v>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂红腰子洗面奶女洁面乳膏氨基酸清洁保湿旗舰店</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E848" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F848" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G848" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H848" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I848" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J848" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:37:02</t>
+        </is>
+      </c>
+      <c r="K848" s="2" t="inlineStr"/>
+      <c r="L848" s="2" t="inlineStr">
+        <is>
+          <t>已选: 125ml [温和保湿]红腰子洁面乳+嫩白洇色蛋</t>
+        </is>
+      </c>
+      <c r="M848" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="n">
+        <v>848</v>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂洁面膏红腰子洗面奶深层清洁保湿去黄黑头提亮</t>
+        </is>
+      </c>
+      <c r="D849" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F849" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G849" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H849" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I849" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J849" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:37:28</t>
+        </is>
+      </c>
+      <c r="K849" s="2" t="inlineStr"/>
+      <c r="L849" s="2" t="inlineStr">
+        <is>
+          <t>已选: 175ml[正装125ml+中样50ml]洁面膏+滴形妆蛋球1</t>
+        </is>
+      </c>
+      <c r="M849" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="n">
+        <v>849</v>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO悦薇抗糖眼霜（新版）15ml</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】资生堂悦薇智感紧塑焕白眼霜15ml 紧致淡纹提亮眼周</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E850" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G850" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H850" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I850" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J850" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:39:06</t>
+        </is>
+      </c>
+      <c r="K850" s="2" t="inlineStr"/>
+      <c r="L850" s="2" t="inlineStr"/>
+      <c r="M850" s="2" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="B851" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO盼丽风姿眼霜（新款）15ml</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂盼丽风姿智感抚纹眼霜15ml小雷达抗皱紧致礼物</t>
+        </is>
+      </c>
+      <c r="D851" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F851" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G851" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H851" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I851" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J851" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:40:39</t>
+        </is>
+      </c>
+      <c r="K851" s="2" t="inlineStr"/>
+      <c r="L851" s="2" t="inlineStr"/>
+      <c r="M851" s="2" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="n">
+        <v>851</v>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1C1 30ML 新版 2026年</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】DW持妆粉底液1C1 66#瓷白色 30ml</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E852" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F852" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G852" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H852" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I852" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J852" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:42:19</t>
+        </is>
+      </c>
+      <c r="K852" s="2" t="inlineStr"/>
+      <c r="L852" s="2" t="inlineStr"/>
+      <c r="M852" s="2" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="n">
+        <v>852</v>
+      </c>
+      <c r="B853" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder/雅诗兰黛 DW持妆粉底液30ml#1N2 柔光遮瑕【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D853" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E853" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F853" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G853" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H853" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I853" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J853" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:44:09</t>
+        </is>
+      </c>
+      <c r="K853" s="2" t="inlineStr"/>
+      <c r="L853" s="2" t="inlineStr"/>
+      <c r="M853" s="2" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="B854" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder/雅诗兰黛dw持粉底液#1N2油皮亲妈持妆粉底液30ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E854" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F854" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G854" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H854" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I854" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J854" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:44:25</t>
+        </is>
+      </c>
+      <c r="K854" s="2" t="inlineStr"/>
+      <c r="L854" s="2" t="inlineStr"/>
+      <c r="M854" s="2" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="n">
+        <v>854</v>
+      </c>
+      <c r="B855" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】雅诗兰黛DW持妆粉底液 油皮亲妈持久不脱妆遮瑕控油</t>
+        </is>
+      </c>
+      <c r="D855" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E855" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G855" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H855" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I855" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J855" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:44:46</t>
+        </is>
+      </c>
+      <c r="K855" s="2" t="inlineStr"/>
+      <c r="L855" s="2" t="inlineStr">
+        <is>
+          <t>已选: 1W2 自然色（全新原装） 30mL 个人 DW-粉底液 赠彩妆蛋 压头[新旧版随机]</t>
+        </is>
+      </c>
+      <c r="M855" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="n">
+        <v>855</v>
+      </c>
+      <c r="B856" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N1 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder/雅诗兰黛 DW持妆粉底液30ml#1N2 柔光遮瑕【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="E856" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛</t>
+        </is>
+      </c>
+      <c r="F856" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G856" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H856" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I856" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J856" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:46:25</t>
+        </is>
+      </c>
+      <c r="K856" s="2" t="inlineStr"/>
+      <c r="L856" s="2" t="inlineStr">
+        <is>
+          <t>已选: 30mL 1N2</t>
+        </is>
+      </c>
+      <c r="M856" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="n">
+        <v>856</v>
+      </c>
+      <c r="B857" s="2" t="inlineStr">
+        <is>
+          <t>MAC魅可 丝柔哑光唇膏 大子弹口红#666 Sweet Deal 玫瑰冷萃</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可大子弹头口红哑光柔雾666大宠粉602大辣椒</t>
+        </is>
+      </c>
+      <c r="D857" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="E857" s="2" t="inlineStr">
+        <is>
+          <t>魅可</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G857" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H857" s="3" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="I857" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J857" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:48:04</t>
+        </is>
+      </c>
+      <c r="K857" s="2" t="inlineStr"/>
+      <c r="L857" s="2" t="inlineStr">
+        <is>
+          <t>已选: 大宠粉[666] 赠专柜礼盒+正品保障+假一赔十</t>
+        </is>
+      </c>
+      <c r="M857" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="n">
+        <v>857</v>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>兰芝马卡龙隔离30ml紫色</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销401万+件】韩国兰芝新款马卡龙防晒隔离霜30ml遮瑕妆前乳打底</t>
+        </is>
+      </c>
+      <c r="D858" s="2" t="inlineStr">
+        <is>
+          <t>兰芝</t>
+        </is>
+      </c>
+      <c r="E858" s="2" t="inlineStr">
+        <is>
+          <t>兰芝</t>
+        </is>
+      </c>
+      <c r="F858" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G858" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H858" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I858" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J858" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:49:34</t>
+        </is>
+      </c>
+      <c r="K858" s="2" t="inlineStr"/>
+      <c r="L858" s="2" t="inlineStr"/>
+      <c r="M858" s="2" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="n">
+        <v>858</v>
+      </c>
+      <c r="B859" s="2" t="inlineStr">
+        <is>
+          <t>兰芝马卡龙隔离30ml绿色</t>
+        </is>
+      </c>
+      <c r="C859" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销401万+件】韩国LANEIGE兰芝新款马卡龙防晒隔离霜遮瑕三合一妆前乳打底</t>
+        </is>
+      </c>
+      <c r="D859" s="2" t="inlineStr">
+        <is>
+          <t>兰芝</t>
+        </is>
+      </c>
+      <c r="E859" s="2" t="inlineStr">
+        <is>
+          <t>兰芝</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G859" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H859" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I859" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J859" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:51:14</t>
+        </is>
+      </c>
+      <c r="K859" s="2" t="inlineStr"/>
+      <c r="L859" s="2" t="inlineStr">
+        <is>
+          <t>已选: 兰芝紫隔离30ml[新版马卡龙]</t>
+        </is>
+      </c>
+      <c r="M859" s="2" t="inlineStr">
+        <is>
+          <t>68.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="n">
+        <v>859</v>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】悦薇抗糖面霜智感塑颜抗皱霜焕白清爽资生堂面霜50ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F860" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G860" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H860" s="3" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I860" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J860" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:52:47</t>
+        </is>
+      </c>
+      <c r="K860" s="2" t="inlineStr"/>
+      <c r="L860" s="2" t="inlineStr"/>
+      <c r="M860" s="2" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="n">
+        <v>860</v>
+      </c>
+      <c r="B861" s="2" t="inlineStr">
+        <is>
+          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】悦薇面霜抗糖抗初老补水紧致智感紧塑焕白霜</t>
+        </is>
+      </c>
+      <c r="D861" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G861" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H861" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I861" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J861" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:53:13</t>
+        </is>
+      </c>
+      <c r="K861" s="2" t="inlineStr"/>
+      <c r="L861" s="2" t="inlineStr">
+        <is>
+          <t>已选: 50mL [滋润型]悦薇面霜</t>
+        </is>
+      </c>
+      <c r="M861" s="2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="n">
+        <v>861</v>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯5894大白饼粉饼控油磨皮持妆蜜粉饼【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E862" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G862" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H862" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I862" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J862" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:55:01</t>
+        </is>
+      </c>
+      <c r="K862" s="2" t="inlineStr"/>
+      <c r="L862" s="2" t="inlineStr"/>
+      <c r="M862" s="2" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="n">
+        <v>862</v>
+      </c>
+      <c r="B863" s="2" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯 流光美肌轻透蜜粉饼5894大白饼粉饼10g【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D863" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E863" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G863" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H863" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I863" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J863" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:55:23</t>
+        </is>
+      </c>
+      <c r="K863" s="2" t="inlineStr"/>
+      <c r="L863" s="2" t="inlineStr"/>
+      <c r="M863" s="2" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="n">
+        <v>863</v>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯5894大白饼粉饼控油磨皮持妆蜜粉饼【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E864" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F864" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G864" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H864" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I864" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J864" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:55:40</t>
+        </is>
+      </c>
+      <c r="K864" s="2" t="inlineStr"/>
+      <c r="L864" s="2" t="inlineStr"/>
+      <c r="M864" s="2" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="n">
+        <v>864</v>
+      </c>
+      <c r="B865" s="2" t="inlineStr">
+        <is>
+          <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销248.5万+件】whoo后拱辰享泡沫洗面奶水妍津率享深层清洁控油洁面女</t>
+        </is>
+      </c>
+      <c r="D865" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="E865" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G865" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H865" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I865" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J865" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:57:16</t>
+        </is>
+      </c>
+      <c r="K865" s="2" t="inlineStr"/>
+      <c r="L865" s="2" t="inlineStr">
+        <is>
+          <t>已选: 美白洁面套180ML+洁面40ML</t>
+        </is>
+      </c>
+      <c r="M865" s="2" t="inlineStr">
+        <is>
+          <t>119.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="n">
+        <v>865</v>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】红腰子精华液4.0紧致抗皱面部护肤抗初老120ml</t>
+        </is>
+      </c>
+      <c r="D866" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E866" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="F866" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G866" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H866" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I866" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J866" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:58:55</t>
+        </is>
+      </c>
+      <c r="K866" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L866" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M866" s="2" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="n">
+        <v>866</v>
+      </c>
+      <c r="B867" s="2" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="C867" s="2" t="inlineStr">
+        <is>
+          <t>同城用户刚刚拼成&amp;#10;可参与拼单马上拼</t>
+        </is>
+      </c>
+      <c r="D867" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E867" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F867" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G867" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H867" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I867" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J867" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:59:25</t>
+        </is>
+      </c>
+      <c r="K867" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L867" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M867" s="2" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="n">
+        <v>867</v>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>【6671人收藏】服装店袋子塑料袋购物袋礼品袋包装袋网红手提袋子服装店袋子批发</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E868" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F868" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G868" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H868" s="3" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I868" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J868" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:59:51</t>
+        </is>
+      </c>
+      <c r="K868" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L868" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M868" s="2" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="n">
+        <v>868</v>
+      </c>
+      <c r="B869" s="2" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="C869" s="2" t="inlineStr">
+        <is>
+          <t>【清仓】筋膜球足底按摩球腰背部肌肉放松瑜伽肩颈腿膜健身筋膜球</t>
+        </is>
+      </c>
+      <c r="D869" s="2" t="inlineStr">
+        <is>
+          <t>资生堂</t>
+        </is>
+      </c>
+      <c r="E869" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H869" s="3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I869" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J869" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:00:22</t>
+        </is>
+      </c>
+      <c r="K869" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L869" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M869" s="2" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="n">
+        <v>869</v>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园香草颂香水100ML</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>【1.37万人评价品牌正品】GUCCI/古驰炼金士花园系列香水100ML正品香氛送礼</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E870" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F870" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H870" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I870" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J870" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:02:00</t>
+        </is>
+      </c>
+      <c r="K870" s="2" t="inlineStr"/>
+      <c r="L870" s="2" t="inlineStr"/>
+      <c r="M870" s="2" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="n">
+        <v>870</v>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园香草颂香水100ML</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="inlineStr">
+        <is>
+          <t>同城用户刚刚拼成&amp;#10;可参与拼单马上拼</t>
+        </is>
+      </c>
+      <c r="D871" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G871" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H871" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I871" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J871" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:02:33</t>
+        </is>
+      </c>
+      <c r="K871" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L871" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M871" s="2" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="n">
+        <v>871</v>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园沐光橙香水100ML</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>【百补品牌热销40.6万件】GUCCI/古驰炼金士花园系列香水150ML简装持久留香</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E872" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F872" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G872" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H872" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I872" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J872" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:04:13</t>
+        </is>
+      </c>
+      <c r="K872" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L872" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M872" s="2" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="n">
+        <v>872</v>
+      </c>
+      <c r="B873" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园沐光橙香水100ML</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="inlineStr">
+        <is>
+          <t>【百补品牌热销40.6万件】GUCCI/古驰炼金士花园系列香水100ML正品香氛送礼</t>
+        </is>
+      </c>
+      <c r="D873" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="inlineStr">
+        <is>
+          <t>古驰</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G873" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H873" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I873" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J873" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:04:41</t>
+        </is>
+      </c>
+      <c r="K873" s="2" t="inlineStr"/>
+      <c r="L873" s="2" t="inlineStr"/>
+      <c r="M873" s="2" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="n">
+        <v>873</v>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>Maison Margiela 梅森马吉拉马丁马吉拉香水 慵懒周末/沙滩漫步【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="E874" s="2" t="inlineStr">
+        <is>
+          <t>梅森马吉拉</t>
+        </is>
+      </c>
+      <c r="F874" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G874" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H874" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I874" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J874" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:06:30</t>
+        </is>
+      </c>
+      <c r="K874" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+      <c r="L874" s="2" t="inlineStr">
+        <is>
+          <t>已选: 温暖壁炉/壁炉火光100ml</t>
+        </is>
+      </c>
+      <c r="M874" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="n">
+        <v>874</v>
+      </c>
+      <c r="B875" s="2" t="inlineStr">
+        <is>
+          <t>YSL新款爱心唇釉610#</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉610 416 622 440限定浮雕黑管</t>
+        </is>
+      </c>
+      <c r="D875" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="E875" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G875" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H875" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I875" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J875" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:08:21</t>
+        </is>
+      </c>
+      <c r="K875" s="2" t="inlineStr"/>
+      <c r="L875" s="2" t="inlineStr">
+        <is>
+          <t>已选: 610 冰乌龙</t>
+        </is>
+      </c>
+      <c r="M875" s="2" t="inlineStr">
+        <is>
+          <t>154.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>【宝格丽】悠境白茶淡香75ml正装新款白茶清新茶香木质花香</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽</t>
+        </is>
+      </c>
+      <c r="E876" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽</t>
+        </is>
+      </c>
+      <c r="F876" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G876" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H876" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I876" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J876" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:09:56</t>
+        </is>
+      </c>
+      <c r="K876" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L876" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M876" s="2" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="n">
+        <v>876</v>
+      </c>
+      <c r="B877" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="inlineStr">
+        <is>
+          <t>已优惠5元券后6.98已拼45.5万+件</t>
+        </is>
+      </c>
+      <c r="D877" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽</t>
+        </is>
+      </c>
+      <c r="E877" s="2" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G877" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H877" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I877" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J877" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:10:17</t>
+        </is>
+      </c>
+      <c r="K877" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L877" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M877" s="2" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="n">
+        <v>877</v>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>【BVLGARI】宝格丽 白茶 香水 茶香系列 淡香水EDT 75ml/150ml</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽</t>
+        </is>
+      </c>
+      <c r="E878" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽</t>
+        </is>
+      </c>
+      <c r="F878" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G878" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H878" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I878" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J878" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:10:42</t>
+        </is>
+      </c>
+      <c r="K878" s="2" t="inlineStr"/>
+      <c r="L878" s="2" t="inlineStr">
+        <is>
+          <t>已选: 150mL 宝格丽白茶</t>
+        </is>
+      </c>
+      <c r="M878" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n">
+        <v>878</v>
+      </c>
+      <c r="B879" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="inlineStr">
+        <is>
+          <t>【宝格丽】悠境白茶淡香75ml正装新款白茶清新茶香木质花香</t>
+        </is>
+      </c>
+      <c r="D879" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽</t>
+        </is>
+      </c>
+      <c r="E879" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G879" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H879" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I879" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J879" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:11:05</t>
+        </is>
+      </c>
+      <c r="K879" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L879" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M879" s="2" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>【宝格丽】宝格丽白茶香水 淡香水 150ml/5oz【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽</t>
+        </is>
+      </c>
+      <c r="E880" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽</t>
+        </is>
+      </c>
+      <c r="F880" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G880" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H880" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I880" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J880" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:11:21</t>
+        </is>
+      </c>
+      <c r="K880" s="2" t="inlineStr"/>
+      <c r="L880" s="2" t="inlineStr">
+        <is>
+          <t>已选: 150mL</t>
+        </is>
+      </c>
+      <c r="M880" s="2" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="B881" s="2" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油150ml</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀绿茶卸妆洁颜油  温和深层清洁彩妆保湿</t>
+        </is>
+      </c>
+      <c r="D881" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G881" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H881" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I881" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J881" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:12:54</t>
+        </is>
+      </c>
+      <c r="K881" s="2" t="inlineStr"/>
+      <c r="L881" s="2" t="inlineStr">
+        <is>
+          <t>已选: 150mL</t>
+        </is>
+      </c>
+      <c r="M881" s="2" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="n">
+        <v>881</v>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油150ml</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀绿茶新肌洁颜油卸妆油150ml 去黄抗氧化</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="E882" s="2" t="inlineStr">
+        <is>
+          <t>植村秀</t>
+        </is>
+      </c>
+      <c r="F882" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G882" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H882" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I882" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J882" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:13:15</t>
+        </is>
+      </c>
+      <c r="K882" s="2" t="inlineStr"/>
+      <c r="L882" s="2" t="inlineStr"/>
+      <c r="M882" s="2" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="n">
+        <v>882</v>
+      </c>
+      <c r="B883" s="2" t="inlineStr">
+        <is>
+          <t>NARS 水光绚色液体腮红 西柚奶桃 BRAZEN 7ml</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯液体腮红BRAZEN西柚奶桃元气清透提气色易上色服帖持妆</t>
+        </is>
+      </c>
+      <c r="D883" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F883" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G883" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H883" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I883" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J883" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:14:44</t>
+        </is>
+      </c>
+      <c r="K883" s="2" t="inlineStr"/>
+      <c r="L883" s="2" t="inlineStr">
+        <is>
+          <t>已选: 7mL （24年4月批次） NARS液体腮红BRAZEN 西柚奶桃</t>
+        </is>
+      </c>
+      <c r="M883" s="2" t="inlineStr">
+        <is>
+          <t>89.9</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/商品校验调试记录.xlsx
+++ b/商品校验调试记录.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M979"/>
+  <dimension ref="A1:M987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -53581,7 +53581,11 @@
           <t>NARS液体腮红 INSATIABLE</t>
         </is>
       </c>
-      <c r="C973" s="2" t="inlineStr"/>
+      <c r="C973" s="2" t="inlineStr">
+        <is>
+          <t>NARS/纳斯 小粉金液体腮红 #INSATIABLE 酒渍樱桃【5天内发货】</t>
+        </is>
+      </c>
       <c r="D973" s="2" t="inlineStr">
         <is>
           <t>纳斯</t>
@@ -53589,12 +53593,12 @@
       </c>
       <c r="E973" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>纳斯</t>
         </is>
       </c>
       <c r="F973" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G973" s="2" t="inlineStr">
@@ -53603,23 +53607,19 @@
         </is>
       </c>
       <c r="H973" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I973" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J973" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:53:16</t>
-        </is>
-      </c>
-      <c r="K973" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>2026-06-16 15:53:42</t>
+        </is>
+      </c>
+      <c r="K973" s="2" t="inlineStr"/>
       <c r="L973" s="2" t="inlineStr"/>
       <c r="M973" s="2" t="inlineStr"/>
     </row>
@@ -53634,7 +53634,7 @@
       </c>
       <c r="C974" s="2" t="inlineStr">
         <is>
-          <t>NARS/纳斯 小粉金液体腮红 #INSATIABLE 酒渍樱桃【5天内发货】</t>
+          <t>Nars纳斯夏季新品液体腮红小粉金管自然服帖显示牛奶粉紫杏茶玫瑰【5天内发货】</t>
         </is>
       </c>
       <c r="D974" s="2" t="inlineStr">
@@ -53667,7 +53667,7 @@
       </c>
       <c r="J974" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:53:42</t>
+          <t>2026-06-16 15:54:01</t>
         </is>
       </c>
       <c r="K974" s="2" t="inlineStr"/>
@@ -53685,7 +53685,7 @@
       </c>
       <c r="C975" s="2" t="inlineStr">
         <is>
-          <t>Nars纳斯夏季新品液体腮红小粉金管自然服帖显示牛奶粉紫杏茶玫瑰【5天内发货】</t>
+          <t>【NARS】纳斯全新小粉金液体腮红 腮紫牛奶粉紫色显嫩自然膨胀收缩色【5天内发货】</t>
         </is>
       </c>
       <c r="D975" s="2" t="inlineStr">
@@ -53718,7 +53718,7 @@
       </c>
       <c r="J975" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:54:01</t>
+          <t>2026-06-16 15:54:20</t>
         </is>
       </c>
       <c r="K975" s="2" t="inlineStr"/>
@@ -53731,22 +53731,22 @@
       </c>
       <c r="B976" s="2" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
+          <t>伊丽莎白雅顿经典唇膏13g</t>
         </is>
       </c>
       <c r="C976" s="2" t="inlineStr">
         <is>
-          <t>【NARS】纳斯全新小粉金液体腮红 腮紫牛奶粉紫色显嫩自然膨胀收缩色【5天内发货】</t>
+          <t>【超值囤货装】伊丽莎白雅顿经典润泽SPF15唇膏8小时保湿滋润防晒</t>
         </is>
       </c>
       <c r="D976" s="2" t="inlineStr">
         <is>
-          <t>纳斯</t>
+          <t>伊丽莎白雅顿</t>
         </is>
       </c>
       <c r="E976" s="2" t="inlineStr">
         <is>
-          <t>纳斯</t>
+          <t>伊丽莎白雅顿</t>
         </is>
       </c>
       <c r="F976" s="2" t="inlineStr">
@@ -53756,7 +53756,7 @@
       </c>
       <c r="G976" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H976" s="3" t="n">
@@ -53764,16 +53764,24 @@
       </c>
       <c r="I976" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J976" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:54:20</t>
-        </is>
-      </c>
-      <c r="K976" s="2" t="inlineStr"/>
-      <c r="L976" s="2" t="inlineStr"/>
+          <t>2026-06-16 15:55:58</t>
+        </is>
+      </c>
+      <c r="K976" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L976" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="M976" s="2" t="inlineStr"/>
     </row>
     <row r="977">
@@ -53787,7 +53795,7 @@
       </c>
       <c r="C977" s="2" t="inlineStr">
         <is>
-          <t>【超值囤货装】伊丽莎白雅顿经典润泽SPF15唇膏8小时保湿滋润防晒</t>
+          <t>【官方正品】伊丽莎白雅顿唇膏经典润泽唇膏雅顿八小时润唇膏</t>
         </is>
       </c>
       <c r="D977" s="2" t="inlineStr">
@@ -53820,7 +53828,7 @@
       </c>
       <c r="J977" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:55:58</t>
+          <t>2026-06-16 15:56:21</t>
         </is>
       </c>
       <c r="K977" s="2" t="inlineStr">
@@ -53879,7 +53887,7 @@
       </c>
       <c r="J978" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:56:21</t>
+          <t>2026-06-16 15:56:49</t>
         </is>
       </c>
       <c r="K978" s="2" t="inlineStr">
@@ -53900,22 +53908,22 @@
       </c>
       <c r="B979" s="2" t="inlineStr">
         <is>
-          <t>伊丽莎白雅顿经典唇膏13g</t>
+          <t>MAC热吻棒67</t>
         </is>
       </c>
       <c r="C979" s="2" t="inlineStr">
         <is>
-          <t>【官方正品】伊丽莎白雅顿唇膏经典润泽唇膏雅顿八小时润唇膏</t>
+          <t>MAC/魅可 热吻棒唇膏口红 显色显白哑光滋润不掉色67狂野棕【5天内发货】</t>
         </is>
       </c>
       <c r="D979" s="2" t="inlineStr">
         <is>
-          <t>伊丽莎白雅顿</t>
+          <t>魅可</t>
         </is>
       </c>
       <c r="E979" s="2" t="inlineStr">
         <is>
-          <t>伊丽莎白雅顿</t>
+          <t>魅可</t>
         </is>
       </c>
       <c r="F979" s="2" t="inlineStr">
@@ -53925,7 +53933,7 @@
       </c>
       <c r="G979" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H979" s="3" t="n">
@@ -53933,25 +53941,471 @@
       </c>
       <c r="I979" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J979" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:56:49</t>
-        </is>
-      </c>
-      <c r="K979" s="2" t="inlineStr">
+          <t>2026-06-17 11:57:16</t>
+        </is>
+      </c>
+      <c r="K979" s="2" t="inlineStr"/>
+      <c r="L979" s="2" t="inlineStr"/>
+      <c r="M979" s="2" t="inlineStr"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="B980" s="2" t="inlineStr">
+        <is>
+          <t>NARS超方瓶粉底液L4</t>
+        </is>
+      </c>
+      <c r="C980" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】超方瓶粉底液持妆持久养肤轻薄轻透奶油肌新年礼物送女友</t>
+        </is>
+      </c>
+      <c r="D980" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E980" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F980" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G980" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H980" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I980" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J980" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:58:53</t>
+        </is>
+      </c>
+      <c r="K980" s="2" t="inlineStr">
         <is>
           <t>规格不匹配；规格匹配失败</t>
         </is>
       </c>
-      <c r="L979" s="2" t="inlineStr">
+      <c r="L980" s="2" t="inlineStr">
         <is>
           <t>匹配失败</t>
         </is>
       </c>
-      <c r="M979" s="2" t="inlineStr"/>
+      <c r="M980" s="2" t="inlineStr"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="B981" s="2" t="inlineStr">
+        <is>
+          <t>NARS超方瓶粉底液L4</t>
+        </is>
+      </c>
+      <c r="C981" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娜斯/纳斯全新超方瓶粉底液L02流光美肌养肤遮瑕持久</t>
+        </is>
+      </c>
+      <c r="D981" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E981" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F981" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G981" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H981" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I981" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J981" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:59:22</t>
+        </is>
+      </c>
+      <c r="K981" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L981" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M981" s="2" t="inlineStr"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="2" t="n">
+        <v>981</v>
+      </c>
+      <c r="B982" s="2" t="inlineStr">
+        <is>
+          <t>NARS超方瓶粉底液L4</t>
+        </is>
+      </c>
+      <c r="C982" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娜斯/纳斯NARS超方瓶粉底液L02流光美肌养肤遮瑕持久</t>
+        </is>
+      </c>
+      <c r="D982" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E982" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F982" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G982" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H982" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I982" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J982" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:59:45</t>
+        </is>
+      </c>
+      <c r="K982" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L982" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M982" s="2" t="inlineStr"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="2" t="n">
+        <v>982</v>
+      </c>
+      <c r="B983" s="2" t="inlineStr">
+        <is>
+          <t>NARS超方瓶粉底液L4</t>
+        </is>
+      </c>
+      <c r="C983" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯超方瓶粉底液新款小方瓶L0L2持久不脱妆养肤保湿遮瑕正品</t>
+        </is>
+      </c>
+      <c r="D983" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E983" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F983" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G983" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H983" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I983" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J983" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:00:11</t>
+        </is>
+      </c>
+      <c r="K983" s="2" t="inlineStr"/>
+      <c r="L983" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 【L4】黄二白 +  美妆蛋</t>
+        </is>
+      </c>
+      <c r="M983" s="2" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="2" t="n">
+        <v>983</v>
+      </c>
+      <c r="B984" s="2" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液#L1</t>
+        </is>
+      </c>
+      <c r="C984" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯 超方瓶流光美肌粉底液 L1 30ml提亮肤色</t>
+        </is>
+      </c>
+      <c r="D984" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="E984" s="2" t="inlineStr">
+        <is>
+          <t>纳斯</t>
+        </is>
+      </c>
+      <c r="F984" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G984" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H984" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I984" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J984" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:43:12</t>
+        </is>
+      </c>
+      <c r="K984" s="2" t="inlineStr"/>
+      <c r="L984" s="2" t="inlineStr"/>
+      <c r="M984" s="2" t="inlineStr"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="2" t="n">
+        <v>984</v>
+      </c>
+      <c r="B985" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+        </is>
+      </c>
+      <c r="C985" s="2" t="inlineStr">
+        <is>
+          <t>【拉夫劳伦】Ralph Lauren POLO俱乐部Ralph'sClub男士浓淡香水木质调【5天内发货】</t>
+        </is>
+      </c>
+      <c r="D985" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦</t>
+        </is>
+      </c>
+      <c r="E985" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦</t>
+        </is>
+      </c>
+      <c r="F985" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G985" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H985" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I985" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J985" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:45:06</t>
+        </is>
+      </c>
+      <c r="K985" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L985" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M985" s="2" t="inlineStr"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="B986" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+        </is>
+      </c>
+      <c r="C986" s="2" t="inlineStr">
+        <is>
+          <t>【拉夫劳伦】俱乐部小熊限定香水l肖战同款馥奇木质香男士持久淡香</t>
+        </is>
+      </c>
+      <c r="D986" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦</t>
+        </is>
+      </c>
+      <c r="E986" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦</t>
+        </is>
+      </c>
+      <c r="F986" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G986" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H986" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I986" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J986" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:45:26</t>
+        </is>
+      </c>
+      <c r="K986" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="L986" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="M986" s="2" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="2" t="n">
+        <v>986</v>
+      </c>
+      <c r="B987" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+        </is>
+      </c>
+      <c r="C987" s="2" t="inlineStr">
+        <is>
+          <t>【拉夫劳伦】俱乐部男士香水100ml 木质调持久留香 秋冬氛围感渣男香</t>
+        </is>
+      </c>
+      <c r="D987" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦</t>
+        </is>
+      </c>
+      <c r="E987" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦</t>
+        </is>
+      </c>
+      <c r="F987" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G987" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H987" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I987" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J987" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:45:41</t>
+        </is>
+      </c>
+      <c r="K987" s="2" t="inlineStr"/>
+      <c r="L987" s="2" t="inlineStr"/>
+      <c r="M987" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
